--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -6953,6 +6953,11 @@
       <c r="C53" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="F53" s="0" t="inlineStr">
+        <is>
+          <t>2000100001,</t>
+        </is>
+      </c>
       <c r="G53" s="0" t="n">
         <v>1000001</v>
       </c>
@@ -6962,10 +6967,15 @@
         </is>
       </c>
       <c r="J53" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="N53" s="0" t="inlineStr">
+        <is>
+          <t>Attack6</t>
+        </is>
       </c>
       <c r="P53" s="0" t="n">
-        <v>100001</v>
+        <v>100002</v>
       </c>
       <c r="S53" s="0" t="n">
         <v>1</v>
@@ -6998,7 +7008,7 @@
         <v>0</v>
       </c>
       <c r="AG53" s="0" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AJ53" s="0" t="n">
         <v>1</v>
@@ -7217,11 +7227,16 @@
         </is>
       </c>
       <c r="J56" s="0" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Walk4</t>
+        </is>
       </c>
       <c r="N56" s="0" t="inlineStr">
         <is>
-          <t>Attack5</t>
+          <t>Attack7</t>
         </is>
       </c>
       <c r="P56" s="0" t="n">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -7142,6 +7142,11 @@
       <c r="J55" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Attack8</t>
+        </is>
+      </c>
       <c r="P55" s="0" t="n">
         <v>101006</v>
       </c>
@@ -7229,7 +7234,7 @@
       <c r="J56" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M56" s="0" t="inlineStr">
         <is>
           <t>Walk4</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -1080,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT115"/>
+  <dimension ref="A1:AT116"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="7.375" customWidth="1" style="3" min="1" max="1"/>
@@ -6943,20 +6943,15 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>104001</v>
+        <v>103104</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>人类-盗贼</t>
+          <t>人类-大魔法师（雷）</t>
         </is>
       </c>
       <c r="C53" s="0" t="n">
         <v>2</v>
-      </c>
-      <c r="F53" s="0" t="inlineStr">
-        <is>
-          <t>2000100001,</t>
-        </is>
       </c>
       <c r="G53" s="0" t="n">
         <v>1000001</v>
@@ -6967,21 +6962,26 @@
         </is>
       </c>
       <c r="J53" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N53" s="0" t="inlineStr">
         <is>
-          <t>Attack6</t>
+          <t>Attack2</t>
         </is>
       </c>
       <c r="P53" s="0" t="n">
-        <v>100002</v>
+        <v>800001</v>
+      </c>
+      <c r="Q53" s="0" t="inlineStr">
+        <is>
+          <t>0,0.6,0</t>
+        </is>
       </c>
       <c r="S53" s="0" t="n">
         <v>1</v>
       </c>
       <c r="T53" s="0" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="U53" s="0" t="n">
         <v>1</v>
@@ -6999,7 +6999,7 @@
         <v>0.5</v>
       </c>
       <c r="AB53" s="0" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AE53" s="0" t="n">
         <v>10</v>
@@ -7008,7 +7008,7 @@
         <v>0</v>
       </c>
       <c r="AG53" s="0" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AJ53" s="0" t="n">
         <v>1</v>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AL53" s="0" t="inlineStr">
         <is>
-          <t>ui_class_3</t>
+          <t>ui_class_5</t>
         </is>
       </c>
       <c r="AM53" s="0" t="inlineStr">
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="AR53" s="0" t="n">
-        <v>104001</v>
+        <v>103104</v>
       </c>
       <c r="AT53" s="0" t="inlineStr">
         <is>
@@ -7037,15 +7037,20 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>104002</v>
+        <v>104001</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>人类-双持战士</t>
+          <t>人类-盗贼</t>
         </is>
       </c>
       <c r="C54" s="0" t="n">
         <v>2</v>
+      </c>
+      <c r="F54" s="0" t="inlineStr">
+        <is>
+          <t>2000100001,</t>
+        </is>
       </c>
       <c r="G54" s="0" t="n">
         <v>1000001</v>
@@ -7056,10 +7061,15 @@
         </is>
       </c>
       <c r="J54" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="N54" s="0" t="inlineStr">
+        <is>
+          <t>Attack6</t>
+        </is>
       </c>
       <c r="P54" s="0" t="n">
-        <v>100001</v>
+        <v>100002</v>
       </c>
       <c r="S54" s="0" t="n">
         <v>1</v>
@@ -7092,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="AG54" s="0" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AJ54" s="0" t="n">
         <v>1</v>
@@ -7111,7 +7121,7 @@
         </is>
       </c>
       <c r="AR54" s="0" t="n">
-        <v>104002</v>
+        <v>104001</v>
       </c>
       <c r="AT54" s="0" t="inlineStr">
         <is>
@@ -7121,11 +7131,11 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>104101</v>
+        <v>104002</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>人类-大剑战士</t>
+          <t>人类-双持战士</t>
         </is>
       </c>
       <c r="C55" s="0" t="n">
@@ -7140,15 +7150,10 @@
         </is>
       </c>
       <c r="J55" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Attack8</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="P55" s="0" t="n">
-        <v>101006</v>
+        <v>100001</v>
       </c>
       <c r="S55" s="0" t="n">
         <v>1</v>
@@ -7174,9 +7179,6 @@
       <c r="AB55" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="AD55" s="0" t="n">
-        <v>100</v>
-      </c>
       <c r="AE55" s="0" t="n">
         <v>10</v>
       </c>
@@ -7194,7 +7196,7 @@
       </c>
       <c r="AL55" s="0" t="inlineStr">
         <is>
-          <t>ui_class_7</t>
+          <t>ui_class_3</t>
         </is>
       </c>
       <c r="AM55" s="0" t="inlineStr">
@@ -7203,7 +7205,7 @@
         </is>
       </c>
       <c r="AR55" s="0" t="n">
-        <v>104101</v>
+        <v>104002</v>
       </c>
       <c r="AT55" s="0" t="inlineStr">
         <is>
@@ -7213,11 +7215,11 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>104102</v>
+        <v>104101</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>人类-大盾战士</t>
+          <t>人类-大剑战士</t>
         </is>
       </c>
       <c r="C56" s="0" t="n">
@@ -7232,20 +7234,15 @@
         </is>
       </c>
       <c r="J56" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="M56" s="0" t="inlineStr">
-        <is>
-          <t>Walk4</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="N56" s="0" t="inlineStr">
         <is>
-          <t>Attack7</t>
+          <t>Attack8</t>
         </is>
       </c>
       <c r="P56" s="0" t="n">
-        <v>100001</v>
+        <v>101006</v>
       </c>
       <c r="S56" s="0" t="n">
         <v>1</v>
@@ -7300,121 +7297,109 @@
         </is>
       </c>
       <c r="AR56" s="0" t="n">
+        <v>104101</v>
+      </c>
+      <c r="AT56" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="n">
         <v>104102</v>
       </c>
-      <c r="AT56" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="n">
-        <v>900001</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>测试骷髅战士</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="n"/>
-      <c r="G57" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="H57" s="5" t="n">
-        <v>21010001</v>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>人类-大盾战士</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2000600001,</t>
+        </is>
+      </c>
+      <c r="G57" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="I57" s="0" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J57" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K57" s="5" t="n"/>
-      <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
-      <c r="N57" s="5" t="inlineStr">
-        <is>
-          <t>Attack2</t>
-        </is>
-      </c>
-      <c r="O57" s="5" t="n"/>
-      <c r="P57" s="5" t="n">
+      <c r="J57" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="M57" s="0" t="inlineStr">
+        <is>
+          <t>Walk4</t>
+        </is>
+      </c>
+      <c r="N57" s="0" t="inlineStr">
+        <is>
+          <t>Attack7</t>
+        </is>
+      </c>
+      <c r="P57" s="0" t="n">
         <v>100001</v>
       </c>
-      <c r="Q57" s="5" t="n"/>
-      <c r="R57" s="5" t="n"/>
-      <c r="S57" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T57" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U57" s="5" t="n">
+      <c r="S57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U57" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V57" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W57" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X57" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y57" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z57" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA57" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB57" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AC57" s="5" t="n"/>
-      <c r="AD57" s="5" t="n"/>
-      <c r="AE57" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH57" s="5" t="n"/>
-      <c r="AI57" s="5" t="n"/>
-      <c r="AJ57" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK57" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="AL57" s="5" t="inlineStr">
-        <is>
-          <t>ui_class_3</t>
-        </is>
-      </c>
-      <c r="AM57" s="5" t="inlineStr">
-        <is>
-          <t>Card_Scene_1</t>
-        </is>
-      </c>
-      <c r="AN57" s="5" t="n">
-        <v>300200001</v>
-      </c>
-      <c r="AR57" s="5" t="n">
-        <v>900001</v>
+      <c r="W57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X57" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y57" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB57" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD57" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE57" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK57" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="AL57" s="0" t="inlineStr">
+        <is>
+          <t>ui_class_7</t>
+        </is>
+      </c>
+      <c r="AM57" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_2</t>
+        </is>
+      </c>
+      <c r="AR57" s="0" t="n">
+        <v>104102</v>
       </c>
       <c r="AT57" s="0" t="inlineStr">
         <is>
@@ -7424,11 +7409,11 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
-        <v>900002</v>
+        <v>900001</v>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>测试骷髅投手</t>
+          <t>测试骷髅战士</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
@@ -7441,7 +7426,7 @@
         <v>2000001</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>21000001</v>
+        <v>21010001</v>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
@@ -7449,31 +7434,27 @@
         </is>
       </c>
       <c r="J58" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K58" s="5" t="n"/>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="5" t="n"/>
       <c r="N58" s="5" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Attack2</t>
         </is>
       </c>
       <c r="O58" s="5" t="n"/>
       <c r="P58" s="5" t="n">
-        <v>200001</v>
-      </c>
-      <c r="Q58" s="5" t="inlineStr">
-        <is>
-          <t>0,0.7,0</t>
-        </is>
-      </c>
+        <v>100001</v>
+      </c>
+      <c r="Q58" s="5" t="n"/>
       <c r="R58" s="5" t="n"/>
       <c r="S58" s="5" t="n">
         <v>2</v>
       </c>
       <c r="T58" s="5" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="U58" s="5" t="n">
         <v>1</v>
@@ -7491,7 +7472,7 @@
         <v>0.5</v>
       </c>
       <c r="Z58" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA58" s="5" t="n">
         <v>10</v>
@@ -7520,87 +7501,137 @@
       </c>
       <c r="AL58" s="5" t="inlineStr">
         <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="AM58" s="5" t="inlineStr">
+        <is>
+          <t>Card_Scene_1</t>
+        </is>
+      </c>
+      <c r="AN58" s="5" t="n">
+        <v>300200001</v>
+      </c>
+      <c r="AR58" s="5" t="n">
+        <v>900001</v>
+      </c>
+      <c r="AT58" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>900002</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>测试骷髅投手</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>21000001</v>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>1,2,3,10,</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="5" t="n">
+        <v>200001</v>
+      </c>
+      <c r="Q59" s="5" t="inlineStr">
+        <is>
+          <t>0,0.7,0</t>
+        </is>
+      </c>
+      <c r="R59" s="5" t="n"/>
+      <c r="S59" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T59" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="U59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X59" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y59" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z59" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA59" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB59" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AC59" s="5" t="n"/>
+      <c r="AD59" s="5" t="n"/>
+      <c r="AE59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH59" s="5" t="n"/>
+      <c r="AI59" s="5" t="n"/>
+      <c r="AJ59" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK59" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="AL59" s="5" t="inlineStr">
+        <is>
           <t>ui_class_6</t>
         </is>
       </c>
-      <c r="AM58" s="5" t="inlineStr">
+      <c r="AM59" s="5" t="inlineStr">
         <is>
           <t>Card_Scene_1</t>
         </is>
       </c>
-      <c r="AN58" s="5" t="n">
+      <c r="AN59" s="5" t="n">
         <v>300200002</v>
       </c>
-      <c r="AR58" s="5" t="n">
+      <c r="AR59" s="5" t="n">
         <v>900002</v>
-      </c>
-      <c r="AT58" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="0" t="n">
-        <v>989996</v>
-      </c>
-      <c r="B59" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C59" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P59" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S59" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T59" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U59" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V59" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X59" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y59" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z59" s="0" t="n"/>
-      <c r="AB59" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE59" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ59" s="0" t="n">
-        <v>989996</v>
-      </c>
-      <c r="AK59" s="0" t="n"/>
-      <c r="AL59" s="0" t="n"/>
-      <c r="AM59" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR59" s="0" t="n">
-        <v>1</v>
       </c>
       <c r="AT59" s="0" t="inlineStr">
         <is>
@@ -7610,7 +7641,7 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>989997</v>
+        <v>989996</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
@@ -7658,7 +7689,7 @@
         <v>10</v>
       </c>
       <c r="AJ60" s="0" t="n">
-        <v>989997</v>
+        <v>989996</v>
       </c>
       <c r="AK60" s="0" t="n"/>
       <c r="AL60" s="0" t="n"/>
@@ -7678,7 +7709,7 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>989998</v>
+        <v>989997</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
@@ -7726,7 +7757,7 @@
         <v>10</v>
       </c>
       <c r="AJ61" s="0" t="n">
-        <v>989998</v>
+        <v>989997</v>
       </c>
       <c r="AK61" s="0" t="n"/>
       <c r="AL61" s="0" t="n"/>
@@ -7746,7 +7777,7 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>989999</v>
+        <v>989998</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
@@ -7794,8 +7825,10 @@
         <v>10</v>
       </c>
       <c r="AJ62" s="0" t="n">
-        <v>989999</v>
-      </c>
+        <v>989998</v>
+      </c>
+      <c r="AK62" s="0" t="n"/>
+      <c r="AL62" s="0" t="n"/>
       <c r="AM62" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -7812,7 +7845,7 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>999947</v>
+        <v>989999</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
@@ -7860,10 +7893,8 @@
         <v>10</v>
       </c>
       <c r="AJ63" s="0" t="n">
-        <v>999947</v>
-      </c>
-      <c r="AK63" s="0" t="n"/>
-      <c r="AL63" s="0" t="n"/>
+        <v>989999</v>
+      </c>
       <c r="AM63" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -7880,7 +7911,7 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>999948</v>
+        <v>999947</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
@@ -7928,7 +7959,7 @@
         <v>10</v>
       </c>
       <c r="AJ64" s="0" t="n">
-        <v>999948</v>
+        <v>999947</v>
       </c>
       <c r="AK64" s="0" t="n"/>
       <c r="AL64" s="0" t="n"/>
@@ -7948,7 +7979,7 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>999949</v>
+        <v>999948</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
@@ -7996,7 +8027,7 @@
         <v>10</v>
       </c>
       <c r="AJ65" s="0" t="n">
-        <v>999949</v>
+        <v>999948</v>
       </c>
       <c r="AK65" s="0" t="n"/>
       <c r="AL65" s="0" t="n"/>
@@ -8016,7 +8047,7 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>999950</v>
+        <v>999949</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
@@ -8064,7 +8095,7 @@
         <v>10</v>
       </c>
       <c r="AJ66" s="0" t="n">
-        <v>999950</v>
+        <v>999949</v>
       </c>
       <c r="AK66" s="0" t="n"/>
       <c r="AL66" s="0" t="n"/>
@@ -8084,7 +8115,7 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>999951</v>
+        <v>999950</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
@@ -8132,7 +8163,7 @@
         <v>10</v>
       </c>
       <c r="AJ67" s="0" t="n">
-        <v>999951</v>
+        <v>999950</v>
       </c>
       <c r="AK67" s="0" t="n"/>
       <c r="AL67" s="0" t="n"/>
@@ -8152,7 +8183,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>999952</v>
+        <v>999951</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
@@ -8200,7 +8231,7 @@
         <v>10</v>
       </c>
       <c r="AJ68" s="0" t="n">
-        <v>999952</v>
+        <v>999951</v>
       </c>
       <c r="AK68" s="0" t="n"/>
       <c r="AL68" s="0" t="n"/>
@@ -8220,7 +8251,7 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>999953</v>
+        <v>999952</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
@@ -8268,7 +8299,7 @@
         <v>10</v>
       </c>
       <c r="AJ69" s="0" t="n">
-        <v>999953</v>
+        <v>999952</v>
       </c>
       <c r="AK69" s="0" t="n"/>
       <c r="AL69" s="0" t="n"/>
@@ -8288,7 +8319,7 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>999954</v>
+        <v>999953</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
@@ -8336,7 +8367,7 @@
         <v>10</v>
       </c>
       <c r="AJ70" s="0" t="n">
-        <v>999954</v>
+        <v>999953</v>
       </c>
       <c r="AK70" s="0" t="n"/>
       <c r="AL70" s="0" t="n"/>
@@ -8356,7 +8387,7 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>999955</v>
+        <v>999954</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
@@ -8404,7 +8435,7 @@
         <v>10</v>
       </c>
       <c r="AJ71" s="0" t="n">
-        <v>999955</v>
+        <v>999954</v>
       </c>
       <c r="AK71" s="0" t="n"/>
       <c r="AL71" s="0" t="n"/>
@@ -8424,7 +8455,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>999956</v>
+        <v>999955</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
@@ -8472,7 +8503,7 @@
         <v>10</v>
       </c>
       <c r="AJ72" s="0" t="n">
-        <v>999956</v>
+        <v>999955</v>
       </c>
       <c r="AK72" s="0" t="n"/>
       <c r="AL72" s="0" t="n"/>
@@ -8492,7 +8523,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>999957</v>
+        <v>999956</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
@@ -8540,7 +8571,7 @@
         <v>10</v>
       </c>
       <c r="AJ73" s="0" t="n">
-        <v>999957</v>
+        <v>999956</v>
       </c>
       <c r="AK73" s="0" t="n"/>
       <c r="AL73" s="0" t="n"/>
@@ -8560,7 +8591,7 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>999958</v>
+        <v>999957</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
@@ -8608,7 +8639,7 @@
         <v>10</v>
       </c>
       <c r="AJ74" s="0" t="n">
-        <v>999958</v>
+        <v>999957</v>
       </c>
       <c r="AK74" s="0" t="n"/>
       <c r="AL74" s="0" t="n"/>
@@ -8628,7 +8659,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>999959</v>
+        <v>999958</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
@@ -8676,7 +8707,7 @@
         <v>10</v>
       </c>
       <c r="AJ75" s="0" t="n">
-        <v>999959</v>
+        <v>999958</v>
       </c>
       <c r="AK75" s="0" t="n"/>
       <c r="AL75" s="0" t="n"/>
@@ -8696,7 +8727,7 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>999960</v>
+        <v>999959</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
@@ -8744,7 +8775,7 @@
         <v>10</v>
       </c>
       <c r="AJ76" s="0" t="n">
-        <v>999960</v>
+        <v>999959</v>
       </c>
       <c r="AK76" s="0" t="n"/>
       <c r="AL76" s="0" t="n"/>
@@ -8764,7 +8795,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>999961</v>
+        <v>999960</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
@@ -8812,7 +8843,7 @@
         <v>10</v>
       </c>
       <c r="AJ77" s="0" t="n">
-        <v>999961</v>
+        <v>999960</v>
       </c>
       <c r="AK77" s="0" t="n"/>
       <c r="AL77" s="0" t="n"/>
@@ -8832,7 +8863,7 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>999962</v>
+        <v>999961</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
@@ -8880,7 +8911,7 @@
         <v>10</v>
       </c>
       <c r="AJ78" s="0" t="n">
-        <v>999962</v>
+        <v>999961</v>
       </c>
       <c r="AK78" s="0" t="n"/>
       <c r="AL78" s="0" t="n"/>
@@ -8900,7 +8931,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>999963</v>
+        <v>999962</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
@@ -8948,7 +8979,7 @@
         <v>10</v>
       </c>
       <c r="AJ79" s="0" t="n">
-        <v>999963</v>
+        <v>999962</v>
       </c>
       <c r="AK79" s="0" t="n"/>
       <c r="AL79" s="0" t="n"/>
@@ -8968,7 +8999,7 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>999964</v>
+        <v>999963</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
@@ -9016,7 +9047,7 @@
         <v>10</v>
       </c>
       <c r="AJ80" s="0" t="n">
-        <v>999964</v>
+        <v>999963</v>
       </c>
       <c r="AK80" s="0" t="n"/>
       <c r="AL80" s="0" t="n"/>
@@ -9036,7 +9067,7 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>999965</v>
+        <v>999964</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
@@ -9084,7 +9115,7 @@
         <v>10</v>
       </c>
       <c r="AJ81" s="0" t="n">
-        <v>999965</v>
+        <v>999964</v>
       </c>
       <c r="AK81" s="0" t="n"/>
       <c r="AL81" s="0" t="n"/>
@@ -9104,7 +9135,7 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>999966</v>
+        <v>999965</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
@@ -9152,7 +9183,7 @@
         <v>10</v>
       </c>
       <c r="AJ82" s="0" t="n">
-        <v>999966</v>
+        <v>999965</v>
       </c>
       <c r="AK82" s="0" t="n"/>
       <c r="AL82" s="0" t="n"/>
@@ -9172,7 +9203,7 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>999967</v>
+        <v>999966</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
@@ -9220,7 +9251,7 @@
         <v>10</v>
       </c>
       <c r="AJ83" s="0" t="n">
-        <v>999967</v>
+        <v>999966</v>
       </c>
       <c r="AK83" s="0" t="n"/>
       <c r="AL83" s="0" t="n"/>
@@ -9240,7 +9271,7 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>999968</v>
+        <v>999967</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
@@ -9288,7 +9319,7 @@
         <v>10</v>
       </c>
       <c r="AJ84" s="0" t="n">
-        <v>999968</v>
+        <v>999967</v>
       </c>
       <c r="AK84" s="0" t="n"/>
       <c r="AL84" s="0" t="n"/>
@@ -9308,7 +9339,7 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>999969</v>
+        <v>999968</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
@@ -9356,7 +9387,7 @@
         <v>10</v>
       </c>
       <c r="AJ85" s="0" t="n">
-        <v>999969</v>
+        <v>999968</v>
       </c>
       <c r="AK85" s="0" t="n"/>
       <c r="AL85" s="0" t="n"/>
@@ -9376,7 +9407,7 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>999970</v>
+        <v>999969</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
@@ -9424,7 +9455,7 @@
         <v>10</v>
       </c>
       <c r="AJ86" s="0" t="n">
-        <v>999970</v>
+        <v>999969</v>
       </c>
       <c r="AK86" s="0" t="n"/>
       <c r="AL86" s="0" t="n"/>
@@ -9444,7 +9475,7 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>999971</v>
+        <v>999970</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
@@ -9492,7 +9523,7 @@
         <v>10</v>
       </c>
       <c r="AJ87" s="0" t="n">
-        <v>999971</v>
+        <v>999970</v>
       </c>
       <c r="AK87" s="0" t="n"/>
       <c r="AL87" s="0" t="n"/>
@@ -9512,7 +9543,7 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>999972</v>
+        <v>999971</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
@@ -9560,7 +9591,7 @@
         <v>10</v>
       </c>
       <c r="AJ88" s="0" t="n">
-        <v>999972</v>
+        <v>999971</v>
       </c>
       <c r="AK88" s="0" t="n"/>
       <c r="AL88" s="0" t="n"/>
@@ -9580,7 +9611,7 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>999973</v>
+        <v>999972</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
@@ -9628,7 +9659,7 @@
         <v>10</v>
       </c>
       <c r="AJ89" s="0" t="n">
-        <v>999973</v>
+        <v>999972</v>
       </c>
       <c r="AK89" s="0" t="n"/>
       <c r="AL89" s="0" t="n"/>
@@ -9648,7 +9679,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>999974</v>
+        <v>999973</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
@@ -9696,7 +9727,7 @@
         <v>10</v>
       </c>
       <c r="AJ90" s="0" t="n">
-        <v>999974</v>
+        <v>999973</v>
       </c>
       <c r="AK90" s="0" t="n"/>
       <c r="AL90" s="0" t="n"/>
@@ -9716,7 +9747,7 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>999975</v>
+        <v>999974</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
@@ -9764,7 +9795,7 @@
         <v>10</v>
       </c>
       <c r="AJ91" s="0" t="n">
-        <v>999975</v>
+        <v>999974</v>
       </c>
       <c r="AK91" s="0" t="n"/>
       <c r="AL91" s="0" t="n"/>
@@ -9784,7 +9815,7 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>999976</v>
+        <v>999975</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
@@ -9832,7 +9863,7 @@
         <v>10</v>
       </c>
       <c r="AJ92" s="0" t="n">
-        <v>999976</v>
+        <v>999975</v>
       </c>
       <c r="AK92" s="0" t="n"/>
       <c r="AL92" s="0" t="n"/>
@@ -9852,7 +9883,7 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>999977</v>
+        <v>999976</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
@@ -9900,7 +9931,7 @@
         <v>10</v>
       </c>
       <c r="AJ93" s="0" t="n">
-        <v>999977</v>
+        <v>999976</v>
       </c>
       <c r="AK93" s="0" t="n"/>
       <c r="AL93" s="0" t="n"/>
@@ -9920,7 +9951,7 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>999978</v>
+        <v>999977</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
@@ -9968,7 +9999,7 @@
         <v>10</v>
       </c>
       <c r="AJ94" s="0" t="n">
-        <v>999978</v>
+        <v>999977</v>
       </c>
       <c r="AK94" s="0" t="n"/>
       <c r="AL94" s="0" t="n"/>
@@ -9988,7 +10019,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>999979</v>
+        <v>999978</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
@@ -10036,7 +10067,7 @@
         <v>10</v>
       </c>
       <c r="AJ95" s="0" t="n">
-        <v>999979</v>
+        <v>999978</v>
       </c>
       <c r="AK95" s="0" t="n"/>
       <c r="AL95" s="0" t="n"/>
@@ -10056,7 +10087,7 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>999980</v>
+        <v>999979</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
@@ -10104,7 +10135,7 @@
         <v>10</v>
       </c>
       <c r="AJ96" s="0" t="n">
-        <v>999980</v>
+        <v>999979</v>
       </c>
       <c r="AK96" s="0" t="n"/>
       <c r="AL96" s="0" t="n"/>
@@ -10124,7 +10155,7 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>999981</v>
+        <v>999980</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
@@ -10172,7 +10203,7 @@
         <v>10</v>
       </c>
       <c r="AJ97" s="0" t="n">
-        <v>999981</v>
+        <v>999980</v>
       </c>
       <c r="AK97" s="0" t="n"/>
       <c r="AL97" s="0" t="n"/>
@@ -10192,7 +10223,7 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>999982</v>
+        <v>999981</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
@@ -10226,6 +10257,7 @@
       <c r="Y98" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="Z98" s="0" t="n"/>
       <c r="AB98" s="0" t="n">
         <v>100</v>
       </c>
@@ -10239,8 +10271,10 @@
         <v>10</v>
       </c>
       <c r="AJ98" s="0" t="n">
-        <v>999982</v>
-      </c>
+        <v>999981</v>
+      </c>
+      <c r="AK98" s="0" t="n"/>
+      <c r="AL98" s="0" t="n"/>
       <c r="AM98" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -10257,7 +10291,7 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>999983</v>
+        <v>999982</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
@@ -10304,7 +10338,7 @@
         <v>10</v>
       </c>
       <c r="AJ99" s="0" t="n">
-        <v>999983</v>
+        <v>999982</v>
       </c>
       <c r="AM99" s="0" t="inlineStr">
         <is>
@@ -10322,7 +10356,7 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>999984</v>
+        <v>999983</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
@@ -10369,7 +10403,7 @@
         <v>10</v>
       </c>
       <c r="AJ100" s="0" t="n">
-        <v>999984</v>
+        <v>999983</v>
       </c>
       <c r="AM100" s="0" t="inlineStr">
         <is>
@@ -10387,7 +10421,7 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>999985</v>
+        <v>999984</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
@@ -10434,7 +10468,7 @@
         <v>10</v>
       </c>
       <c r="AJ101" s="0" t="n">
-        <v>999985</v>
+        <v>999984</v>
       </c>
       <c r="AM101" s="0" t="inlineStr">
         <is>
@@ -10452,7 +10486,7 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>999986</v>
+        <v>999985</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
@@ -10499,7 +10533,7 @@
         <v>10</v>
       </c>
       <c r="AJ102" s="0" t="n">
-        <v>999986</v>
+        <v>999985</v>
       </c>
       <c r="AM102" s="0" t="inlineStr">
         <is>
@@ -10517,7 +10551,7 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>999987</v>
+        <v>999986</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
@@ -10564,7 +10598,7 @@
         <v>10</v>
       </c>
       <c r="AJ103" s="0" t="n">
-        <v>999987</v>
+        <v>999986</v>
       </c>
       <c r="AM103" s="0" t="inlineStr">
         <is>
@@ -10582,7 +10616,7 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>999988</v>
+        <v>999987</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
@@ -10629,7 +10663,7 @@
         <v>10</v>
       </c>
       <c r="AJ104" s="0" t="n">
-        <v>999988</v>
+        <v>999987</v>
       </c>
       <c r="AM104" s="0" t="inlineStr">
         <is>
@@ -10647,7 +10681,7 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>999989</v>
+        <v>999988</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
@@ -10694,7 +10728,7 @@
         <v>10</v>
       </c>
       <c r="AJ105" s="0" t="n">
-        <v>999989</v>
+        <v>999988</v>
       </c>
       <c r="AM105" s="0" t="inlineStr">
         <is>
@@ -10712,7 +10746,7 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>999990</v>
+        <v>999989</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
@@ -10759,7 +10793,7 @@
         <v>10</v>
       </c>
       <c r="AJ106" s="0" t="n">
-        <v>999990</v>
+        <v>999989</v>
       </c>
       <c r="AM106" s="0" t="inlineStr">
         <is>
@@ -10777,7 +10811,7 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>999991</v>
+        <v>999990</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
@@ -10824,7 +10858,7 @@
         <v>10</v>
       </c>
       <c r="AJ107" s="0" t="n">
-        <v>999991</v>
+        <v>999990</v>
       </c>
       <c r="AM107" s="0" t="inlineStr">
         <is>
@@ -10842,7 +10876,7 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>999992</v>
+        <v>999991</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
@@ -10889,7 +10923,7 @@
         <v>10</v>
       </c>
       <c r="AJ108" s="0" t="n">
-        <v>999992</v>
+        <v>999991</v>
       </c>
       <c r="AM108" s="0" t="inlineStr">
         <is>
@@ -10907,7 +10941,7 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>999993</v>
+        <v>999992</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
@@ -10954,7 +10988,7 @@
         <v>10</v>
       </c>
       <c r="AJ109" s="0" t="n">
-        <v>999993</v>
+        <v>999992</v>
       </c>
       <c r="AM109" s="0" t="inlineStr">
         <is>
@@ -10972,7 +11006,7 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>999994</v>
+        <v>999993</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
@@ -11019,7 +11053,7 @@
         <v>10</v>
       </c>
       <c r="AJ110" s="0" t="n">
-        <v>999994</v>
+        <v>999993</v>
       </c>
       <c r="AM110" s="0" t="inlineStr">
         <is>
@@ -11037,7 +11071,7 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>999995</v>
+        <v>999994</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
@@ -11084,7 +11118,7 @@
         <v>10</v>
       </c>
       <c r="AJ111" s="0" t="n">
-        <v>999995</v>
+        <v>999994</v>
       </c>
       <c r="AM111" s="0" t="inlineStr">
         <is>
@@ -11102,7 +11136,7 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>999996</v>
+        <v>999995</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
@@ -11149,7 +11183,7 @@
         <v>10</v>
       </c>
       <c r="AJ112" s="0" t="n">
-        <v>999996</v>
+        <v>999995</v>
       </c>
       <c r="AM112" s="0" t="inlineStr">
         <is>
@@ -11167,7 +11201,7 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>999997</v>
+        <v>999996</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
@@ -11214,7 +11248,7 @@
         <v>10</v>
       </c>
       <c r="AJ113" s="0" t="n">
-        <v>999997</v>
+        <v>999996</v>
       </c>
       <c r="AM113" s="0" t="inlineStr">
         <is>
@@ -11232,7 +11266,7 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>999998</v>
+        <v>999997</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
@@ -11279,7 +11313,7 @@
         <v>10</v>
       </c>
       <c r="AJ114" s="0" t="n">
-        <v>999998</v>
+        <v>999997</v>
       </c>
       <c r="AM114" s="0" t="inlineStr">
         <is>
@@ -11297,7 +11331,7 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>999999</v>
+        <v>999998</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
@@ -11344,17 +11378,82 @@
         <v>10</v>
       </c>
       <c r="AJ115" s="0" t="n">
+        <v>999998</v>
+      </c>
+      <c r="AM115" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_4</t>
+        </is>
+      </c>
+      <c r="AR115" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT115" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="n">
         <v>999999</v>
       </c>
-      <c r="AM115" s="0" t="inlineStr">
+      <c r="B116" s="0" t="inlineStr">
+        <is>
+          <t>测试数据</t>
+        </is>
+      </c>
+      <c r="C116" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P116" s="0" t="n">
+        <v>200001</v>
+      </c>
+      <c r="S116" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="T116" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="U116" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V116" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X116" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y116" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB116" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE116" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF116" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG116" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ116" s="0" t="n">
+        <v>999999</v>
+      </c>
+      <c r="AM116" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AR115" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT115" s="0" t="inlineStr">
+      <c r="AR116" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT116" s="0" t="inlineStr">
         <is>
           <t>1,3,4,6</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -9,7 +9,7 @@
     <sheet name="CreatureInfo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CreatureInfo'!$A$1:$AN$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CreatureInfo'!$A$1:$AN$116</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="Q4" s="0" t="inlineStr">
         <is>
-          <t>0,0.6,0</t>
+          <t>0,0.5,0</t>
         </is>
       </c>
       <c r="U4" s="0" t="n">
@@ -2367,6 +2367,11 @@
       <c r="P11" s="1" t="n">
         <v>101005</v>
       </c>
+      <c r="Q11" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
+        </is>
+      </c>
       <c r="S11" s="1" t="n">
         <v>2</v>
       </c>
@@ -2814,6 +2819,11 @@
       <c r="P15" s="1" t="n">
         <v>100001</v>
       </c>
+      <c r="Q15" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
+        </is>
+      </c>
       <c r="S15" s="1" t="n">
         <v>2</v>
       </c>
@@ -4528,6 +4538,7 @@
       <c r="G31" s="1" t="n">
         <v>5000001</v>
       </c>
+      <c r="H31" s="1" t="n"/>
       <c r="I31" s="1" t="inlineStr">
         <is>
           <t>1,2,3,5</t>
@@ -4647,6 +4658,11 @@
       </c>
       <c r="P32" s="1" t="n">
         <v>100001</v>
+      </c>
+      <c r="Q32" s="1" t="inlineStr">
+        <is>
+          <t>0,0.3,0</t>
+        </is>
       </c>
       <c r="S32" s="1" t="n">
         <v>2</v>
@@ -5666,7 +5682,11 @@
       <c r="P41" s="4" t="n">
         <v>100001</v>
       </c>
-      <c r="Q41" s="4" t="inlineStr"/>
+      <c r="Q41" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
+        </is>
+      </c>
       <c r="R41" s="4" t="n"/>
       <c r="S41" s="4" t="n">
         <v>1</v>
@@ -5772,7 +5792,11 @@
       <c r="P42" s="4" t="n">
         <v>100001</v>
       </c>
-      <c r="Q42" s="4" t="n"/>
+      <c r="Q42" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
+        </is>
+      </c>
       <c r="R42" s="4" t="n"/>
       <c r="S42" s="4" t="n">
         <v>1</v>
@@ -6872,7 +6896,7 @@
       </c>
       <c r="Q52" s="4" t="inlineStr">
         <is>
-          <t>0,6,0</t>
+          <t>0,0.6,0</t>
         </is>
       </c>
       <c r="R52" s="4" t="n"/>
@@ -6972,7 +6996,7 @@
       <c r="P53" s="0" t="n">
         <v>800001</v>
       </c>
-      <c r="Q53" s="0" t="inlineStr">
+      <c r="Q53" s="4" t="inlineStr">
         <is>
           <t>0,0.6,0</t>
         </is>
@@ -7071,6 +7095,11 @@
       <c r="P54" s="0" t="n">
         <v>100002</v>
       </c>
+      <c r="Q54" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
+        </is>
+      </c>
       <c r="S54" s="0" t="n">
         <v>1</v>
       </c>
@@ -7155,6 +7184,11 @@
       <c r="P55" s="0" t="n">
         <v>100001</v>
       </c>
+      <c r="Q55" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
+        </is>
+      </c>
       <c r="S55" s="0" t="n">
         <v>1</v>
       </c>
@@ -7244,6 +7278,11 @@
       <c r="P56" s="0" t="n">
         <v>101006</v>
       </c>
+      <c r="Q56" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
+        </is>
+      </c>
       <c r="S56" s="0" t="n">
         <v>1</v>
       </c>
@@ -7317,7 +7356,7 @@
       <c r="C57" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="0" t="inlineStr">
         <is>
           <t>2000600001,</t>
         </is>
@@ -7345,6 +7384,11 @@
       </c>
       <c r="P57" s="0" t="n">
         <v>100001</v>
+      </c>
+      <c r="Q57" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
+        </is>
       </c>
       <c r="S57" s="0" t="n">
         <v>1</v>
@@ -7448,7 +7492,11 @@
       <c r="P58" s="5" t="n">
         <v>100001</v>
       </c>
-      <c r="Q58" s="5" t="n"/>
+      <c r="Q58" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
+        </is>
+      </c>
       <c r="R58" s="5" t="n"/>
       <c r="S58" s="5" t="n">
         <v>2</v>
@@ -11480,7 +11528,7 @@
     <row r="180" ht="12" customHeight="1" s="3"/>
     <row r="181" ht="12" customHeight="1" s="3"/>
   </sheetData>
-  <autoFilter ref="A1:AN111"/>
+  <autoFilter ref="A1:AN116"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -6892,7 +6892,7 @@
       </c>
       <c r="O52" s="4" t="n"/>
       <c r="P52" s="4" t="n">
-        <v>700003</v>
+        <v>200004</v>
       </c>
       <c r="Q52" s="4" t="inlineStr">
         <is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -1080,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT116"/>
+  <dimension ref="A1:AT118"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="7.375" customWidth="1" style="3" min="1" max="1"/>
@@ -7060,99 +7060,94 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="0" t="n">
-        <v>104001</v>
-      </c>
-      <c r="B54" s="0" t="inlineStr">
-        <is>
-          <t>人类-盗贼</t>
-        </is>
-      </c>
-      <c r="C54" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F54" s="0" t="inlineStr">
-        <is>
-          <t>2000100001,</t>
-        </is>
-      </c>
-      <c r="G54" s="0" t="n">
+      <c r="A54" t="n">
+        <v>103105</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>骷髅召唤师</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" t="n">
         <v>1000001</v>
       </c>
-      <c r="I54" s="0" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J54" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N54" s="0" t="inlineStr">
-        <is>
-          <t>Attack6</t>
-        </is>
-      </c>
-      <c r="P54" s="0" t="n">
-        <v>100002</v>
-      </c>
-      <c r="Q54" s="0" t="inlineStr">
-        <is>
-          <t>0,0.5,0</t>
-        </is>
-      </c>
-      <c r="S54" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="T54" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U54" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V54" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X54" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y54" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB54" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE54" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF54" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ54" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK54" s="0" t="n">
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Attack2</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>200002</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>0,0.6,0</t>
+        </is>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>10</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK54" t="n">
         <v>1000001</v>
       </c>
-      <c r="AL54" s="0" t="inlineStr">
-        <is>
-          <t>ui_class_3</t>
-        </is>
-      </c>
-      <c r="AM54" s="0" t="inlineStr">
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>ui_class_2</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
         <is>
           <t>Card_Scene_2</t>
         </is>
       </c>
-      <c r="AR54" s="0" t="n">
-        <v>104001</v>
-      </c>
-      <c r="AT54" s="0" t="inlineStr">
+      <c r="AR54" t="n">
+        <v>103105</v>
+      </c>
+      <c r="AT54" t="inlineStr">
         <is>
           <t>1,3,4,6</t>
         </is>
@@ -7160,15 +7155,20 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>104002</v>
+        <v>104001</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>人类-双持战士</t>
+          <t>人类-盗贼</t>
         </is>
       </c>
       <c r="C55" s="0" t="n">
         <v>2</v>
+      </c>
+      <c r="F55" s="0" t="inlineStr">
+        <is>
+          <t>2000100001,</t>
+        </is>
       </c>
       <c r="G55" s="0" t="n">
         <v>1000001</v>
@@ -7179,10 +7179,15 @@
         </is>
       </c>
       <c r="J55" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="N55" s="0" t="inlineStr">
+        <is>
+          <t>Attack6</t>
+        </is>
       </c>
       <c r="P55" s="0" t="n">
-        <v>100001</v>
+        <v>100002</v>
       </c>
       <c r="Q55" s="0" t="inlineStr">
         <is>
@@ -7220,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="AG55" s="0" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AJ55" s="0" t="n">
         <v>1</v>
@@ -7239,7 +7244,7 @@
         </is>
       </c>
       <c r="AR55" s="0" t="n">
-        <v>104002</v>
+        <v>104001</v>
       </c>
       <c r="AT55" s="0" t="inlineStr">
         <is>
@@ -7249,11 +7254,11 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>104101</v>
+        <v>104002</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>人类-大剑战士</t>
+          <t>人类-双持战士</t>
         </is>
       </c>
       <c r="C56" s="0" t="n">
@@ -7268,15 +7273,10 @@
         </is>
       </c>
       <c r="J56" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N56" s="0" t="inlineStr">
-        <is>
-          <t>Attack8</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="P56" s="0" t="n">
-        <v>101006</v>
+        <v>100001</v>
       </c>
       <c r="Q56" s="0" t="inlineStr">
         <is>
@@ -7307,9 +7307,6 @@
       <c r="AB56" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="AD56" s="0" t="n">
-        <v>100</v>
-      </c>
       <c r="AE56" s="0" t="n">
         <v>10</v>
       </c>
@@ -7327,7 +7324,7 @@
       </c>
       <c r="AL56" s="0" t="inlineStr">
         <is>
-          <t>ui_class_7</t>
+          <t>ui_class_3</t>
         </is>
       </c>
       <c r="AM56" s="0" t="inlineStr">
@@ -7336,7 +7333,7 @@
         </is>
       </c>
       <c r="AR56" s="0" t="n">
-        <v>104101</v>
+        <v>104002</v>
       </c>
       <c r="AT56" s="0" t="inlineStr">
         <is>
@@ -7346,20 +7343,15 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>104102</v>
+        <v>104101</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>人类-大盾战士</t>
+          <t>人类-大剑战士</t>
         </is>
       </c>
       <c r="C57" s="0" t="n">
         <v>2</v>
-      </c>
-      <c r="F57" s="0" t="inlineStr">
-        <is>
-          <t>2000600001,</t>
-        </is>
       </c>
       <c r="G57" s="0" t="n">
         <v>1000001</v>
@@ -7370,20 +7362,15 @@
         </is>
       </c>
       <c r="J57" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="M57" s="0" t="inlineStr">
-        <is>
-          <t>Walk4</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="N57" s="0" t="inlineStr">
         <is>
-          <t>Attack7</t>
+          <t>Attack8</t>
         </is>
       </c>
       <c r="P57" s="0" t="n">
-        <v>100001</v>
+        <v>101006</v>
       </c>
       <c r="Q57" s="0" t="inlineStr">
         <is>
@@ -7443,7 +7430,7 @@
         </is>
       </c>
       <c r="AR57" s="0" t="n">
-        <v>104102</v>
+        <v>104101</v>
       </c>
       <c r="AT57" s="0" t="inlineStr">
         <is>
@@ -7452,44 +7439,44 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
-        <v>900001</v>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>测试骷髅战士</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="n"/>
-      <c r="G58" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="H58" s="5" t="n">
-        <v>21010001</v>
-      </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="A58" s="0" t="n">
+        <v>104102</v>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>人类-大盾战士</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" s="0" t="inlineStr">
+        <is>
+          <t>2000600001,</t>
+        </is>
+      </c>
+      <c r="G58" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="I58" s="0" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J58" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K58" s="5" t="n"/>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="inlineStr">
-        <is>
-          <t>Attack2</t>
-        </is>
-      </c>
-      <c r="O58" s="5" t="n"/>
-      <c r="P58" s="5" t="n">
+      <c r="J58" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="M58" s="0" t="inlineStr">
+        <is>
+          <t>Walk4</t>
+        </is>
+      </c>
+      <c r="N58" s="0" t="inlineStr">
+        <is>
+          <t>Attack7</t>
+        </is>
+      </c>
+      <c r="P58" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="Q58" s="0" t="inlineStr">
@@ -7497,71 +7484,60 @@
           <t>0,0.5,0</t>
         </is>
       </c>
-      <c r="R58" s="5" t="n"/>
-      <c r="S58" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T58" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U58" s="5" t="n">
+      <c r="S58" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U58" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V58" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W58" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X58" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y58" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z58" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA58" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB58" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AC58" s="5" t="n"/>
-      <c r="AD58" s="5" t="n"/>
-      <c r="AE58" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG58" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH58" s="5" t="n"/>
-      <c r="AI58" s="5" t="n"/>
-      <c r="AJ58" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK58" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="AL58" s="5" t="inlineStr">
-        <is>
-          <t>ui_class_3</t>
-        </is>
-      </c>
-      <c r="AM58" s="5" t="inlineStr">
-        <is>
-          <t>Card_Scene_1</t>
-        </is>
-      </c>
-      <c r="AN58" s="5" t="n">
-        <v>300200001</v>
-      </c>
-      <c r="AR58" s="5" t="n">
-        <v>900001</v>
+      <c r="W58" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X58" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y58" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB58" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD58" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE58" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ58" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK58" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="AL58" s="0" t="inlineStr">
+        <is>
+          <t>ui_class_7</t>
+        </is>
+      </c>
+      <c r="AM58" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_2</t>
+        </is>
+      </c>
+      <c r="AR58" s="0" t="n">
+        <v>104102</v>
       </c>
       <c r="AT58" s="0" t="inlineStr">
         <is>
@@ -7570,116 +7546,95 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
-        <v>900002</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>测试骷髅投手</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="n"/>
-      <c r="G59" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>21000001</v>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="A59" s="0" t="n">
+        <v>104103</v>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>人类-长枪骑士</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="I59" s="0" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J59" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K59" s="5" t="n"/>
-      <c r="L59" s="5" t="n"/>
-      <c r="M59" s="5" t="n"/>
-      <c r="N59" s="5" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="O59" s="5" t="n"/>
-      <c r="P59" s="5" t="n">
-        <v>200001</v>
-      </c>
-      <c r="Q59" s="5" t="inlineStr">
-        <is>
-          <t>0,0.7,0</t>
-        </is>
-      </c>
-      <c r="R59" s="5" t="n"/>
-      <c r="S59" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T59" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="U59" s="5" t="n">
+      <c r="J59" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N59" s="0" t="inlineStr">
+        <is>
+          <t>Attack8</t>
+        </is>
+      </c>
+      <c r="P59" s="0" t="n">
+        <v>101006</v>
+      </c>
+      <c r="Q59" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
+        </is>
+      </c>
+      <c r="S59" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U59" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V59" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X59" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y59" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z59" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA59" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB59" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AC59" s="5" t="n"/>
-      <c r="AD59" s="5" t="n"/>
-      <c r="AE59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH59" s="5" t="n"/>
-      <c r="AI59" s="5" t="n"/>
-      <c r="AJ59" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK59" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="AL59" s="5" t="inlineStr">
-        <is>
-          <t>ui_class_6</t>
-        </is>
-      </c>
-      <c r="AM59" s="5" t="inlineStr">
-        <is>
-          <t>Card_Scene_1</t>
-        </is>
-      </c>
-      <c r="AN59" s="5" t="n">
-        <v>300200002</v>
-      </c>
-      <c r="AR59" s="5" t="n">
-        <v>900002</v>
+      <c r="W59" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X59" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y59" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB59" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD59" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE59" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ59" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK59" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="AL59" s="0" t="inlineStr">
+        <is>
+          <t>ui_class_7</t>
+        </is>
+      </c>
+      <c r="AM59" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_2</t>
+        </is>
+      </c>
+      <c r="AR59" s="0" t="n">
+        <v>104103</v>
       </c>
       <c r="AT59" s="0" t="inlineStr">
         <is>
@@ -7688,47 +7643,86 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="0" t="n">
-        <v>989996</v>
-      </c>
-      <c r="B60" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C60" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P60" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S60" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T60" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U60" s="0" t="n">
+      <c r="A60" s="5" t="n">
+        <v>900001</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>测试骷髅战士</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>21010001</v>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>1,2,3,10,</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>Attack2</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="5" t="n">
+        <v>100001</v>
+      </c>
+      <c r="Q60" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
+        </is>
+      </c>
+      <c r="R60" s="5" t="n"/>
+      <c r="S60" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T60" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U60" s="5" t="n">
         <v>1</v>
       </c>
       <c r="V60" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W60" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X60" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y60" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z60" s="0" t="n"/>
-      <c r="AB60" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE60" s="0" t="n">
-        <v>35</v>
+      <c r="W60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X60" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y60" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA60" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB60" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AC60" s="5" t="n"/>
+      <c r="AD60" s="5" t="n"/>
+      <c r="AE60" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AF60" s="1" t="n">
         <v>0</v>
@@ -7736,18 +7730,29 @@
       <c r="AG60" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AJ60" s="0" t="n">
-        <v>989996</v>
-      </c>
-      <c r="AK60" s="0" t="n"/>
-      <c r="AL60" s="0" t="n"/>
-      <c r="AM60" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR60" s="0" t="n">
-        <v>1</v>
+      <c r="AH60" s="5" t="n"/>
+      <c r="AI60" s="5" t="n"/>
+      <c r="AJ60" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK60" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="AL60" s="5" t="inlineStr">
+        <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="AM60" s="5" t="inlineStr">
+        <is>
+          <t>Card_Scene_1</t>
+        </is>
+      </c>
+      <c r="AN60" s="5" t="n">
+        <v>300200001</v>
+      </c>
+      <c r="AR60" s="5" t="n">
+        <v>900001</v>
       </c>
       <c r="AT60" s="0" t="inlineStr">
         <is>
@@ -7756,47 +7761,86 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="0" t="n">
-        <v>989997</v>
-      </c>
-      <c r="B61" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C61" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P61" s="0" t="n">
+      <c r="A61" s="5" t="n">
+        <v>900002</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>测试骷髅投手</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>21000001</v>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>1,2,3,10,</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="n">
         <v>200001</v>
       </c>
-      <c r="S61" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T61" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U61" s="0" t="n">
+      <c r="Q61" s="5" t="inlineStr">
+        <is>
+          <t>0,0.7,0</t>
+        </is>
+      </c>
+      <c r="R61" s="5" t="n"/>
+      <c r="S61" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T61" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="U61" s="5" t="n">
         <v>1</v>
       </c>
       <c r="V61" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W61" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X61" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y61" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z61" s="0" t="n"/>
-      <c r="AB61" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE61" s="0" t="n">
-        <v>35</v>
+      <c r="W61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X61" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y61" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z61" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA61" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB61" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AC61" s="5" t="n"/>
+      <c r="AD61" s="5" t="n"/>
+      <c r="AE61" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AF61" s="1" t="n">
         <v>0</v>
@@ -7804,18 +7848,29 @@
       <c r="AG61" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AJ61" s="0" t="n">
-        <v>989997</v>
-      </c>
-      <c r="AK61" s="0" t="n"/>
-      <c r="AL61" s="0" t="n"/>
-      <c r="AM61" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR61" s="0" t="n">
-        <v>1</v>
+      <c r="AH61" s="5" t="n"/>
+      <c r="AI61" s="5" t="n"/>
+      <c r="AJ61" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK61" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="AL61" s="5" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="AM61" s="5" t="inlineStr">
+        <is>
+          <t>Card_Scene_1</t>
+        </is>
+      </c>
+      <c r="AN61" s="5" t="n">
+        <v>300200002</v>
+      </c>
+      <c r="AR61" s="5" t="n">
+        <v>900002</v>
       </c>
       <c r="AT61" s="0" t="inlineStr">
         <is>
@@ -7825,7 +7880,7 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>989998</v>
+        <v>989996</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
@@ -7873,7 +7928,7 @@
         <v>10</v>
       </c>
       <c r="AJ62" s="0" t="n">
-        <v>989998</v>
+        <v>989996</v>
       </c>
       <c r="AK62" s="0" t="n"/>
       <c r="AL62" s="0" t="n"/>
@@ -7893,7 +7948,7 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>989999</v>
+        <v>989997</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
@@ -7941,8 +7996,10 @@
         <v>10</v>
       </c>
       <c r="AJ63" s="0" t="n">
-        <v>989999</v>
-      </c>
+        <v>989997</v>
+      </c>
+      <c r="AK63" s="0" t="n"/>
+      <c r="AL63" s="0" t="n"/>
       <c r="AM63" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -7959,7 +8016,7 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>999947</v>
+        <v>989998</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
@@ -8007,7 +8064,7 @@
         <v>10</v>
       </c>
       <c r="AJ64" s="0" t="n">
-        <v>999947</v>
+        <v>989998</v>
       </c>
       <c r="AK64" s="0" t="n"/>
       <c r="AL64" s="0" t="n"/>
@@ -8027,7 +8084,7 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>999948</v>
+        <v>989999</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
@@ -8075,10 +8132,8 @@
         <v>10</v>
       </c>
       <c r="AJ65" s="0" t="n">
-        <v>999948</v>
-      </c>
-      <c r="AK65" s="0" t="n"/>
-      <c r="AL65" s="0" t="n"/>
+        <v>989999</v>
+      </c>
       <c r="AM65" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -8095,7 +8150,7 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>999949</v>
+        <v>999947</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
@@ -8143,7 +8198,7 @@
         <v>10</v>
       </c>
       <c r="AJ66" s="0" t="n">
-        <v>999949</v>
+        <v>999947</v>
       </c>
       <c r="AK66" s="0" t="n"/>
       <c r="AL66" s="0" t="n"/>
@@ -8163,7 +8218,7 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>999950</v>
+        <v>999948</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
@@ -8211,7 +8266,7 @@
         <v>10</v>
       </c>
       <c r="AJ67" s="0" t="n">
-        <v>999950</v>
+        <v>999948</v>
       </c>
       <c r="AK67" s="0" t="n"/>
       <c r="AL67" s="0" t="n"/>
@@ -8231,7 +8286,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>999951</v>
+        <v>999949</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
@@ -8279,7 +8334,7 @@
         <v>10</v>
       </c>
       <c r="AJ68" s="0" t="n">
-        <v>999951</v>
+        <v>999949</v>
       </c>
       <c r="AK68" s="0" t="n"/>
       <c r="AL68" s="0" t="n"/>
@@ -8299,7 +8354,7 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>999952</v>
+        <v>999950</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
@@ -8347,7 +8402,7 @@
         <v>10</v>
       </c>
       <c r="AJ69" s="0" t="n">
-        <v>999952</v>
+        <v>999950</v>
       </c>
       <c r="AK69" s="0" t="n"/>
       <c r="AL69" s="0" t="n"/>
@@ -8367,7 +8422,7 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>999953</v>
+        <v>999951</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
@@ -8415,7 +8470,7 @@
         <v>10</v>
       </c>
       <c r="AJ70" s="0" t="n">
-        <v>999953</v>
+        <v>999951</v>
       </c>
       <c r="AK70" s="0" t="n"/>
       <c r="AL70" s="0" t="n"/>
@@ -8435,7 +8490,7 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>999954</v>
+        <v>999952</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
@@ -8483,7 +8538,7 @@
         <v>10</v>
       </c>
       <c r="AJ71" s="0" t="n">
-        <v>999954</v>
+        <v>999952</v>
       </c>
       <c r="AK71" s="0" t="n"/>
       <c r="AL71" s="0" t="n"/>
@@ -8503,7 +8558,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>999955</v>
+        <v>999953</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
@@ -8551,7 +8606,7 @@
         <v>10</v>
       </c>
       <c r="AJ72" s="0" t="n">
-        <v>999955</v>
+        <v>999953</v>
       </c>
       <c r="AK72" s="0" t="n"/>
       <c r="AL72" s="0" t="n"/>
@@ -8571,7 +8626,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>999956</v>
+        <v>999954</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
@@ -8619,7 +8674,7 @@
         <v>10</v>
       </c>
       <c r="AJ73" s="0" t="n">
-        <v>999956</v>
+        <v>999954</v>
       </c>
       <c r="AK73" s="0" t="n"/>
       <c r="AL73" s="0" t="n"/>
@@ -8639,7 +8694,7 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>999957</v>
+        <v>999955</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
@@ -8687,7 +8742,7 @@
         <v>10</v>
       </c>
       <c r="AJ74" s="0" t="n">
-        <v>999957</v>
+        <v>999955</v>
       </c>
       <c r="AK74" s="0" t="n"/>
       <c r="AL74" s="0" t="n"/>
@@ -8707,7 +8762,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>999958</v>
+        <v>999956</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
@@ -8755,7 +8810,7 @@
         <v>10</v>
       </c>
       <c r="AJ75" s="0" t="n">
-        <v>999958</v>
+        <v>999956</v>
       </c>
       <c r="AK75" s="0" t="n"/>
       <c r="AL75" s="0" t="n"/>
@@ -8775,7 +8830,7 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>999959</v>
+        <v>999957</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
@@ -8823,7 +8878,7 @@
         <v>10</v>
       </c>
       <c r="AJ76" s="0" t="n">
-        <v>999959</v>
+        <v>999957</v>
       </c>
       <c r="AK76" s="0" t="n"/>
       <c r="AL76" s="0" t="n"/>
@@ -8843,7 +8898,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>999960</v>
+        <v>999958</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
@@ -8891,7 +8946,7 @@
         <v>10</v>
       </c>
       <c r="AJ77" s="0" t="n">
-        <v>999960</v>
+        <v>999958</v>
       </c>
       <c r="AK77" s="0" t="n"/>
       <c r="AL77" s="0" t="n"/>
@@ -8911,7 +8966,7 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>999961</v>
+        <v>999959</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
@@ -8959,7 +9014,7 @@
         <v>10</v>
       </c>
       <c r="AJ78" s="0" t="n">
-        <v>999961</v>
+        <v>999959</v>
       </c>
       <c r="AK78" s="0" t="n"/>
       <c r="AL78" s="0" t="n"/>
@@ -8979,7 +9034,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>999962</v>
+        <v>999960</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
@@ -9027,7 +9082,7 @@
         <v>10</v>
       </c>
       <c r="AJ79" s="0" t="n">
-        <v>999962</v>
+        <v>999960</v>
       </c>
       <c r="AK79" s="0" t="n"/>
       <c r="AL79" s="0" t="n"/>
@@ -9047,7 +9102,7 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>999963</v>
+        <v>999961</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
@@ -9095,7 +9150,7 @@
         <v>10</v>
       </c>
       <c r="AJ80" s="0" t="n">
-        <v>999963</v>
+        <v>999961</v>
       </c>
       <c r="AK80" s="0" t="n"/>
       <c r="AL80" s="0" t="n"/>
@@ -9115,7 +9170,7 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>999964</v>
+        <v>999962</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
@@ -9163,7 +9218,7 @@
         <v>10</v>
       </c>
       <c r="AJ81" s="0" t="n">
-        <v>999964</v>
+        <v>999962</v>
       </c>
       <c r="AK81" s="0" t="n"/>
       <c r="AL81" s="0" t="n"/>
@@ -9183,7 +9238,7 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>999965</v>
+        <v>999963</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
@@ -9231,7 +9286,7 @@
         <v>10</v>
       </c>
       <c r="AJ82" s="0" t="n">
-        <v>999965</v>
+        <v>999963</v>
       </c>
       <c r="AK82" s="0" t="n"/>
       <c r="AL82" s="0" t="n"/>
@@ -9251,7 +9306,7 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>999966</v>
+        <v>999964</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
@@ -9299,7 +9354,7 @@
         <v>10</v>
       </c>
       <c r="AJ83" s="0" t="n">
-        <v>999966</v>
+        <v>999964</v>
       </c>
       <c r="AK83" s="0" t="n"/>
       <c r="AL83" s="0" t="n"/>
@@ -9319,7 +9374,7 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>999967</v>
+        <v>999965</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
@@ -9367,7 +9422,7 @@
         <v>10</v>
       </c>
       <c r="AJ84" s="0" t="n">
-        <v>999967</v>
+        <v>999965</v>
       </c>
       <c r="AK84" s="0" t="n"/>
       <c r="AL84" s="0" t="n"/>
@@ -9387,7 +9442,7 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>999968</v>
+        <v>999966</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
@@ -9435,7 +9490,7 @@
         <v>10</v>
       </c>
       <c r="AJ85" s="0" t="n">
-        <v>999968</v>
+        <v>999966</v>
       </c>
       <c r="AK85" s="0" t="n"/>
       <c r="AL85" s="0" t="n"/>
@@ -9455,7 +9510,7 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>999969</v>
+        <v>999967</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
@@ -9503,7 +9558,7 @@
         <v>10</v>
       </c>
       <c r="AJ86" s="0" t="n">
-        <v>999969</v>
+        <v>999967</v>
       </c>
       <c r="AK86" s="0" t="n"/>
       <c r="AL86" s="0" t="n"/>
@@ -9523,7 +9578,7 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>999970</v>
+        <v>999968</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
@@ -9571,7 +9626,7 @@
         <v>10</v>
       </c>
       <c r="AJ87" s="0" t="n">
-        <v>999970</v>
+        <v>999968</v>
       </c>
       <c r="AK87" s="0" t="n"/>
       <c r="AL87" s="0" t="n"/>
@@ -9591,7 +9646,7 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>999971</v>
+        <v>999969</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
@@ -9639,7 +9694,7 @@
         <v>10</v>
       </c>
       <c r="AJ88" s="0" t="n">
-        <v>999971</v>
+        <v>999969</v>
       </c>
       <c r="AK88" s="0" t="n"/>
       <c r="AL88" s="0" t="n"/>
@@ -9659,7 +9714,7 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>999972</v>
+        <v>999970</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
@@ -9707,7 +9762,7 @@
         <v>10</v>
       </c>
       <c r="AJ89" s="0" t="n">
-        <v>999972</v>
+        <v>999970</v>
       </c>
       <c r="AK89" s="0" t="n"/>
       <c r="AL89" s="0" t="n"/>
@@ -9727,7 +9782,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>999973</v>
+        <v>999971</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
@@ -9775,7 +9830,7 @@
         <v>10</v>
       </c>
       <c r="AJ90" s="0" t="n">
-        <v>999973</v>
+        <v>999971</v>
       </c>
       <c r="AK90" s="0" t="n"/>
       <c r="AL90" s="0" t="n"/>
@@ -9795,7 +9850,7 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>999974</v>
+        <v>999972</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
@@ -9843,7 +9898,7 @@
         <v>10</v>
       </c>
       <c r="AJ91" s="0" t="n">
-        <v>999974</v>
+        <v>999972</v>
       </c>
       <c r="AK91" s="0" t="n"/>
       <c r="AL91" s="0" t="n"/>
@@ -9863,7 +9918,7 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>999975</v>
+        <v>999973</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
@@ -9911,7 +9966,7 @@
         <v>10</v>
       </c>
       <c r="AJ92" s="0" t="n">
-        <v>999975</v>
+        <v>999973</v>
       </c>
       <c r="AK92" s="0" t="n"/>
       <c r="AL92" s="0" t="n"/>
@@ -9931,7 +9986,7 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>999976</v>
+        <v>999974</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
@@ -9979,7 +10034,7 @@
         <v>10</v>
       </c>
       <c r="AJ93" s="0" t="n">
-        <v>999976</v>
+        <v>999974</v>
       </c>
       <c r="AK93" s="0" t="n"/>
       <c r="AL93" s="0" t="n"/>
@@ -9999,7 +10054,7 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>999977</v>
+        <v>999975</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
@@ -10047,7 +10102,7 @@
         <v>10</v>
       </c>
       <c r="AJ94" s="0" t="n">
-        <v>999977</v>
+        <v>999975</v>
       </c>
       <c r="AK94" s="0" t="n"/>
       <c r="AL94" s="0" t="n"/>
@@ -10067,7 +10122,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>999978</v>
+        <v>999976</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
@@ -10115,7 +10170,7 @@
         <v>10</v>
       </c>
       <c r="AJ95" s="0" t="n">
-        <v>999978</v>
+        <v>999976</v>
       </c>
       <c r="AK95" s="0" t="n"/>
       <c r="AL95" s="0" t="n"/>
@@ -10135,7 +10190,7 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>999979</v>
+        <v>999977</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
@@ -10183,7 +10238,7 @@
         <v>10</v>
       </c>
       <c r="AJ96" s="0" t="n">
-        <v>999979</v>
+        <v>999977</v>
       </c>
       <c r="AK96" s="0" t="n"/>
       <c r="AL96" s="0" t="n"/>
@@ -10203,7 +10258,7 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>999980</v>
+        <v>999978</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
@@ -10251,7 +10306,7 @@
         <v>10</v>
       </c>
       <c r="AJ97" s="0" t="n">
-        <v>999980</v>
+        <v>999978</v>
       </c>
       <c r="AK97" s="0" t="n"/>
       <c r="AL97" s="0" t="n"/>
@@ -10271,7 +10326,7 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>999981</v>
+        <v>999979</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
@@ -10319,7 +10374,7 @@
         <v>10</v>
       </c>
       <c r="AJ98" s="0" t="n">
-        <v>999981</v>
+        <v>999979</v>
       </c>
       <c r="AK98" s="0" t="n"/>
       <c r="AL98" s="0" t="n"/>
@@ -10339,7 +10394,7 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>999982</v>
+        <v>999980</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
@@ -10373,6 +10428,7 @@
       <c r="Y99" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="Z99" s="0" t="n"/>
       <c r="AB99" s="0" t="n">
         <v>100</v>
       </c>
@@ -10386,8 +10442,10 @@
         <v>10</v>
       </c>
       <c r="AJ99" s="0" t="n">
-        <v>999982</v>
-      </c>
+        <v>999980</v>
+      </c>
+      <c r="AK99" s="0" t="n"/>
+      <c r="AL99" s="0" t="n"/>
       <c r="AM99" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -10404,7 +10462,7 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>999983</v>
+        <v>999981</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
@@ -10438,6 +10496,7 @@
       <c r="Y100" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="Z100" s="0" t="n"/>
       <c r="AB100" s="0" t="n">
         <v>100</v>
       </c>
@@ -10451,8 +10510,10 @@
         <v>10</v>
       </c>
       <c r="AJ100" s="0" t="n">
-        <v>999983</v>
-      </c>
+        <v>999981</v>
+      </c>
+      <c r="AK100" s="0" t="n"/>
+      <c r="AL100" s="0" t="n"/>
       <c r="AM100" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -10469,7 +10530,7 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>999984</v>
+        <v>999982</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
@@ -10516,7 +10577,7 @@
         <v>10</v>
       </c>
       <c r="AJ101" s="0" t="n">
-        <v>999984</v>
+        <v>999982</v>
       </c>
       <c r="AM101" s="0" t="inlineStr">
         <is>
@@ -10534,7 +10595,7 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>999985</v>
+        <v>999983</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
@@ -10581,7 +10642,7 @@
         <v>10</v>
       </c>
       <c r="AJ102" s="0" t="n">
-        <v>999985</v>
+        <v>999983</v>
       </c>
       <c r="AM102" s="0" t="inlineStr">
         <is>
@@ -10599,7 +10660,7 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>999986</v>
+        <v>999984</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
@@ -10646,7 +10707,7 @@
         <v>10</v>
       </c>
       <c r="AJ103" s="0" t="n">
-        <v>999986</v>
+        <v>999984</v>
       </c>
       <c r="AM103" s="0" t="inlineStr">
         <is>
@@ -10664,7 +10725,7 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>999987</v>
+        <v>999985</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
@@ -10711,7 +10772,7 @@
         <v>10</v>
       </c>
       <c r="AJ104" s="0" t="n">
-        <v>999987</v>
+        <v>999985</v>
       </c>
       <c r="AM104" s="0" t="inlineStr">
         <is>
@@ -10729,7 +10790,7 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>999988</v>
+        <v>999986</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
@@ -10776,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="AJ105" s="0" t="n">
-        <v>999988</v>
+        <v>999986</v>
       </c>
       <c r="AM105" s="0" t="inlineStr">
         <is>
@@ -10794,7 +10855,7 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>999989</v>
+        <v>999987</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
@@ -10841,7 +10902,7 @@
         <v>10</v>
       </c>
       <c r="AJ106" s="0" t="n">
-        <v>999989</v>
+        <v>999987</v>
       </c>
       <c r="AM106" s="0" t="inlineStr">
         <is>
@@ -10859,7 +10920,7 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>999990</v>
+        <v>999988</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
@@ -10906,7 +10967,7 @@
         <v>10</v>
       </c>
       <c r="AJ107" s="0" t="n">
-        <v>999990</v>
+        <v>999988</v>
       </c>
       <c r="AM107" s="0" t="inlineStr">
         <is>
@@ -10924,7 +10985,7 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>999991</v>
+        <v>999989</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
@@ -10971,7 +11032,7 @@
         <v>10</v>
       </c>
       <c r="AJ108" s="0" t="n">
-        <v>999991</v>
+        <v>999989</v>
       </c>
       <c r="AM108" s="0" t="inlineStr">
         <is>
@@ -10989,7 +11050,7 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>999992</v>
+        <v>999990</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
@@ -11036,7 +11097,7 @@
         <v>10</v>
       </c>
       <c r="AJ109" s="0" t="n">
-        <v>999992</v>
+        <v>999990</v>
       </c>
       <c r="AM109" s="0" t="inlineStr">
         <is>
@@ -11054,7 +11115,7 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>999993</v>
+        <v>999991</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
@@ -11101,7 +11162,7 @@
         <v>10</v>
       </c>
       <c r="AJ110" s="0" t="n">
-        <v>999993</v>
+        <v>999991</v>
       </c>
       <c r="AM110" s="0" t="inlineStr">
         <is>
@@ -11119,7 +11180,7 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>999994</v>
+        <v>999992</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
@@ -11166,7 +11227,7 @@
         <v>10</v>
       </c>
       <c r="AJ111" s="0" t="n">
-        <v>999994</v>
+        <v>999992</v>
       </c>
       <c r="AM111" s="0" t="inlineStr">
         <is>
@@ -11184,7 +11245,7 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>999995</v>
+        <v>999993</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
@@ -11231,7 +11292,7 @@
         <v>10</v>
       </c>
       <c r="AJ112" s="0" t="n">
-        <v>999995</v>
+        <v>999993</v>
       </c>
       <c r="AM112" s="0" t="inlineStr">
         <is>
@@ -11249,7 +11310,7 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>999996</v>
+        <v>999994</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
@@ -11296,7 +11357,7 @@
         <v>10</v>
       </c>
       <c r="AJ113" s="0" t="n">
-        <v>999996</v>
+        <v>999994</v>
       </c>
       <c r="AM113" s="0" t="inlineStr">
         <is>
@@ -11314,7 +11375,7 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>999997</v>
+        <v>999995</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
@@ -11361,7 +11422,7 @@
         <v>10</v>
       </c>
       <c r="AJ114" s="0" t="n">
-        <v>999997</v>
+        <v>999995</v>
       </c>
       <c r="AM114" s="0" t="inlineStr">
         <is>
@@ -11379,7 +11440,7 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>999998</v>
+        <v>999996</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
@@ -11426,7 +11487,7 @@
         <v>10</v>
       </c>
       <c r="AJ115" s="0" t="n">
-        <v>999998</v>
+        <v>999996</v>
       </c>
       <c r="AM115" s="0" t="inlineStr">
         <is>
@@ -11444,7 +11505,7 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>999999</v>
+        <v>999997</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
@@ -11491,17 +11552,147 @@
         <v>10</v>
       </c>
       <c r="AJ116" s="0" t="n">
+        <v>999997</v>
+      </c>
+      <c r="AM116" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_4</t>
+        </is>
+      </c>
+      <c r="AR116" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT116" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="n">
+        <v>999998</v>
+      </c>
+      <c r="B117" s="0" t="inlineStr">
+        <is>
+          <t>测试数据</t>
+        </is>
+      </c>
+      <c r="C117" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P117" s="0" t="n">
+        <v>200001</v>
+      </c>
+      <c r="S117" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="T117" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="U117" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V117" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X117" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y117" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB117" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE117" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF117" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG117" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ117" s="0" t="n">
+        <v>999998</v>
+      </c>
+      <c r="AM117" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_4</t>
+        </is>
+      </c>
+      <c r="AR117" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT117" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="n">
         <v>999999</v>
       </c>
-      <c r="AM116" s="0" t="inlineStr">
+      <c r="B118" s="0" t="inlineStr">
+        <is>
+          <t>测试数据</t>
+        </is>
+      </c>
+      <c r="C118" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P118" s="0" t="n">
+        <v>200001</v>
+      </c>
+      <c r="S118" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="T118" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="U118" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V118" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X118" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y118" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB118" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE118" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF118" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG118" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ118" s="0" t="n">
+        <v>999999</v>
+      </c>
+      <c r="AM118" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AR116" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT116" s="0" t="inlineStr">
+      <c r="AR118" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT118" s="0" t="inlineStr">
         <is>
           <t>1,3,4,6</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -1080,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT118"/>
+  <dimension ref="A1:AT120"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="7.375" customWidth="1" style="3" min="1" max="1"/>
@@ -7060,94 +7060,94 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
+      <c r="A54" s="0" t="n">
         <v>103105</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>骷髅召唤师</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>2</v>
-      </c>
-      <c r="G54" t="n">
+      <c r="C54" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" s="0" t="n">
         <v>1000001</v>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" s="0" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J54" t="n">
-        <v>1</v>
-      </c>
-      <c r="N54" t="inlineStr">
+      <c r="J54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" s="0" t="inlineStr">
         <is>
           <t>Attack2</t>
         </is>
       </c>
-      <c r="P54" t="n">
-        <v>200002</v>
-      </c>
-      <c r="Q54" t="inlineStr">
+      <c r="P54" s="0" t="n">
+        <v>500004</v>
+      </c>
+      <c r="Q54" s="0" t="inlineStr">
         <is>
           <t>0,0.6,0</t>
         </is>
       </c>
-      <c r="S54" t="n">
-        <v>1</v>
-      </c>
-      <c r="T54" t="n">
-        <v>10</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB54" t="n">
+      <c r="S54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="U54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="0" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X54" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y54" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB54" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="AE54" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK54" t="n">
+      <c r="AE54" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK54" s="0" t="n">
         <v>1000001</v>
       </c>
-      <c r="AL54" t="inlineStr">
+      <c r="AL54" s="0" t="inlineStr">
         <is>
           <t>ui_class_2</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
+      <c r="AM54" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_2</t>
         </is>
       </c>
-      <c r="AR54" t="n">
+      <c r="AR54" s="0" t="n">
         <v>103105</v>
       </c>
-      <c r="AT54" t="inlineStr">
+      <c r="AT54" s="0" t="inlineStr">
         <is>
           <t>1,3,4,6</t>
         </is>
@@ -7155,23 +7155,21 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>104001</v>
+        <v>103106</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>人类-盗贼</t>
+          <t>骷髅战士（召唤物，克隆2001改索敌防守方）</t>
         </is>
       </c>
       <c r="C55" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F55" s="0" t="inlineStr">
-        <is>
-          <t>2000100001,</t>
-        </is>
-      </c>
       <c r="G55" s="0" t="n">
-        <v>1000001</v>
+        <v>2000001</v>
+      </c>
+      <c r="H55" s="0" t="n">
+        <v>21010001</v>
       </c>
       <c r="I55" s="0" t="inlineStr">
         <is>
@@ -7179,15 +7177,15 @@
         </is>
       </c>
       <c r="J55" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N55" s="0" t="inlineStr">
         <is>
-          <t>Attack6</t>
+          <t>Attack2</t>
         </is>
       </c>
       <c r="P55" s="0" t="n">
-        <v>100002</v>
+        <v>100001</v>
       </c>
       <c r="Q55" s="0" t="inlineStr">
         <is>
@@ -7198,7 +7196,7 @@
         <v>1</v>
       </c>
       <c r="T55" s="0" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="U55" s="0" t="n">
         <v>1</v>
@@ -7214,6 +7212,12 @@
       </c>
       <c r="Y55" s="0" t="n">
         <v>0.5</v>
+      </c>
+      <c r="Z55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="AB55" s="0" t="n">
         <v>100</v>
@@ -7225,13 +7229,13 @@
         <v>0</v>
       </c>
       <c r="AG55" s="0" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AJ55" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK55" s="0" t="n">
-        <v>1000001</v>
+        <v>0</v>
       </c>
       <c r="AL55" s="0" t="inlineStr">
         <is>
@@ -7240,11 +7244,22 @@
       </c>
       <c r="AM55" s="0" t="inlineStr">
         <is>
-          <t>Card_Scene_2</t>
+          <t>Card_Scene_1</t>
+        </is>
+      </c>
+      <c r="AN55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
         </is>
       </c>
       <c r="AR55" s="0" t="n">
-        <v>104001</v>
+        <v>2001</v>
+      </c>
+      <c r="AS55" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="AT55" s="0" t="inlineStr">
         <is>
@@ -7254,18 +7269,21 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>104002</v>
+        <v>103107</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>人类-双持战士</t>
+          <t>骷髅投手（召唤物，克隆2002改索敌防守方）</t>
         </is>
       </c>
       <c r="C56" s="0" t="n">
         <v>2</v>
       </c>
       <c r="G56" s="0" t="n">
-        <v>1000001</v>
+        <v>2000001</v>
+      </c>
+      <c r="H56" s="0" t="n">
+        <v>21000001</v>
       </c>
       <c r="I56" s="0" t="inlineStr">
         <is>
@@ -7273,21 +7291,26 @@
         </is>
       </c>
       <c r="J56" s="0" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="N56" s="0" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
       </c>
       <c r="P56" s="0" t="n">
-        <v>100001</v>
+        <v>200001</v>
       </c>
       <c r="Q56" s="0" t="inlineStr">
         <is>
-          <t>0,0.5,0</t>
+          <t>0,0.7,0</t>
         </is>
       </c>
       <c r="S56" s="0" t="n">
         <v>1</v>
       </c>
       <c r="T56" s="0" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="U56" s="0" t="n">
         <v>1</v>
@@ -7304,8 +7327,14 @@
       <c r="Y56" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="Z56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="AB56" s="0" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AE56" s="0" t="n">
         <v>10</v>
@@ -7317,23 +7346,34 @@
         <v>10</v>
       </c>
       <c r="AJ56" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK56" s="0" t="n">
-        <v>1000001</v>
+        <v>0</v>
       </c>
       <c r="AL56" s="0" t="inlineStr">
         <is>
-          <t>ui_class_3</t>
+          <t>ui_class_6</t>
         </is>
       </c>
       <c r="AM56" s="0" t="inlineStr">
         <is>
-          <t>Card_Scene_2</t>
+          <t>Card_Scene_1</t>
+        </is>
+      </c>
+      <c r="AN56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO56" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
         </is>
       </c>
       <c r="AR56" s="0" t="n">
-        <v>104002</v>
+        <v>2002</v>
+      </c>
+      <c r="AS56" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="AT56" s="0" t="inlineStr">
         <is>
@@ -7343,15 +7383,20 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>104101</v>
+        <v>104001</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>人类-大剑战士</t>
+          <t>人类-盗贼</t>
         </is>
       </c>
       <c r="C57" s="0" t="n">
         <v>2</v>
+      </c>
+      <c r="F57" s="0" t="inlineStr">
+        <is>
+          <t>2000100001,</t>
+        </is>
       </c>
       <c r="G57" s="0" t="n">
         <v>1000001</v>
@@ -7366,11 +7411,11 @@
       </c>
       <c r="N57" s="0" t="inlineStr">
         <is>
-          <t>Attack8</t>
+          <t>Attack6</t>
         </is>
       </c>
       <c r="P57" s="0" t="n">
-        <v>101006</v>
+        <v>100002</v>
       </c>
       <c r="Q57" s="0" t="inlineStr">
         <is>
@@ -7401,9 +7446,6 @@
       <c r="AB57" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="AD57" s="0" t="n">
-        <v>100</v>
-      </c>
       <c r="AE57" s="0" t="n">
         <v>10</v>
       </c>
@@ -7411,7 +7453,7 @@
         <v>0</v>
       </c>
       <c r="AG57" s="0" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AJ57" s="0" t="n">
         <v>1</v>
@@ -7421,7 +7463,7 @@
       </c>
       <c r="AL57" s="0" t="inlineStr">
         <is>
-          <t>ui_class_7</t>
+          <t>ui_class_3</t>
         </is>
       </c>
       <c r="AM57" s="0" t="inlineStr">
@@ -7430,7 +7472,7 @@
         </is>
       </c>
       <c r="AR57" s="0" t="n">
-        <v>104101</v>
+        <v>104001</v>
       </c>
       <c r="AT57" s="0" t="inlineStr">
         <is>
@@ -7440,20 +7482,15 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>104102</v>
+        <v>104002</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>人类-大盾战士</t>
+          <t>人类-双持战士</t>
         </is>
       </c>
       <c r="C58" s="0" t="n">
         <v>2</v>
-      </c>
-      <c r="F58" s="0" t="inlineStr">
-        <is>
-          <t>2000600001,</t>
-        </is>
       </c>
       <c r="G58" s="0" t="n">
         <v>1000001</v>
@@ -7464,17 +7501,7 @@
         </is>
       </c>
       <c r="J58" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="M58" s="0" t="inlineStr">
-        <is>
-          <t>Walk4</t>
-        </is>
-      </c>
-      <c r="N58" s="0" t="inlineStr">
-        <is>
-          <t>Attack7</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="P58" s="0" t="n">
         <v>100001</v>
@@ -7508,9 +7535,6 @@
       <c r="AB58" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="AD58" s="0" t="n">
-        <v>100</v>
-      </c>
       <c r="AE58" s="0" t="n">
         <v>10</v>
       </c>
@@ -7528,7 +7552,7 @@
       </c>
       <c r="AL58" s="0" t="inlineStr">
         <is>
-          <t>ui_class_7</t>
+          <t>ui_class_3</t>
         </is>
       </c>
       <c r="AM58" s="0" t="inlineStr">
@@ -7537,7 +7561,7 @@
         </is>
       </c>
       <c r="AR58" s="0" t="n">
-        <v>104102</v>
+        <v>104002</v>
       </c>
       <c r="AT58" s="0" t="inlineStr">
         <is>
@@ -7547,11 +7571,11 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>104103</v>
+        <v>104101</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>人类-长枪骑士</t>
+          <t>人类-大剑战士</t>
         </is>
       </c>
       <c r="C59" s="0" t="n">
@@ -7634,7 +7658,7 @@
         </is>
       </c>
       <c r="AR59" s="0" t="n">
-        <v>104103</v>
+        <v>104101</v>
       </c>
       <c r="AT59" s="0" t="inlineStr">
         <is>
@@ -7643,44 +7667,44 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
-        <v>900001</v>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>测试骷髅战士</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>21010001</v>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="A60" s="0" t="n">
+        <v>104102</v>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>人类-大盾战士</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" s="0" t="inlineStr">
+        <is>
+          <t>2000600001,</t>
+        </is>
+      </c>
+      <c r="G60" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="I60" s="0" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J60" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K60" s="5" t="n"/>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
-      <c r="N60" s="5" t="inlineStr">
-        <is>
-          <t>Attack2</t>
-        </is>
-      </c>
-      <c r="O60" s="5" t="n"/>
-      <c r="P60" s="5" t="n">
+      <c r="J60" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="M60" s="0" t="inlineStr">
+        <is>
+          <t>Walk4</t>
+        </is>
+      </c>
+      <c r="N60" s="0" t="inlineStr">
+        <is>
+          <t>Attack7</t>
+        </is>
+      </c>
+      <c r="P60" s="0" t="n">
         <v>100001</v>
       </c>
       <c r="Q60" s="0" t="inlineStr">
@@ -7688,71 +7712,60 @@
           <t>0,0.5,0</t>
         </is>
       </c>
-      <c r="R60" s="5" t="n"/>
-      <c r="S60" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T60" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U60" s="5" t="n">
+      <c r="S60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U60" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V60" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W60" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X60" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y60" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z60" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA60" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB60" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AC60" s="5" t="n"/>
-      <c r="AD60" s="5" t="n"/>
-      <c r="AE60" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF60" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG60" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH60" s="5" t="n"/>
-      <c r="AI60" s="5" t="n"/>
-      <c r="AJ60" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK60" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="AL60" s="5" t="inlineStr">
-        <is>
-          <t>ui_class_3</t>
-        </is>
-      </c>
-      <c r="AM60" s="5" t="inlineStr">
-        <is>
-          <t>Card_Scene_1</t>
-        </is>
-      </c>
-      <c r="AN60" s="5" t="n">
-        <v>300200001</v>
-      </c>
-      <c r="AR60" s="5" t="n">
-        <v>900001</v>
+      <c r="W60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X60" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y60" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB60" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD60" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE60" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK60" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="AL60" s="0" t="inlineStr">
+        <is>
+          <t>ui_class_7</t>
+        </is>
+      </c>
+      <c r="AM60" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_2</t>
+        </is>
+      </c>
+      <c r="AR60" s="0" t="n">
+        <v>104102</v>
       </c>
       <c r="AT60" s="0" t="inlineStr">
         <is>
@@ -7761,116 +7774,95 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
-        <v>900002</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>测试骷髅投手</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="n"/>
-      <c r="G61" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>21000001</v>
-      </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="A61" s="0" t="n">
+        <v>104103</v>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>人类-长枪骑士</t>
+        </is>
+      </c>
+      <c r="C61" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="I61" s="0" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J61" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K61" s="5" t="n"/>
-      <c r="L61" s="5" t="n"/>
-      <c r="M61" s="5" t="n"/>
-      <c r="N61" s="5" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="O61" s="5" t="n"/>
-      <c r="P61" s="5" t="n">
-        <v>200001</v>
-      </c>
-      <c r="Q61" s="5" t="inlineStr">
-        <is>
-          <t>0,0.7,0</t>
-        </is>
-      </c>
-      <c r="R61" s="5" t="n"/>
-      <c r="S61" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T61" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="U61" s="5" t="n">
+      <c r="J61" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N61" s="0" t="inlineStr">
+        <is>
+          <t>Attack8</t>
+        </is>
+      </c>
+      <c r="P61" s="0" t="n">
+        <v>101006</v>
+      </c>
+      <c r="Q61" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
+        </is>
+      </c>
+      <c r="S61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U61" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V61" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X61" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y61" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z61" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA61" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB61" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AC61" s="5" t="n"/>
-      <c r="AD61" s="5" t="n"/>
-      <c r="AE61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF61" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG61" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH61" s="5" t="n"/>
-      <c r="AI61" s="5" t="n"/>
-      <c r="AJ61" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK61" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="AL61" s="5" t="inlineStr">
-        <is>
-          <t>ui_class_6</t>
-        </is>
-      </c>
-      <c r="AM61" s="5" t="inlineStr">
-        <is>
-          <t>Card_Scene_1</t>
-        </is>
-      </c>
-      <c r="AN61" s="5" t="n">
-        <v>300200002</v>
-      </c>
-      <c r="AR61" s="5" t="n">
-        <v>900002</v>
+      <c r="W61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X61" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y61" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB61" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD61" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE61" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK61" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="AL61" s="0" t="inlineStr">
+        <is>
+          <t>ui_class_7</t>
+        </is>
+      </c>
+      <c r="AM61" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_2</t>
+        </is>
+      </c>
+      <c r="AR61" s="0" t="n">
+        <v>104103</v>
       </c>
       <c r="AT61" s="0" t="inlineStr">
         <is>
@@ -7879,47 +7871,86 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="0" t="n">
-        <v>989996</v>
-      </c>
-      <c r="B62" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C62" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P62" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S62" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T62" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U62" s="0" t="n">
+      <c r="A62" s="5" t="n">
+        <v>900001</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>测试骷髅战士</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>21010001</v>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>1,2,3,10,</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K62" s="5" t="n"/>
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="n"/>
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t>Attack2</t>
+        </is>
+      </c>
+      <c r="O62" s="5" t="n"/>
+      <c r="P62" s="5" t="n">
+        <v>100001</v>
+      </c>
+      <c r="Q62" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
+        </is>
+      </c>
+      <c r="R62" s="5" t="n"/>
+      <c r="S62" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T62" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U62" s="5" t="n">
         <v>1</v>
       </c>
       <c r="V62" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W62" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X62" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y62" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z62" s="0" t="n"/>
-      <c r="AB62" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE62" s="0" t="n">
-        <v>35</v>
+      <c r="W62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X62" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y62" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA62" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB62" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AC62" s="5" t="n"/>
+      <c r="AD62" s="5" t="n"/>
+      <c r="AE62" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AF62" s="1" t="n">
         <v>0</v>
@@ -7927,18 +7958,29 @@
       <c r="AG62" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AJ62" s="0" t="n">
-        <v>989996</v>
-      </c>
-      <c r="AK62" s="0" t="n"/>
-      <c r="AL62" s="0" t="n"/>
-      <c r="AM62" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR62" s="0" t="n">
-        <v>1</v>
+      <c r="AH62" s="5" t="n"/>
+      <c r="AI62" s="5" t="n"/>
+      <c r="AJ62" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK62" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="AL62" s="5" t="inlineStr">
+        <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="AM62" s="5" t="inlineStr">
+        <is>
+          <t>Card_Scene_1</t>
+        </is>
+      </c>
+      <c r="AN62" s="5" t="n">
+        <v>300200001</v>
+      </c>
+      <c r="AR62" s="5" t="n">
+        <v>900001</v>
       </c>
       <c r="AT62" s="0" t="inlineStr">
         <is>
@@ -7947,47 +7989,86 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="0" t="n">
-        <v>989997</v>
-      </c>
-      <c r="B63" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C63" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P63" s="0" t="n">
+      <c r="A63" s="5" t="n">
+        <v>900002</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>测试骷髅投手</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>21000001</v>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>1,2,3,10,</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="O63" s="5" t="n"/>
+      <c r="P63" s="5" t="n">
         <v>200001</v>
       </c>
-      <c r="S63" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T63" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U63" s="0" t="n">
+      <c r="Q63" s="5" t="inlineStr">
+        <is>
+          <t>0,0.7,0</t>
+        </is>
+      </c>
+      <c r="R63" s="5" t="n"/>
+      <c r="S63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T63" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="U63" s="5" t="n">
         <v>1</v>
       </c>
       <c r="V63" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W63" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X63" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y63" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z63" s="0" t="n"/>
-      <c r="AB63" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE63" s="0" t="n">
-        <v>35</v>
+      <c r="W63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X63" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y63" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA63" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB63" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AC63" s="5" t="n"/>
+      <c r="AD63" s="5" t="n"/>
+      <c r="AE63" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AF63" s="1" t="n">
         <v>0</v>
@@ -7995,18 +8076,29 @@
       <c r="AG63" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AJ63" s="0" t="n">
-        <v>989997</v>
-      </c>
-      <c r="AK63" s="0" t="n"/>
-      <c r="AL63" s="0" t="n"/>
-      <c r="AM63" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR63" s="0" t="n">
-        <v>1</v>
+      <c r="AH63" s="5" t="n"/>
+      <c r="AI63" s="5" t="n"/>
+      <c r="AJ63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK63" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="AL63" s="5" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="AM63" s="5" t="inlineStr">
+        <is>
+          <t>Card_Scene_1</t>
+        </is>
+      </c>
+      <c r="AN63" s="5" t="n">
+        <v>300200002</v>
+      </c>
+      <c r="AR63" s="5" t="n">
+        <v>900002</v>
       </c>
       <c r="AT63" s="0" t="inlineStr">
         <is>
@@ -8016,7 +8108,7 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>989998</v>
+        <v>989996</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
@@ -8064,7 +8156,7 @@
         <v>10</v>
       </c>
       <c r="AJ64" s="0" t="n">
-        <v>989998</v>
+        <v>989996</v>
       </c>
       <c r="AK64" s="0" t="n"/>
       <c r="AL64" s="0" t="n"/>
@@ -8084,7 +8176,7 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>989999</v>
+        <v>989997</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
@@ -8132,8 +8224,10 @@
         <v>10</v>
       </c>
       <c r="AJ65" s="0" t="n">
-        <v>989999</v>
-      </c>
+        <v>989997</v>
+      </c>
+      <c r="AK65" s="0" t="n"/>
+      <c r="AL65" s="0" t="n"/>
       <c r="AM65" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -8150,7 +8244,7 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>999947</v>
+        <v>989998</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
@@ -8198,7 +8292,7 @@
         <v>10</v>
       </c>
       <c r="AJ66" s="0" t="n">
-        <v>999947</v>
+        <v>989998</v>
       </c>
       <c r="AK66" s="0" t="n"/>
       <c r="AL66" s="0" t="n"/>
@@ -8218,7 +8312,7 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>999948</v>
+        <v>989999</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
@@ -8266,10 +8360,8 @@
         <v>10</v>
       </c>
       <c r="AJ67" s="0" t="n">
-        <v>999948</v>
-      </c>
-      <c r="AK67" s="0" t="n"/>
-      <c r="AL67" s="0" t="n"/>
+        <v>989999</v>
+      </c>
       <c r="AM67" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -8286,7 +8378,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>999949</v>
+        <v>999947</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
@@ -8334,7 +8426,7 @@
         <v>10</v>
       </c>
       <c r="AJ68" s="0" t="n">
-        <v>999949</v>
+        <v>999947</v>
       </c>
       <c r="AK68" s="0" t="n"/>
       <c r="AL68" s="0" t="n"/>
@@ -8354,7 +8446,7 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>999950</v>
+        <v>999948</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
@@ -8402,7 +8494,7 @@
         <v>10</v>
       </c>
       <c r="AJ69" s="0" t="n">
-        <v>999950</v>
+        <v>999948</v>
       </c>
       <c r="AK69" s="0" t="n"/>
       <c r="AL69" s="0" t="n"/>
@@ -8422,7 +8514,7 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>999951</v>
+        <v>999949</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
@@ -8470,7 +8562,7 @@
         <v>10</v>
       </c>
       <c r="AJ70" s="0" t="n">
-        <v>999951</v>
+        <v>999949</v>
       </c>
       <c r="AK70" s="0" t="n"/>
       <c r="AL70" s="0" t="n"/>
@@ -8490,7 +8582,7 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>999952</v>
+        <v>999950</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
@@ -8538,7 +8630,7 @@
         <v>10</v>
       </c>
       <c r="AJ71" s="0" t="n">
-        <v>999952</v>
+        <v>999950</v>
       </c>
       <c r="AK71" s="0" t="n"/>
       <c r="AL71" s="0" t="n"/>
@@ -8558,7 +8650,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>999953</v>
+        <v>999951</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
@@ -8606,7 +8698,7 @@
         <v>10</v>
       </c>
       <c r="AJ72" s="0" t="n">
-        <v>999953</v>
+        <v>999951</v>
       </c>
       <c r="AK72" s="0" t="n"/>
       <c r="AL72" s="0" t="n"/>
@@ -8626,7 +8718,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>999954</v>
+        <v>999952</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
@@ -8674,7 +8766,7 @@
         <v>10</v>
       </c>
       <c r="AJ73" s="0" t="n">
-        <v>999954</v>
+        <v>999952</v>
       </c>
       <c r="AK73" s="0" t="n"/>
       <c r="AL73" s="0" t="n"/>
@@ -8694,7 +8786,7 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>999955</v>
+        <v>999953</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
@@ -8742,7 +8834,7 @@
         <v>10</v>
       </c>
       <c r="AJ74" s="0" t="n">
-        <v>999955</v>
+        <v>999953</v>
       </c>
       <c r="AK74" s="0" t="n"/>
       <c r="AL74" s="0" t="n"/>
@@ -8762,7 +8854,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>999956</v>
+        <v>999954</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
@@ -8810,7 +8902,7 @@
         <v>10</v>
       </c>
       <c r="AJ75" s="0" t="n">
-        <v>999956</v>
+        <v>999954</v>
       </c>
       <c r="AK75" s="0" t="n"/>
       <c r="AL75" s="0" t="n"/>
@@ -8830,7 +8922,7 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>999957</v>
+        <v>999955</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
@@ -8878,7 +8970,7 @@
         <v>10</v>
       </c>
       <c r="AJ76" s="0" t="n">
-        <v>999957</v>
+        <v>999955</v>
       </c>
       <c r="AK76" s="0" t="n"/>
       <c r="AL76" s="0" t="n"/>
@@ -8898,7 +8990,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>999958</v>
+        <v>999956</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
@@ -8946,7 +9038,7 @@
         <v>10</v>
       </c>
       <c r="AJ77" s="0" t="n">
-        <v>999958</v>
+        <v>999956</v>
       </c>
       <c r="AK77" s="0" t="n"/>
       <c r="AL77" s="0" t="n"/>
@@ -8966,7 +9058,7 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>999959</v>
+        <v>999957</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
@@ -9014,7 +9106,7 @@
         <v>10</v>
       </c>
       <c r="AJ78" s="0" t="n">
-        <v>999959</v>
+        <v>999957</v>
       </c>
       <c r="AK78" s="0" t="n"/>
       <c r="AL78" s="0" t="n"/>
@@ -9034,7 +9126,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>999960</v>
+        <v>999958</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
@@ -9082,7 +9174,7 @@
         <v>10</v>
       </c>
       <c r="AJ79" s="0" t="n">
-        <v>999960</v>
+        <v>999958</v>
       </c>
       <c r="AK79" s="0" t="n"/>
       <c r="AL79" s="0" t="n"/>
@@ -9102,7 +9194,7 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>999961</v>
+        <v>999959</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
@@ -9150,7 +9242,7 @@
         <v>10</v>
       </c>
       <c r="AJ80" s="0" t="n">
-        <v>999961</v>
+        <v>999959</v>
       </c>
       <c r="AK80" s="0" t="n"/>
       <c r="AL80" s="0" t="n"/>
@@ -9170,7 +9262,7 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>999962</v>
+        <v>999960</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
@@ -9218,7 +9310,7 @@
         <v>10</v>
       </c>
       <c r="AJ81" s="0" t="n">
-        <v>999962</v>
+        <v>999960</v>
       </c>
       <c r="AK81" s="0" t="n"/>
       <c r="AL81" s="0" t="n"/>
@@ -9238,7 +9330,7 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>999963</v>
+        <v>999961</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
@@ -9286,7 +9378,7 @@
         <v>10</v>
       </c>
       <c r="AJ82" s="0" t="n">
-        <v>999963</v>
+        <v>999961</v>
       </c>
       <c r="AK82" s="0" t="n"/>
       <c r="AL82" s="0" t="n"/>
@@ -9306,7 +9398,7 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>999964</v>
+        <v>999962</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
@@ -9354,7 +9446,7 @@
         <v>10</v>
       </c>
       <c r="AJ83" s="0" t="n">
-        <v>999964</v>
+        <v>999962</v>
       </c>
       <c r="AK83" s="0" t="n"/>
       <c r="AL83" s="0" t="n"/>
@@ -9374,7 +9466,7 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>999965</v>
+        <v>999963</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
@@ -9422,7 +9514,7 @@
         <v>10</v>
       </c>
       <c r="AJ84" s="0" t="n">
-        <v>999965</v>
+        <v>999963</v>
       </c>
       <c r="AK84" s="0" t="n"/>
       <c r="AL84" s="0" t="n"/>
@@ -9442,7 +9534,7 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>999966</v>
+        <v>999964</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
@@ -9490,7 +9582,7 @@
         <v>10</v>
       </c>
       <c r="AJ85" s="0" t="n">
-        <v>999966</v>
+        <v>999964</v>
       </c>
       <c r="AK85" s="0" t="n"/>
       <c r="AL85" s="0" t="n"/>
@@ -9510,7 +9602,7 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>999967</v>
+        <v>999965</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
@@ -9558,7 +9650,7 @@
         <v>10</v>
       </c>
       <c r="AJ86" s="0" t="n">
-        <v>999967</v>
+        <v>999965</v>
       </c>
       <c r="AK86" s="0" t="n"/>
       <c r="AL86" s="0" t="n"/>
@@ -9578,7 +9670,7 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>999968</v>
+        <v>999966</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
@@ -9626,7 +9718,7 @@
         <v>10</v>
       </c>
       <c r="AJ87" s="0" t="n">
-        <v>999968</v>
+        <v>999966</v>
       </c>
       <c r="AK87" s="0" t="n"/>
       <c r="AL87" s="0" t="n"/>
@@ -9646,7 +9738,7 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>999969</v>
+        <v>999967</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
@@ -9694,7 +9786,7 @@
         <v>10</v>
       </c>
       <c r="AJ88" s="0" t="n">
-        <v>999969</v>
+        <v>999967</v>
       </c>
       <c r="AK88" s="0" t="n"/>
       <c r="AL88" s="0" t="n"/>
@@ -9714,7 +9806,7 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>999970</v>
+        <v>999968</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
@@ -9762,7 +9854,7 @@
         <v>10</v>
       </c>
       <c r="AJ89" s="0" t="n">
-        <v>999970</v>
+        <v>999968</v>
       </c>
       <c r="AK89" s="0" t="n"/>
       <c r="AL89" s="0" t="n"/>
@@ -9782,7 +9874,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>999971</v>
+        <v>999969</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
@@ -9830,7 +9922,7 @@
         <v>10</v>
       </c>
       <c r="AJ90" s="0" t="n">
-        <v>999971</v>
+        <v>999969</v>
       </c>
       <c r="AK90" s="0" t="n"/>
       <c r="AL90" s="0" t="n"/>
@@ -9850,7 +9942,7 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>999972</v>
+        <v>999970</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
@@ -9898,7 +9990,7 @@
         <v>10</v>
       </c>
       <c r="AJ91" s="0" t="n">
-        <v>999972</v>
+        <v>999970</v>
       </c>
       <c r="AK91" s="0" t="n"/>
       <c r="AL91" s="0" t="n"/>
@@ -9918,7 +10010,7 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>999973</v>
+        <v>999971</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
@@ -9966,7 +10058,7 @@
         <v>10</v>
       </c>
       <c r="AJ92" s="0" t="n">
-        <v>999973</v>
+        <v>999971</v>
       </c>
       <c r="AK92" s="0" t="n"/>
       <c r="AL92" s="0" t="n"/>
@@ -9986,7 +10078,7 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>999974</v>
+        <v>999972</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
@@ -10034,7 +10126,7 @@
         <v>10</v>
       </c>
       <c r="AJ93" s="0" t="n">
-        <v>999974</v>
+        <v>999972</v>
       </c>
       <c r="AK93" s="0" t="n"/>
       <c r="AL93" s="0" t="n"/>
@@ -10054,7 +10146,7 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>999975</v>
+        <v>999973</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
@@ -10102,7 +10194,7 @@
         <v>10</v>
       </c>
       <c r="AJ94" s="0" t="n">
-        <v>999975</v>
+        <v>999973</v>
       </c>
       <c r="AK94" s="0" t="n"/>
       <c r="AL94" s="0" t="n"/>
@@ -10122,7 +10214,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>999976</v>
+        <v>999974</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
@@ -10170,7 +10262,7 @@
         <v>10</v>
       </c>
       <c r="AJ95" s="0" t="n">
-        <v>999976</v>
+        <v>999974</v>
       </c>
       <c r="AK95" s="0" t="n"/>
       <c r="AL95" s="0" t="n"/>
@@ -10190,7 +10282,7 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>999977</v>
+        <v>999975</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
@@ -10238,7 +10330,7 @@
         <v>10</v>
       </c>
       <c r="AJ96" s="0" t="n">
-        <v>999977</v>
+        <v>999975</v>
       </c>
       <c r="AK96" s="0" t="n"/>
       <c r="AL96" s="0" t="n"/>
@@ -10258,7 +10350,7 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>999978</v>
+        <v>999976</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
@@ -10306,7 +10398,7 @@
         <v>10</v>
       </c>
       <c r="AJ97" s="0" t="n">
-        <v>999978</v>
+        <v>999976</v>
       </c>
       <c r="AK97" s="0" t="n"/>
       <c r="AL97" s="0" t="n"/>
@@ -10326,7 +10418,7 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>999979</v>
+        <v>999977</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
@@ -10374,7 +10466,7 @@
         <v>10</v>
       </c>
       <c r="AJ98" s="0" t="n">
-        <v>999979</v>
+        <v>999977</v>
       </c>
       <c r="AK98" s="0" t="n"/>
       <c r="AL98" s="0" t="n"/>
@@ -10394,7 +10486,7 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>999980</v>
+        <v>999978</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
@@ -10442,7 +10534,7 @@
         <v>10</v>
       </c>
       <c r="AJ99" s="0" t="n">
-        <v>999980</v>
+        <v>999978</v>
       </c>
       <c r="AK99" s="0" t="n"/>
       <c r="AL99" s="0" t="n"/>
@@ -10462,7 +10554,7 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>999981</v>
+        <v>999979</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
@@ -10510,7 +10602,7 @@
         <v>10</v>
       </c>
       <c r="AJ100" s="0" t="n">
-        <v>999981</v>
+        <v>999979</v>
       </c>
       <c r="AK100" s="0" t="n"/>
       <c r="AL100" s="0" t="n"/>
@@ -10530,7 +10622,7 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>999982</v>
+        <v>999980</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
@@ -10564,6 +10656,7 @@
       <c r="Y101" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="Z101" s="0" t="n"/>
       <c r="AB101" s="0" t="n">
         <v>100</v>
       </c>
@@ -10577,8 +10670,10 @@
         <v>10</v>
       </c>
       <c r="AJ101" s="0" t="n">
-        <v>999982</v>
-      </c>
+        <v>999980</v>
+      </c>
+      <c r="AK101" s="0" t="n"/>
+      <c r="AL101" s="0" t="n"/>
       <c r="AM101" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -10595,7 +10690,7 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>999983</v>
+        <v>999981</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
@@ -10629,6 +10724,7 @@
       <c r="Y102" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="Z102" s="0" t="n"/>
       <c r="AB102" s="0" t="n">
         <v>100</v>
       </c>
@@ -10642,8 +10738,10 @@
         <v>10</v>
       </c>
       <c r="AJ102" s="0" t="n">
-        <v>999983</v>
-      </c>
+        <v>999981</v>
+      </c>
+      <c r="AK102" s="0" t="n"/>
+      <c r="AL102" s="0" t="n"/>
       <c r="AM102" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -10660,7 +10758,7 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>999984</v>
+        <v>999982</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
@@ -10707,7 +10805,7 @@
         <v>10</v>
       </c>
       <c r="AJ103" s="0" t="n">
-        <v>999984</v>
+        <v>999982</v>
       </c>
       <c r="AM103" s="0" t="inlineStr">
         <is>
@@ -10725,7 +10823,7 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>999985</v>
+        <v>999983</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
@@ -10772,7 +10870,7 @@
         <v>10</v>
       </c>
       <c r="AJ104" s="0" t="n">
-        <v>999985</v>
+        <v>999983</v>
       </c>
       <c r="AM104" s="0" t="inlineStr">
         <is>
@@ -10790,7 +10888,7 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>999986</v>
+        <v>999984</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
@@ -10837,7 +10935,7 @@
         <v>10</v>
       </c>
       <c r="AJ105" s="0" t="n">
-        <v>999986</v>
+        <v>999984</v>
       </c>
       <c r="AM105" s="0" t="inlineStr">
         <is>
@@ -10855,7 +10953,7 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>999987</v>
+        <v>999985</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
@@ -10902,7 +11000,7 @@
         <v>10</v>
       </c>
       <c r="AJ106" s="0" t="n">
-        <v>999987</v>
+        <v>999985</v>
       </c>
       <c r="AM106" s="0" t="inlineStr">
         <is>
@@ -10920,7 +11018,7 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>999988</v>
+        <v>999986</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
@@ -10967,7 +11065,7 @@
         <v>10</v>
       </c>
       <c r="AJ107" s="0" t="n">
-        <v>999988</v>
+        <v>999986</v>
       </c>
       <c r="AM107" s="0" t="inlineStr">
         <is>
@@ -10985,7 +11083,7 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>999989</v>
+        <v>999987</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
@@ -11032,7 +11130,7 @@
         <v>10</v>
       </c>
       <c r="AJ108" s="0" t="n">
-        <v>999989</v>
+        <v>999987</v>
       </c>
       <c r="AM108" s="0" t="inlineStr">
         <is>
@@ -11050,7 +11148,7 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>999990</v>
+        <v>999988</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
@@ -11097,7 +11195,7 @@
         <v>10</v>
       </c>
       <c r="AJ109" s="0" t="n">
-        <v>999990</v>
+        <v>999988</v>
       </c>
       <c r="AM109" s="0" t="inlineStr">
         <is>
@@ -11115,7 +11213,7 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>999991</v>
+        <v>999989</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
@@ -11162,7 +11260,7 @@
         <v>10</v>
       </c>
       <c r="AJ110" s="0" t="n">
-        <v>999991</v>
+        <v>999989</v>
       </c>
       <c r="AM110" s="0" t="inlineStr">
         <is>
@@ -11180,7 +11278,7 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>999992</v>
+        <v>999990</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
@@ -11227,7 +11325,7 @@
         <v>10</v>
       </c>
       <c r="AJ111" s="0" t="n">
-        <v>999992</v>
+        <v>999990</v>
       </c>
       <c r="AM111" s="0" t="inlineStr">
         <is>
@@ -11245,7 +11343,7 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>999993</v>
+        <v>999991</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
@@ -11292,7 +11390,7 @@
         <v>10</v>
       </c>
       <c r="AJ112" s="0" t="n">
-        <v>999993</v>
+        <v>999991</v>
       </c>
       <c r="AM112" s="0" t="inlineStr">
         <is>
@@ -11310,7 +11408,7 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>999994</v>
+        <v>999992</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
@@ -11357,7 +11455,7 @@
         <v>10</v>
       </c>
       <c r="AJ113" s="0" t="n">
-        <v>999994</v>
+        <v>999992</v>
       </c>
       <c r="AM113" s="0" t="inlineStr">
         <is>
@@ -11375,7 +11473,7 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>999995</v>
+        <v>999993</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
@@ -11422,7 +11520,7 @@
         <v>10</v>
       </c>
       <c r="AJ114" s="0" t="n">
-        <v>999995</v>
+        <v>999993</v>
       </c>
       <c r="AM114" s="0" t="inlineStr">
         <is>
@@ -11440,7 +11538,7 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>999996</v>
+        <v>999994</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
@@ -11487,7 +11585,7 @@
         <v>10</v>
       </c>
       <c r="AJ115" s="0" t="n">
-        <v>999996</v>
+        <v>999994</v>
       </c>
       <c r="AM115" s="0" t="inlineStr">
         <is>
@@ -11505,7 +11603,7 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>999997</v>
+        <v>999995</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
@@ -11552,7 +11650,7 @@
         <v>10</v>
       </c>
       <c r="AJ116" s="0" t="n">
-        <v>999997</v>
+        <v>999995</v>
       </c>
       <c r="AM116" s="0" t="inlineStr">
         <is>
@@ -11570,7 +11668,7 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>999998</v>
+        <v>999996</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
@@ -11617,7 +11715,7 @@
         <v>10</v>
       </c>
       <c r="AJ117" s="0" t="n">
-        <v>999998</v>
+        <v>999996</v>
       </c>
       <c r="AM117" s="0" t="inlineStr">
         <is>
@@ -11635,7 +11733,7 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>999999</v>
+        <v>999997</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
@@ -11682,17 +11780,147 @@
         <v>10</v>
       </c>
       <c r="AJ118" s="0" t="n">
+        <v>999997</v>
+      </c>
+      <c r="AM118" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_4</t>
+        </is>
+      </c>
+      <c r="AR118" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT118" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="n">
+        <v>999998</v>
+      </c>
+      <c r="B119" s="0" t="inlineStr">
+        <is>
+          <t>测试数据</t>
+        </is>
+      </c>
+      <c r="C119" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P119" s="0" t="n">
+        <v>200001</v>
+      </c>
+      <c r="S119" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="T119" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="U119" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V119" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X119" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y119" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB119" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE119" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF119" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG119" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ119" s="0" t="n">
+        <v>999998</v>
+      </c>
+      <c r="AM119" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_4</t>
+        </is>
+      </c>
+      <c r="AR119" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT119" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="n">
         <v>999999</v>
       </c>
-      <c r="AM118" s="0" t="inlineStr">
+      <c r="B120" s="0" t="inlineStr">
+        <is>
+          <t>测试数据</t>
+        </is>
+      </c>
+      <c r="C120" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P120" s="0" t="n">
+        <v>200001</v>
+      </c>
+      <c r="S120" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="T120" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="U120" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V120" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X120" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y120" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB120" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE120" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG120" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ120" s="0" t="n">
+        <v>999999</v>
+      </c>
+      <c r="AM120" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AR118" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT118" s="0" t="inlineStr">
+      <c r="AR120" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT120" s="0" t="inlineStr">
         <is>
           <t>1,3,4,6</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -1080,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT120"/>
+  <dimension ref="A1:AT121"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="7.375" customWidth="1" style="3" min="1" max="1"/>
@@ -7382,99 +7382,130 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="0" t="n">
-        <v>104001</v>
-      </c>
-      <c r="B57" s="0" t="inlineStr">
-        <is>
-          <t>人类-盗贼</t>
-        </is>
-      </c>
-      <c r="C57" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F57" s="0" t="inlineStr">
-        <is>
-          <t>2000100001,</t>
-        </is>
-      </c>
-      <c r="G57" s="0" t="n">
+      <c r="A57" t="n">
+        <v>103108</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>人类-牧师</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" t="n">
         <v>1000001</v>
       </c>
-      <c r="I57" s="0" t="inlineStr">
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J57" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N57" s="0" t="inlineStr">
-        <is>
-          <t>Attack6</t>
-        </is>
-      </c>
-      <c r="P57" s="0" t="n">
-        <v>100002</v>
-      </c>
-      <c r="Q57" s="0" t="inlineStr">
-        <is>
-          <t>0,0.5,0</t>
-        </is>
-      </c>
-      <c r="S57" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="T57" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U57" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X57" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y57" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB57" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE57" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ57" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK57" s="0" t="n">
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Attack2</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>102003</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>0,0.6,0</t>
+        </is>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>5</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK57" t="n">
         <v>1000001</v>
       </c>
-      <c r="AL57" s="0" t="inlineStr">
-        <is>
-          <t>ui_class_3</t>
-        </is>
-      </c>
-      <c r="AM57" s="0" t="inlineStr">
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>ui_class_5</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
         <is>
           <t>Card_Scene_2</t>
         </is>
       </c>
-      <c r="AR57" s="0" t="n">
-        <v>104001</v>
-      </c>
-      <c r="AT57" s="0" t="inlineStr">
+      <c r="AN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>103108</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr">
         <is>
           <t>1,3,4,6</t>
         </is>
@@ -7482,15 +7513,20 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>104002</v>
+        <v>104001</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>人类-双持战士</t>
+          <t>人类-盗贼</t>
         </is>
       </c>
       <c r="C58" s="0" t="n">
         <v>2</v>
+      </c>
+      <c r="F58" s="0" t="inlineStr">
+        <is>
+          <t>2000100001,</t>
+        </is>
       </c>
       <c r="G58" s="0" t="n">
         <v>1000001</v>
@@ -7501,10 +7537,15 @@
         </is>
       </c>
       <c r="J58" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="N58" s="0" t="inlineStr">
+        <is>
+          <t>Attack6</t>
+        </is>
       </c>
       <c r="P58" s="0" t="n">
-        <v>100001</v>
+        <v>100002</v>
       </c>
       <c r="Q58" s="0" t="inlineStr">
         <is>
@@ -7542,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="AG58" s="0" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AJ58" s="0" t="n">
         <v>1</v>
@@ -7561,7 +7602,7 @@
         </is>
       </c>
       <c r="AR58" s="0" t="n">
-        <v>104002</v>
+        <v>104001</v>
       </c>
       <c r="AT58" s="0" t="inlineStr">
         <is>
@@ -7571,11 +7612,11 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>104101</v>
+        <v>104002</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>人类-大剑战士</t>
+          <t>人类-双持战士</t>
         </is>
       </c>
       <c r="C59" s="0" t="n">
@@ -7590,15 +7631,10 @@
         </is>
       </c>
       <c r="J59" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N59" s="0" t="inlineStr">
-        <is>
-          <t>Attack8</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="P59" s="0" t="n">
-        <v>101006</v>
+        <v>100001</v>
       </c>
       <c r="Q59" s="0" t="inlineStr">
         <is>
@@ -7629,9 +7665,6 @@
       <c r="AB59" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="AD59" s="0" t="n">
-        <v>100</v>
-      </c>
       <c r="AE59" s="0" t="n">
         <v>10</v>
       </c>
@@ -7649,7 +7682,7 @@
       </c>
       <c r="AL59" s="0" t="inlineStr">
         <is>
-          <t>ui_class_7</t>
+          <t>ui_class_3</t>
         </is>
       </c>
       <c r="AM59" s="0" t="inlineStr">
@@ -7658,7 +7691,7 @@
         </is>
       </c>
       <c r="AR59" s="0" t="n">
-        <v>104101</v>
+        <v>104002</v>
       </c>
       <c r="AT59" s="0" t="inlineStr">
         <is>
@@ -7668,20 +7701,15 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>104102</v>
+        <v>104101</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>人类-大盾战士</t>
+          <t>人类-大剑战士</t>
         </is>
       </c>
       <c r="C60" s="0" t="n">
         <v>2</v>
-      </c>
-      <c r="F60" s="0" t="inlineStr">
-        <is>
-          <t>2000600001,</t>
-        </is>
       </c>
       <c r="G60" s="0" t="n">
         <v>1000001</v>
@@ -7692,20 +7720,15 @@
         </is>
       </c>
       <c r="J60" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="M60" s="0" t="inlineStr">
-        <is>
-          <t>Walk4</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="N60" s="0" t="inlineStr">
         <is>
-          <t>Attack7</t>
+          <t>Attack8</t>
         </is>
       </c>
       <c r="P60" s="0" t="n">
-        <v>100001</v>
+        <v>101006</v>
       </c>
       <c r="Q60" s="0" t="inlineStr">
         <is>
@@ -7765,7 +7788,7 @@
         </is>
       </c>
       <c r="AR60" s="0" t="n">
-        <v>104102</v>
+        <v>104101</v>
       </c>
       <c r="AT60" s="0" t="inlineStr">
         <is>
@@ -7775,15 +7798,20 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>104103</v>
+        <v>104102</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>人类-长枪骑士</t>
+          <t>人类-大盾战士</t>
         </is>
       </c>
       <c r="C61" s="0" t="n">
         <v>2</v>
+      </c>
+      <c r="F61" s="0" t="inlineStr">
+        <is>
+          <t>2000600001,</t>
+        </is>
       </c>
       <c r="G61" s="0" t="n">
         <v>1000001</v>
@@ -7794,15 +7822,20 @@
         </is>
       </c>
       <c r="J61" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="M61" s="0" t="inlineStr">
+        <is>
+          <t>Walk4</t>
+        </is>
       </c>
       <c r="N61" s="0" t="inlineStr">
         <is>
-          <t>Attack8</t>
+          <t>Attack7</t>
         </is>
       </c>
       <c r="P61" s="0" t="n">
-        <v>101006</v>
+        <v>100001</v>
       </c>
       <c r="Q61" s="0" t="inlineStr">
         <is>
@@ -7862,7 +7895,7 @@
         </is>
       </c>
       <c r="AR61" s="0" t="n">
-        <v>104103</v>
+        <v>104102</v>
       </c>
       <c r="AT61" s="0" t="inlineStr">
         <is>
@@ -7871,116 +7904,95 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
-        <v>900001</v>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>测试骷髅战士</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="n"/>
-      <c r="G62" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>21010001</v>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="A62" s="0" t="n">
+        <v>104103</v>
+      </c>
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>人类-长枪骑士</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="I62" s="0" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J62" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K62" s="5" t="n"/>
-      <c r="L62" s="5" t="n"/>
-      <c r="M62" s="5" t="n"/>
-      <c r="N62" s="5" t="inlineStr">
-        <is>
-          <t>Attack2</t>
-        </is>
-      </c>
-      <c r="O62" s="5" t="n"/>
-      <c r="P62" s="5" t="n">
-        <v>100001</v>
+      <c r="J62" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N62" s="0" t="inlineStr">
+        <is>
+          <t>Attack8</t>
+        </is>
+      </c>
+      <c r="P62" s="0" t="n">
+        <v>101006</v>
       </c>
       <c r="Q62" s="0" t="inlineStr">
         <is>
           <t>0,0.5,0</t>
         </is>
       </c>
-      <c r="R62" s="5" t="n"/>
-      <c r="S62" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T62" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U62" s="5" t="n">
+      <c r="S62" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U62" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V62" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W62" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X62" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y62" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z62" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA62" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB62" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AC62" s="5" t="n"/>
-      <c r="AD62" s="5" t="n"/>
-      <c r="AE62" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF62" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG62" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH62" s="5" t="n"/>
-      <c r="AI62" s="5" t="n"/>
-      <c r="AJ62" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK62" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="AL62" s="5" t="inlineStr">
-        <is>
-          <t>ui_class_3</t>
-        </is>
-      </c>
-      <c r="AM62" s="5" t="inlineStr">
-        <is>
-          <t>Card_Scene_1</t>
-        </is>
-      </c>
-      <c r="AN62" s="5" t="n">
-        <v>300200001</v>
-      </c>
-      <c r="AR62" s="5" t="n">
-        <v>900001</v>
+      <c r="W62" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X62" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y62" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB62" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD62" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE62" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ62" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK62" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="AL62" s="0" t="inlineStr">
+        <is>
+          <t>ui_class_7</t>
+        </is>
+      </c>
+      <c r="AM62" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_2</t>
+        </is>
+      </c>
+      <c r="AR62" s="0" t="n">
+        <v>104103</v>
       </c>
       <c r="AT62" s="0" t="inlineStr">
         <is>
@@ -7990,11 +8002,11 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>900002</v>
+        <v>900001</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>测试骷髅投手</t>
+          <t>测试骷髅战士</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
@@ -8007,7 +8019,7 @@
         <v>2000001</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>21000001</v>
+        <v>21010001</v>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
@@ -8015,23 +8027,23 @@
         </is>
       </c>
       <c r="J63" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K63" s="5" t="n"/>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="5" t="n"/>
       <c r="N63" s="5" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Attack2</t>
         </is>
       </c>
       <c r="O63" s="5" t="n"/>
       <c r="P63" s="5" t="n">
-        <v>200001</v>
-      </c>
-      <c r="Q63" s="5" t="inlineStr">
-        <is>
-          <t>0,0.7,0</t>
+        <v>100001</v>
+      </c>
+      <c r="Q63" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
         </is>
       </c>
       <c r="R63" s="5" t="n"/>
@@ -8039,7 +8051,7 @@
         <v>2</v>
       </c>
       <c r="T63" s="5" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="U63" s="5" t="n">
         <v>1</v>
@@ -8057,7 +8069,7 @@
         <v>0.5</v>
       </c>
       <c r="Z63" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA63" s="5" t="n">
         <v>10</v>
@@ -8086,7 +8098,7 @@
       </c>
       <c r="AL63" s="5" t="inlineStr">
         <is>
-          <t>ui_class_6</t>
+          <t>ui_class_3</t>
         </is>
       </c>
       <c r="AM63" s="5" t="inlineStr">
@@ -8095,10 +8107,10 @@
         </is>
       </c>
       <c r="AN63" s="5" t="n">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="AR63" s="5" t="n">
-        <v>900002</v>
+        <v>900001</v>
       </c>
       <c r="AT63" s="0" t="inlineStr">
         <is>
@@ -8107,47 +8119,86 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="0" t="n">
-        <v>989996</v>
-      </c>
-      <c r="B64" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C64" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P64" s="0" t="n">
+      <c r="A64" s="5" t="n">
+        <v>900002</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>测试骷髅投手</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>21000001</v>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>1,2,3,10,</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="O64" s="5" t="n"/>
+      <c r="P64" s="5" t="n">
         <v>200001</v>
       </c>
-      <c r="S64" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T64" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U64" s="0" t="n">
+      <c r="Q64" s="5" t="inlineStr">
+        <is>
+          <t>0,0.7,0</t>
+        </is>
+      </c>
+      <c r="R64" s="5" t="n"/>
+      <c r="S64" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T64" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="U64" s="5" t="n">
         <v>1</v>
       </c>
       <c r="V64" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W64" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X64" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y64" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z64" s="0" t="n"/>
-      <c r="AB64" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE64" s="0" t="n">
-        <v>35</v>
+      <c r="W64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X64" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y64" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z64" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA64" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB64" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AC64" s="5" t="n"/>
+      <c r="AD64" s="5" t="n"/>
+      <c r="AE64" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AF64" s="1" t="n">
         <v>0</v>
@@ -8155,18 +8206,29 @@
       <c r="AG64" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AJ64" s="0" t="n">
-        <v>989996</v>
-      </c>
-      <c r="AK64" s="0" t="n"/>
-      <c r="AL64" s="0" t="n"/>
-      <c r="AM64" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR64" s="0" t="n">
-        <v>1</v>
+      <c r="AH64" s="5" t="n"/>
+      <c r="AI64" s="5" t="n"/>
+      <c r="AJ64" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK64" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="AL64" s="5" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="AM64" s="5" t="inlineStr">
+        <is>
+          <t>Card_Scene_1</t>
+        </is>
+      </c>
+      <c r="AN64" s="5" t="n">
+        <v>300200002</v>
+      </c>
+      <c r="AR64" s="5" t="n">
+        <v>900002</v>
       </c>
       <c r="AT64" s="0" t="inlineStr">
         <is>
@@ -8176,7 +8238,7 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>989997</v>
+        <v>989996</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
@@ -8224,7 +8286,7 @@
         <v>10</v>
       </c>
       <c r="AJ65" s="0" t="n">
-        <v>989997</v>
+        <v>989996</v>
       </c>
       <c r="AK65" s="0" t="n"/>
       <c r="AL65" s="0" t="n"/>
@@ -8244,7 +8306,7 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>989998</v>
+        <v>989997</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
@@ -8292,7 +8354,7 @@
         <v>10</v>
       </c>
       <c r="AJ66" s="0" t="n">
-        <v>989998</v>
+        <v>989997</v>
       </c>
       <c r="AK66" s="0" t="n"/>
       <c r="AL66" s="0" t="n"/>
@@ -8312,7 +8374,7 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>989999</v>
+        <v>989998</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
@@ -8360,8 +8422,10 @@
         <v>10</v>
       </c>
       <c r="AJ67" s="0" t="n">
-        <v>989999</v>
-      </c>
+        <v>989998</v>
+      </c>
+      <c r="AK67" s="0" t="n"/>
+      <c r="AL67" s="0" t="n"/>
       <c r="AM67" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -8378,7 +8442,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>999947</v>
+        <v>989999</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
@@ -8426,10 +8490,8 @@
         <v>10</v>
       </c>
       <c r="AJ68" s="0" t="n">
-        <v>999947</v>
-      </c>
-      <c r="AK68" s="0" t="n"/>
-      <c r="AL68" s="0" t="n"/>
+        <v>989999</v>
+      </c>
       <c r="AM68" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -8446,7 +8508,7 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>999948</v>
+        <v>999947</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
@@ -8494,7 +8556,7 @@
         <v>10</v>
       </c>
       <c r="AJ69" s="0" t="n">
-        <v>999948</v>
+        <v>999947</v>
       </c>
       <c r="AK69" s="0" t="n"/>
       <c r="AL69" s="0" t="n"/>
@@ -8514,7 +8576,7 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>999949</v>
+        <v>999948</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
@@ -8562,7 +8624,7 @@
         <v>10</v>
       </c>
       <c r="AJ70" s="0" t="n">
-        <v>999949</v>
+        <v>999948</v>
       </c>
       <c r="AK70" s="0" t="n"/>
       <c r="AL70" s="0" t="n"/>
@@ -8582,7 +8644,7 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>999950</v>
+        <v>999949</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
@@ -8630,7 +8692,7 @@
         <v>10</v>
       </c>
       <c r="AJ71" s="0" t="n">
-        <v>999950</v>
+        <v>999949</v>
       </c>
       <c r="AK71" s="0" t="n"/>
       <c r="AL71" s="0" t="n"/>
@@ -8650,7 +8712,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>999951</v>
+        <v>999950</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
@@ -8698,7 +8760,7 @@
         <v>10</v>
       </c>
       <c r="AJ72" s="0" t="n">
-        <v>999951</v>
+        <v>999950</v>
       </c>
       <c r="AK72" s="0" t="n"/>
       <c r="AL72" s="0" t="n"/>
@@ -8718,7 +8780,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>999952</v>
+        <v>999951</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
@@ -8766,7 +8828,7 @@
         <v>10</v>
       </c>
       <c r="AJ73" s="0" t="n">
-        <v>999952</v>
+        <v>999951</v>
       </c>
       <c r="AK73" s="0" t="n"/>
       <c r="AL73" s="0" t="n"/>
@@ -8786,7 +8848,7 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>999953</v>
+        <v>999952</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
@@ -8834,7 +8896,7 @@
         <v>10</v>
       </c>
       <c r="AJ74" s="0" t="n">
-        <v>999953</v>
+        <v>999952</v>
       </c>
       <c r="AK74" s="0" t="n"/>
       <c r="AL74" s="0" t="n"/>
@@ -8854,7 +8916,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>999954</v>
+        <v>999953</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
@@ -8902,7 +8964,7 @@
         <v>10</v>
       </c>
       <c r="AJ75" s="0" t="n">
-        <v>999954</v>
+        <v>999953</v>
       </c>
       <c r="AK75" s="0" t="n"/>
       <c r="AL75" s="0" t="n"/>
@@ -8922,7 +8984,7 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>999955</v>
+        <v>999954</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
@@ -8970,7 +9032,7 @@
         <v>10</v>
       </c>
       <c r="AJ76" s="0" t="n">
-        <v>999955</v>
+        <v>999954</v>
       </c>
       <c r="AK76" s="0" t="n"/>
       <c r="AL76" s="0" t="n"/>
@@ -8990,7 +9052,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>999956</v>
+        <v>999955</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
@@ -9038,7 +9100,7 @@
         <v>10</v>
       </c>
       <c r="AJ77" s="0" t="n">
-        <v>999956</v>
+        <v>999955</v>
       </c>
       <c r="AK77" s="0" t="n"/>
       <c r="AL77" s="0" t="n"/>
@@ -9058,7 +9120,7 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>999957</v>
+        <v>999956</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
@@ -9106,7 +9168,7 @@
         <v>10</v>
       </c>
       <c r="AJ78" s="0" t="n">
-        <v>999957</v>
+        <v>999956</v>
       </c>
       <c r="AK78" s="0" t="n"/>
       <c r="AL78" s="0" t="n"/>
@@ -9126,7 +9188,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>999958</v>
+        <v>999957</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
@@ -9174,7 +9236,7 @@
         <v>10</v>
       </c>
       <c r="AJ79" s="0" t="n">
-        <v>999958</v>
+        <v>999957</v>
       </c>
       <c r="AK79" s="0" t="n"/>
       <c r="AL79" s="0" t="n"/>
@@ -9194,7 +9256,7 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>999959</v>
+        <v>999958</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
@@ -9242,7 +9304,7 @@
         <v>10</v>
       </c>
       <c r="AJ80" s="0" t="n">
-        <v>999959</v>
+        <v>999958</v>
       </c>
       <c r="AK80" s="0" t="n"/>
       <c r="AL80" s="0" t="n"/>
@@ -9262,7 +9324,7 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>999960</v>
+        <v>999959</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
@@ -9310,7 +9372,7 @@
         <v>10</v>
       </c>
       <c r="AJ81" s="0" t="n">
-        <v>999960</v>
+        <v>999959</v>
       </c>
       <c r="AK81" s="0" t="n"/>
       <c r="AL81" s="0" t="n"/>
@@ -9330,7 +9392,7 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>999961</v>
+        <v>999960</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
@@ -9378,7 +9440,7 @@
         <v>10</v>
       </c>
       <c r="AJ82" s="0" t="n">
-        <v>999961</v>
+        <v>999960</v>
       </c>
       <c r="AK82" s="0" t="n"/>
       <c r="AL82" s="0" t="n"/>
@@ -9398,7 +9460,7 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>999962</v>
+        <v>999961</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
@@ -9446,7 +9508,7 @@
         <v>10</v>
       </c>
       <c r="AJ83" s="0" t="n">
-        <v>999962</v>
+        <v>999961</v>
       </c>
       <c r="AK83" s="0" t="n"/>
       <c r="AL83" s="0" t="n"/>
@@ -9466,7 +9528,7 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>999963</v>
+        <v>999962</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
@@ -9514,7 +9576,7 @@
         <v>10</v>
       </c>
       <c r="AJ84" s="0" t="n">
-        <v>999963</v>
+        <v>999962</v>
       </c>
       <c r="AK84" s="0" t="n"/>
       <c r="AL84" s="0" t="n"/>
@@ -9534,7 +9596,7 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>999964</v>
+        <v>999963</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
@@ -9582,7 +9644,7 @@
         <v>10</v>
       </c>
       <c r="AJ85" s="0" t="n">
-        <v>999964</v>
+        <v>999963</v>
       </c>
       <c r="AK85" s="0" t="n"/>
       <c r="AL85" s="0" t="n"/>
@@ -9602,7 +9664,7 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>999965</v>
+        <v>999964</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
@@ -9650,7 +9712,7 @@
         <v>10</v>
       </c>
       <c r="AJ86" s="0" t="n">
-        <v>999965</v>
+        <v>999964</v>
       </c>
       <c r="AK86" s="0" t="n"/>
       <c r="AL86" s="0" t="n"/>
@@ -9670,7 +9732,7 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>999966</v>
+        <v>999965</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
@@ -9718,7 +9780,7 @@
         <v>10</v>
       </c>
       <c r="AJ87" s="0" t="n">
-        <v>999966</v>
+        <v>999965</v>
       </c>
       <c r="AK87" s="0" t="n"/>
       <c r="AL87" s="0" t="n"/>
@@ -9738,7 +9800,7 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>999967</v>
+        <v>999966</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
@@ -9786,7 +9848,7 @@
         <v>10</v>
       </c>
       <c r="AJ88" s="0" t="n">
-        <v>999967</v>
+        <v>999966</v>
       </c>
       <c r="AK88" s="0" t="n"/>
       <c r="AL88" s="0" t="n"/>
@@ -9806,7 +9868,7 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>999968</v>
+        <v>999967</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
@@ -9854,7 +9916,7 @@
         <v>10</v>
       </c>
       <c r="AJ89" s="0" t="n">
-        <v>999968</v>
+        <v>999967</v>
       </c>
       <c r="AK89" s="0" t="n"/>
       <c r="AL89" s="0" t="n"/>
@@ -9874,7 +9936,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>999969</v>
+        <v>999968</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
@@ -9922,7 +9984,7 @@
         <v>10</v>
       </c>
       <c r="AJ90" s="0" t="n">
-        <v>999969</v>
+        <v>999968</v>
       </c>
       <c r="AK90" s="0" t="n"/>
       <c r="AL90" s="0" t="n"/>
@@ -9942,7 +10004,7 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>999970</v>
+        <v>999969</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
@@ -9990,7 +10052,7 @@
         <v>10</v>
       </c>
       <c r="AJ91" s="0" t="n">
-        <v>999970</v>
+        <v>999969</v>
       </c>
       <c r="AK91" s="0" t="n"/>
       <c r="AL91" s="0" t="n"/>
@@ -10010,7 +10072,7 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>999971</v>
+        <v>999970</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
@@ -10058,7 +10120,7 @@
         <v>10</v>
       </c>
       <c r="AJ92" s="0" t="n">
-        <v>999971</v>
+        <v>999970</v>
       </c>
       <c r="AK92" s="0" t="n"/>
       <c r="AL92" s="0" t="n"/>
@@ -10078,7 +10140,7 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>999972</v>
+        <v>999971</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
@@ -10126,7 +10188,7 @@
         <v>10</v>
       </c>
       <c r="AJ93" s="0" t="n">
-        <v>999972</v>
+        <v>999971</v>
       </c>
       <c r="AK93" s="0" t="n"/>
       <c r="AL93" s="0" t="n"/>
@@ -10146,7 +10208,7 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>999973</v>
+        <v>999972</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
@@ -10194,7 +10256,7 @@
         <v>10</v>
       </c>
       <c r="AJ94" s="0" t="n">
-        <v>999973</v>
+        <v>999972</v>
       </c>
       <c r="AK94" s="0" t="n"/>
       <c r="AL94" s="0" t="n"/>
@@ -10214,7 +10276,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>999974</v>
+        <v>999973</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
@@ -10262,7 +10324,7 @@
         <v>10</v>
       </c>
       <c r="AJ95" s="0" t="n">
-        <v>999974</v>
+        <v>999973</v>
       </c>
       <c r="AK95" s="0" t="n"/>
       <c r="AL95" s="0" t="n"/>
@@ -10282,7 +10344,7 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>999975</v>
+        <v>999974</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
@@ -10330,7 +10392,7 @@
         <v>10</v>
       </c>
       <c r="AJ96" s="0" t="n">
-        <v>999975</v>
+        <v>999974</v>
       </c>
       <c r="AK96" s="0" t="n"/>
       <c r="AL96" s="0" t="n"/>
@@ -10350,7 +10412,7 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>999976</v>
+        <v>999975</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
@@ -10398,7 +10460,7 @@
         <v>10</v>
       </c>
       <c r="AJ97" s="0" t="n">
-        <v>999976</v>
+        <v>999975</v>
       </c>
       <c r="AK97" s="0" t="n"/>
       <c r="AL97" s="0" t="n"/>
@@ -10418,7 +10480,7 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>999977</v>
+        <v>999976</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
@@ -10466,7 +10528,7 @@
         <v>10</v>
       </c>
       <c r="AJ98" s="0" t="n">
-        <v>999977</v>
+        <v>999976</v>
       </c>
       <c r="AK98" s="0" t="n"/>
       <c r="AL98" s="0" t="n"/>
@@ -10486,7 +10548,7 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>999978</v>
+        <v>999977</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
@@ -10534,7 +10596,7 @@
         <v>10</v>
       </c>
       <c r="AJ99" s="0" t="n">
-        <v>999978</v>
+        <v>999977</v>
       </c>
       <c r="AK99" s="0" t="n"/>
       <c r="AL99" s="0" t="n"/>
@@ -10554,7 +10616,7 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>999979</v>
+        <v>999978</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
@@ -10602,7 +10664,7 @@
         <v>10</v>
       </c>
       <c r="AJ100" s="0" t="n">
-        <v>999979</v>
+        <v>999978</v>
       </c>
       <c r="AK100" s="0" t="n"/>
       <c r="AL100" s="0" t="n"/>
@@ -10622,7 +10684,7 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>999980</v>
+        <v>999979</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
@@ -10670,7 +10732,7 @@
         <v>10</v>
       </c>
       <c r="AJ101" s="0" t="n">
-        <v>999980</v>
+        <v>999979</v>
       </c>
       <c r="AK101" s="0" t="n"/>
       <c r="AL101" s="0" t="n"/>
@@ -10690,7 +10752,7 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>999981</v>
+        <v>999980</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
@@ -10738,7 +10800,7 @@
         <v>10</v>
       </c>
       <c r="AJ102" s="0" t="n">
-        <v>999981</v>
+        <v>999980</v>
       </c>
       <c r="AK102" s="0" t="n"/>
       <c r="AL102" s="0" t="n"/>
@@ -10758,7 +10820,7 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>999982</v>
+        <v>999981</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
@@ -10792,6 +10854,7 @@
       <c r="Y103" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="Z103" s="0" t="n"/>
       <c r="AB103" s="0" t="n">
         <v>100</v>
       </c>
@@ -10805,8 +10868,10 @@
         <v>10</v>
       </c>
       <c r="AJ103" s="0" t="n">
-        <v>999982</v>
-      </c>
+        <v>999981</v>
+      </c>
+      <c r="AK103" s="0" t="n"/>
+      <c r="AL103" s="0" t="n"/>
       <c r="AM103" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -10823,7 +10888,7 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>999983</v>
+        <v>999982</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
@@ -10870,7 +10935,7 @@
         <v>10</v>
       </c>
       <c r="AJ104" s="0" t="n">
-        <v>999983</v>
+        <v>999982</v>
       </c>
       <c r="AM104" s="0" t="inlineStr">
         <is>
@@ -10888,7 +10953,7 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>999984</v>
+        <v>999983</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
@@ -10935,7 +11000,7 @@
         <v>10</v>
       </c>
       <c r="AJ105" s="0" t="n">
-        <v>999984</v>
+        <v>999983</v>
       </c>
       <c r="AM105" s="0" t="inlineStr">
         <is>
@@ -10953,7 +11018,7 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>999985</v>
+        <v>999984</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
@@ -11000,7 +11065,7 @@
         <v>10</v>
       </c>
       <c r="AJ106" s="0" t="n">
-        <v>999985</v>
+        <v>999984</v>
       </c>
       <c r="AM106" s="0" t="inlineStr">
         <is>
@@ -11018,7 +11083,7 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>999986</v>
+        <v>999985</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
@@ -11065,7 +11130,7 @@
         <v>10</v>
       </c>
       <c r="AJ107" s="0" t="n">
-        <v>999986</v>
+        <v>999985</v>
       </c>
       <c r="AM107" s="0" t="inlineStr">
         <is>
@@ -11083,7 +11148,7 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>999987</v>
+        <v>999986</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
@@ -11130,7 +11195,7 @@
         <v>10</v>
       </c>
       <c r="AJ108" s="0" t="n">
-        <v>999987</v>
+        <v>999986</v>
       </c>
       <c r="AM108" s="0" t="inlineStr">
         <is>
@@ -11148,7 +11213,7 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>999988</v>
+        <v>999987</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
@@ -11195,7 +11260,7 @@
         <v>10</v>
       </c>
       <c r="AJ109" s="0" t="n">
-        <v>999988</v>
+        <v>999987</v>
       </c>
       <c r="AM109" s="0" t="inlineStr">
         <is>
@@ -11213,7 +11278,7 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>999989</v>
+        <v>999988</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
@@ -11260,7 +11325,7 @@
         <v>10</v>
       </c>
       <c r="AJ110" s="0" t="n">
-        <v>999989</v>
+        <v>999988</v>
       </c>
       <c r="AM110" s="0" t="inlineStr">
         <is>
@@ -11278,7 +11343,7 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>999990</v>
+        <v>999989</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
@@ -11325,7 +11390,7 @@
         <v>10</v>
       </c>
       <c r="AJ111" s="0" t="n">
-        <v>999990</v>
+        <v>999989</v>
       </c>
       <c r="AM111" s="0" t="inlineStr">
         <is>
@@ -11343,7 +11408,7 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>999991</v>
+        <v>999990</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
@@ -11390,7 +11455,7 @@
         <v>10</v>
       </c>
       <c r="AJ112" s="0" t="n">
-        <v>999991</v>
+        <v>999990</v>
       </c>
       <c r="AM112" s="0" t="inlineStr">
         <is>
@@ -11408,7 +11473,7 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>999992</v>
+        <v>999991</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
@@ -11455,7 +11520,7 @@
         <v>10</v>
       </c>
       <c r="AJ113" s="0" t="n">
-        <v>999992</v>
+        <v>999991</v>
       </c>
       <c r="AM113" s="0" t="inlineStr">
         <is>
@@ -11473,7 +11538,7 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>999993</v>
+        <v>999992</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
@@ -11520,7 +11585,7 @@
         <v>10</v>
       </c>
       <c r="AJ114" s="0" t="n">
-        <v>999993</v>
+        <v>999992</v>
       </c>
       <c r="AM114" s="0" t="inlineStr">
         <is>
@@ -11538,7 +11603,7 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>999994</v>
+        <v>999993</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
@@ -11585,7 +11650,7 @@
         <v>10</v>
       </c>
       <c r="AJ115" s="0" t="n">
-        <v>999994</v>
+        <v>999993</v>
       </c>
       <c r="AM115" s="0" t="inlineStr">
         <is>
@@ -11603,7 +11668,7 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>999995</v>
+        <v>999994</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
@@ -11650,7 +11715,7 @@
         <v>10</v>
       </c>
       <c r="AJ116" s="0" t="n">
-        <v>999995</v>
+        <v>999994</v>
       </c>
       <c r="AM116" s="0" t="inlineStr">
         <is>
@@ -11668,7 +11733,7 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>999996</v>
+        <v>999995</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
@@ -11715,7 +11780,7 @@
         <v>10</v>
       </c>
       <c r="AJ117" s="0" t="n">
-        <v>999996</v>
+        <v>999995</v>
       </c>
       <c r="AM117" s="0" t="inlineStr">
         <is>
@@ -11733,7 +11798,7 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>999997</v>
+        <v>999996</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
@@ -11780,7 +11845,7 @@
         <v>10</v>
       </c>
       <c r="AJ118" s="0" t="n">
-        <v>999997</v>
+        <v>999996</v>
       </c>
       <c r="AM118" s="0" t="inlineStr">
         <is>
@@ -11798,7 +11863,7 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>999998</v>
+        <v>999997</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
@@ -11845,7 +11910,7 @@
         <v>10</v>
       </c>
       <c r="AJ119" s="0" t="n">
-        <v>999998</v>
+        <v>999997</v>
       </c>
       <c r="AM119" s="0" t="inlineStr">
         <is>
@@ -11863,7 +11928,7 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>999999</v>
+        <v>999998</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
@@ -11910,17 +11975,82 @@
         <v>10</v>
       </c>
       <c r="AJ120" s="0" t="n">
+        <v>999998</v>
+      </c>
+      <c r="AM120" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_4</t>
+        </is>
+      </c>
+      <c r="AR120" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT120" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="n">
         <v>999999</v>
       </c>
-      <c r="AM120" s="0" t="inlineStr">
+      <c r="B121" s="0" t="inlineStr">
+        <is>
+          <t>测试数据</t>
+        </is>
+      </c>
+      <c r="C121" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P121" s="0" t="n">
+        <v>200001</v>
+      </c>
+      <c r="S121" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="T121" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="U121" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V121" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X121" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y121" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB121" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE121" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG121" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ121" s="0" t="n">
+        <v>999999</v>
+      </c>
+      <c r="AM121" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AR120" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT120" s="0" t="inlineStr">
+      <c r="AR121" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT121" s="0" t="inlineStr">
         <is>
           <t>1,3,4,6</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -1080,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT121"/>
+  <dimension ref="A1:AT122"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="7.375" customWidth="1" style="3" min="1" max="1"/>
@@ -7382,130 +7382,130 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57" s="0" t="n">
         <v>103108</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="0" t="inlineStr">
         <is>
           <t>人类-牧师</t>
         </is>
       </c>
-      <c r="C57" t="n">
-        <v>2</v>
-      </c>
-      <c r="G57" t="n">
+      <c r="C57" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" s="0" t="n">
         <v>1000001</v>
       </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="inlineStr">
+      <c r="H57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="0" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
-      <c r="N57" t="inlineStr">
+      <c r="J57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" s="0" t="inlineStr">
         <is>
           <t>Attack2</t>
         </is>
       </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
+      <c r="O57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="0" t="n">
         <v>102003</v>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="Q57" s="0" t="inlineStr">
         <is>
           <t>0,0.6,0</t>
         </is>
       </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>1</v>
-      </c>
-      <c r="T57" t="n">
+      <c r="R57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="U57" t="n">
-        <v>1</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB57" t="n">
+      <c r="U57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X57" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y57" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="AC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK57" t="n">
+      <c r="AC57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK57" s="0" t="n">
         <v>1000001</v>
       </c>
-      <c r="AL57" t="inlineStr">
+      <c r="AL57" s="0" t="inlineStr">
         <is>
           <t>ui_class_5</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
+      <c r="AM57" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_2</t>
         </is>
       </c>
-      <c r="AN57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR57" t="n">
+      <c r="AN57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR57" s="0" t="n">
         <v>103108</v>
       </c>
-      <c r="AS57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr">
+      <c r="AS57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT57" s="0" t="inlineStr">
         <is>
           <t>1,3,4,6</t>
         </is>
@@ -8001,118 +8001,102 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
-        <v>900001</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>测试骷髅战士</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="n"/>
-      <c r="G63" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>21010001</v>
-      </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="A63" t="n">
+        <v>104104</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>人类-大剑战士-勇者</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2000100001,</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="I63" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J63" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K63" s="5" t="n"/>
-      <c r="L63" s="5" t="n"/>
-      <c r="M63" s="5" t="n"/>
-      <c r="N63" s="5" t="inlineStr">
-        <is>
-          <t>Attack2</t>
-        </is>
-      </c>
-      <c r="O63" s="5" t="n"/>
-      <c r="P63" s="5" t="n">
-        <v>100001</v>
-      </c>
-      <c r="Q63" s="0" t="inlineStr">
+      <c r="J63" t="n">
+        <v>3</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Attack8</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>101007</v>
+      </c>
+      <c r="Q63" t="inlineStr">
         <is>
           <t>0,0.5,0</t>
         </is>
       </c>
-      <c r="R63" s="5" t="n"/>
-      <c r="S63" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T63" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X63" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y63" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA63" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB63" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AC63" s="5" t="n"/>
-      <c r="AD63" s="5" t="n"/>
-      <c r="AE63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF63" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG63" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH63" s="5" t="n"/>
-      <c r="AI63" s="5" t="n"/>
-      <c r="AJ63" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK63" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="AL63" s="5" t="inlineStr">
-        <is>
-          <t>ui_class_3</t>
-        </is>
-      </c>
-      <c r="AM63" s="5" t="inlineStr">
-        <is>
-          <t>Card_Scene_1</t>
-        </is>
-      </c>
-      <c r="AN63" s="5" t="n">
-        <v>300200001</v>
-      </c>
-      <c r="AR63" s="5" t="n">
-        <v>900001</v>
-      </c>
-      <c r="AT63" s="0" t="inlineStr">
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>ui_class_7</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Card_Scene_2</t>
+        </is>
+      </c>
+      <c r="AR63" t="n">
+        <v>104101</v>
+      </c>
+      <c r="AT63" t="inlineStr">
         <is>
           <t>1,3,4,6</t>
         </is>
@@ -8120,11 +8104,11 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
-        <v>900002</v>
+        <v>900001</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>测试骷髅投手</t>
+          <t>测试骷髅战士</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
@@ -8137,7 +8121,7 @@
         <v>2000001</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>21000001</v>
+        <v>21010001</v>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
@@ -8145,23 +8129,23 @@
         </is>
       </c>
       <c r="J64" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K64" s="5" t="n"/>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="5" t="n"/>
       <c r="N64" s="5" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Attack2</t>
         </is>
       </c>
       <c r="O64" s="5" t="n"/>
       <c r="P64" s="5" t="n">
-        <v>200001</v>
-      </c>
-      <c r="Q64" s="5" t="inlineStr">
-        <is>
-          <t>0,0.7,0</t>
+        <v>100001</v>
+      </c>
+      <c r="Q64" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
         </is>
       </c>
       <c r="R64" s="5" t="n"/>
@@ -8169,7 +8153,7 @@
         <v>2</v>
       </c>
       <c r="T64" s="5" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="U64" s="5" t="n">
         <v>1</v>
@@ -8187,7 +8171,7 @@
         <v>0.5</v>
       </c>
       <c r="Z64" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA64" s="5" t="n">
         <v>10</v>
@@ -8216,7 +8200,7 @@
       </c>
       <c r="AL64" s="5" t="inlineStr">
         <is>
-          <t>ui_class_6</t>
+          <t>ui_class_3</t>
         </is>
       </c>
       <c r="AM64" s="5" t="inlineStr">
@@ -8225,10 +8209,10 @@
         </is>
       </c>
       <c r="AN64" s="5" t="n">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="AR64" s="5" t="n">
-        <v>900002</v>
+        <v>900001</v>
       </c>
       <c r="AT64" s="0" t="inlineStr">
         <is>
@@ -8237,47 +8221,86 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="0" t="n">
-        <v>989996</v>
-      </c>
-      <c r="B65" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C65" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" s="0" t="n">
+      <c r="A65" s="5" t="n">
+        <v>900002</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>测试骷髅投手</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>21000001</v>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>1,2,3,10,</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="O65" s="5" t="n"/>
+      <c r="P65" s="5" t="n">
         <v>200001</v>
       </c>
-      <c r="S65" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T65" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U65" s="0" t="n">
+      <c r="Q65" s="5" t="inlineStr">
+        <is>
+          <t>0,0.7,0</t>
+        </is>
+      </c>
+      <c r="R65" s="5" t="n"/>
+      <c r="S65" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T65" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="U65" s="5" t="n">
         <v>1</v>
       </c>
       <c r="V65" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W65" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X65" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y65" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z65" s="0" t="n"/>
-      <c r="AB65" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE65" s="0" t="n">
-        <v>35</v>
+      <c r="W65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X65" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y65" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z65" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA65" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB65" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AC65" s="5" t="n"/>
+      <c r="AD65" s="5" t="n"/>
+      <c r="AE65" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AF65" s="1" t="n">
         <v>0</v>
@@ -8285,18 +8308,29 @@
       <c r="AG65" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AJ65" s="0" t="n">
-        <v>989996</v>
-      </c>
-      <c r="AK65" s="0" t="n"/>
-      <c r="AL65" s="0" t="n"/>
-      <c r="AM65" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR65" s="0" t="n">
-        <v>1</v>
+      <c r="AH65" s="5" t="n"/>
+      <c r="AI65" s="5" t="n"/>
+      <c r="AJ65" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK65" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="AL65" s="5" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="AM65" s="5" t="inlineStr">
+        <is>
+          <t>Card_Scene_1</t>
+        </is>
+      </c>
+      <c r="AN65" s="5" t="n">
+        <v>300200002</v>
+      </c>
+      <c r="AR65" s="5" t="n">
+        <v>900002</v>
       </c>
       <c r="AT65" s="0" t="inlineStr">
         <is>
@@ -8306,7 +8340,7 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>989997</v>
+        <v>989996</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
@@ -8354,7 +8388,7 @@
         <v>10</v>
       </c>
       <c r="AJ66" s="0" t="n">
-        <v>989997</v>
+        <v>989996</v>
       </c>
       <c r="AK66" s="0" t="n"/>
       <c r="AL66" s="0" t="n"/>
@@ -8374,7 +8408,7 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>989998</v>
+        <v>989997</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
@@ -8422,7 +8456,7 @@
         <v>10</v>
       </c>
       <c r="AJ67" s="0" t="n">
-        <v>989998</v>
+        <v>989997</v>
       </c>
       <c r="AK67" s="0" t="n"/>
       <c r="AL67" s="0" t="n"/>
@@ -8442,7 +8476,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>989999</v>
+        <v>989998</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
@@ -8490,8 +8524,10 @@
         <v>10</v>
       </c>
       <c r="AJ68" s="0" t="n">
-        <v>989999</v>
-      </c>
+        <v>989998</v>
+      </c>
+      <c r="AK68" s="0" t="n"/>
+      <c r="AL68" s="0" t="n"/>
       <c r="AM68" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -8508,7 +8544,7 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>999947</v>
+        <v>989999</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
@@ -8556,10 +8592,8 @@
         <v>10</v>
       </c>
       <c r="AJ69" s="0" t="n">
-        <v>999947</v>
-      </c>
-      <c r="AK69" s="0" t="n"/>
-      <c r="AL69" s="0" t="n"/>
+        <v>989999</v>
+      </c>
       <c r="AM69" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -8576,7 +8610,7 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>999948</v>
+        <v>999947</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
@@ -8624,7 +8658,7 @@
         <v>10</v>
       </c>
       <c r="AJ70" s="0" t="n">
-        <v>999948</v>
+        <v>999947</v>
       </c>
       <c r="AK70" s="0" t="n"/>
       <c r="AL70" s="0" t="n"/>
@@ -8644,7 +8678,7 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>999949</v>
+        <v>999948</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
@@ -8692,7 +8726,7 @@
         <v>10</v>
       </c>
       <c r="AJ71" s="0" t="n">
-        <v>999949</v>
+        <v>999948</v>
       </c>
       <c r="AK71" s="0" t="n"/>
       <c r="AL71" s="0" t="n"/>
@@ -8712,7 +8746,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>999950</v>
+        <v>999949</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
@@ -8760,7 +8794,7 @@
         <v>10</v>
       </c>
       <c r="AJ72" s="0" t="n">
-        <v>999950</v>
+        <v>999949</v>
       </c>
       <c r="AK72" s="0" t="n"/>
       <c r="AL72" s="0" t="n"/>
@@ -8780,7 +8814,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>999951</v>
+        <v>999950</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
@@ -8828,7 +8862,7 @@
         <v>10</v>
       </c>
       <c r="AJ73" s="0" t="n">
-        <v>999951</v>
+        <v>999950</v>
       </c>
       <c r="AK73" s="0" t="n"/>
       <c r="AL73" s="0" t="n"/>
@@ -8848,7 +8882,7 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>999952</v>
+        <v>999951</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
@@ -8896,7 +8930,7 @@
         <v>10</v>
       </c>
       <c r="AJ74" s="0" t="n">
-        <v>999952</v>
+        <v>999951</v>
       </c>
       <c r="AK74" s="0" t="n"/>
       <c r="AL74" s="0" t="n"/>
@@ -8916,7 +8950,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>999953</v>
+        <v>999952</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
@@ -8964,7 +8998,7 @@
         <v>10</v>
       </c>
       <c r="AJ75" s="0" t="n">
-        <v>999953</v>
+        <v>999952</v>
       </c>
       <c r="AK75" s="0" t="n"/>
       <c r="AL75" s="0" t="n"/>
@@ -8984,7 +9018,7 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>999954</v>
+        <v>999953</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
@@ -9032,7 +9066,7 @@
         <v>10</v>
       </c>
       <c r="AJ76" s="0" t="n">
-        <v>999954</v>
+        <v>999953</v>
       </c>
       <c r="AK76" s="0" t="n"/>
       <c r="AL76" s="0" t="n"/>
@@ -9052,7 +9086,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>999955</v>
+        <v>999954</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
@@ -9100,7 +9134,7 @@
         <v>10</v>
       </c>
       <c r="AJ77" s="0" t="n">
-        <v>999955</v>
+        <v>999954</v>
       </c>
       <c r="AK77" s="0" t="n"/>
       <c r="AL77" s="0" t="n"/>
@@ -9120,7 +9154,7 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>999956</v>
+        <v>999955</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
@@ -9168,7 +9202,7 @@
         <v>10</v>
       </c>
       <c r="AJ78" s="0" t="n">
-        <v>999956</v>
+        <v>999955</v>
       </c>
       <c r="AK78" s="0" t="n"/>
       <c r="AL78" s="0" t="n"/>
@@ -9188,7 +9222,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>999957</v>
+        <v>999956</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
@@ -9236,7 +9270,7 @@
         <v>10</v>
       </c>
       <c r="AJ79" s="0" t="n">
-        <v>999957</v>
+        <v>999956</v>
       </c>
       <c r="AK79" s="0" t="n"/>
       <c r="AL79" s="0" t="n"/>
@@ -9256,7 +9290,7 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>999958</v>
+        <v>999957</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
@@ -9304,7 +9338,7 @@
         <v>10</v>
       </c>
       <c r="AJ80" s="0" t="n">
-        <v>999958</v>
+        <v>999957</v>
       </c>
       <c r="AK80" s="0" t="n"/>
       <c r="AL80" s="0" t="n"/>
@@ -9324,7 +9358,7 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>999959</v>
+        <v>999958</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
@@ -9372,7 +9406,7 @@
         <v>10</v>
       </c>
       <c r="AJ81" s="0" t="n">
-        <v>999959</v>
+        <v>999958</v>
       </c>
       <c r="AK81" s="0" t="n"/>
       <c r="AL81" s="0" t="n"/>
@@ -9392,7 +9426,7 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>999960</v>
+        <v>999959</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
@@ -9440,7 +9474,7 @@
         <v>10</v>
       </c>
       <c r="AJ82" s="0" t="n">
-        <v>999960</v>
+        <v>999959</v>
       </c>
       <c r="AK82" s="0" t="n"/>
       <c r="AL82" s="0" t="n"/>
@@ -9460,7 +9494,7 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>999961</v>
+        <v>999960</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
@@ -9508,7 +9542,7 @@
         <v>10</v>
       </c>
       <c r="AJ83" s="0" t="n">
-        <v>999961</v>
+        <v>999960</v>
       </c>
       <c r="AK83" s="0" t="n"/>
       <c r="AL83" s="0" t="n"/>
@@ -9528,7 +9562,7 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>999962</v>
+        <v>999961</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
@@ -9576,7 +9610,7 @@
         <v>10</v>
       </c>
       <c r="AJ84" s="0" t="n">
-        <v>999962</v>
+        <v>999961</v>
       </c>
       <c r="AK84" s="0" t="n"/>
       <c r="AL84" s="0" t="n"/>
@@ -9596,7 +9630,7 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>999963</v>
+        <v>999962</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
@@ -9644,7 +9678,7 @@
         <v>10</v>
       </c>
       <c r="AJ85" s="0" t="n">
-        <v>999963</v>
+        <v>999962</v>
       </c>
       <c r="AK85" s="0" t="n"/>
       <c r="AL85" s="0" t="n"/>
@@ -9664,7 +9698,7 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>999964</v>
+        <v>999963</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
@@ -9712,7 +9746,7 @@
         <v>10</v>
       </c>
       <c r="AJ86" s="0" t="n">
-        <v>999964</v>
+        <v>999963</v>
       </c>
       <c r="AK86" s="0" t="n"/>
       <c r="AL86" s="0" t="n"/>
@@ -9732,7 +9766,7 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>999965</v>
+        <v>999964</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
@@ -9780,7 +9814,7 @@
         <v>10</v>
       </c>
       <c r="AJ87" s="0" t="n">
-        <v>999965</v>
+        <v>999964</v>
       </c>
       <c r="AK87" s="0" t="n"/>
       <c r="AL87" s="0" t="n"/>
@@ -9800,7 +9834,7 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>999966</v>
+        <v>999965</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
@@ -9848,7 +9882,7 @@
         <v>10</v>
       </c>
       <c r="AJ88" s="0" t="n">
-        <v>999966</v>
+        <v>999965</v>
       </c>
       <c r="AK88" s="0" t="n"/>
       <c r="AL88" s="0" t="n"/>
@@ -9868,7 +9902,7 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>999967</v>
+        <v>999966</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
@@ -9916,7 +9950,7 @@
         <v>10</v>
       </c>
       <c r="AJ89" s="0" t="n">
-        <v>999967</v>
+        <v>999966</v>
       </c>
       <c r="AK89" s="0" t="n"/>
       <c r="AL89" s="0" t="n"/>
@@ -9936,7 +9970,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>999968</v>
+        <v>999967</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
@@ -9984,7 +10018,7 @@
         <v>10</v>
       </c>
       <c r="AJ90" s="0" t="n">
-        <v>999968</v>
+        <v>999967</v>
       </c>
       <c r="AK90" s="0" t="n"/>
       <c r="AL90" s="0" t="n"/>
@@ -10004,7 +10038,7 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>999969</v>
+        <v>999968</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
@@ -10052,7 +10086,7 @@
         <v>10</v>
       </c>
       <c r="AJ91" s="0" t="n">
-        <v>999969</v>
+        <v>999968</v>
       </c>
       <c r="AK91" s="0" t="n"/>
       <c r="AL91" s="0" t="n"/>
@@ -10072,7 +10106,7 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>999970</v>
+        <v>999969</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
@@ -10120,7 +10154,7 @@
         <v>10</v>
       </c>
       <c r="AJ92" s="0" t="n">
-        <v>999970</v>
+        <v>999969</v>
       </c>
       <c r="AK92" s="0" t="n"/>
       <c r="AL92" s="0" t="n"/>
@@ -10140,7 +10174,7 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>999971</v>
+        <v>999970</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
@@ -10188,7 +10222,7 @@
         <v>10</v>
       </c>
       <c r="AJ93" s="0" t="n">
-        <v>999971</v>
+        <v>999970</v>
       </c>
       <c r="AK93" s="0" t="n"/>
       <c r="AL93" s="0" t="n"/>
@@ -10208,7 +10242,7 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>999972</v>
+        <v>999971</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
@@ -10256,7 +10290,7 @@
         <v>10</v>
       </c>
       <c r="AJ94" s="0" t="n">
-        <v>999972</v>
+        <v>999971</v>
       </c>
       <c r="AK94" s="0" t="n"/>
       <c r="AL94" s="0" t="n"/>
@@ -10276,7 +10310,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>999973</v>
+        <v>999972</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
@@ -10324,7 +10358,7 @@
         <v>10</v>
       </c>
       <c r="AJ95" s="0" t="n">
-        <v>999973</v>
+        <v>999972</v>
       </c>
       <c r="AK95" s="0" t="n"/>
       <c r="AL95" s="0" t="n"/>
@@ -10344,7 +10378,7 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>999974</v>
+        <v>999973</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
@@ -10392,7 +10426,7 @@
         <v>10</v>
       </c>
       <c r="AJ96" s="0" t="n">
-        <v>999974</v>
+        <v>999973</v>
       </c>
       <c r="AK96" s="0" t="n"/>
       <c r="AL96" s="0" t="n"/>
@@ -10412,7 +10446,7 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>999975</v>
+        <v>999974</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
@@ -10460,7 +10494,7 @@
         <v>10</v>
       </c>
       <c r="AJ97" s="0" t="n">
-        <v>999975</v>
+        <v>999974</v>
       </c>
       <c r="AK97" s="0" t="n"/>
       <c r="AL97" s="0" t="n"/>
@@ -10480,7 +10514,7 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>999976</v>
+        <v>999975</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
@@ -10528,7 +10562,7 @@
         <v>10</v>
       </c>
       <c r="AJ98" s="0" t="n">
-        <v>999976</v>
+        <v>999975</v>
       </c>
       <c r="AK98" s="0" t="n"/>
       <c r="AL98" s="0" t="n"/>
@@ -10548,7 +10582,7 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>999977</v>
+        <v>999976</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
@@ -10596,7 +10630,7 @@
         <v>10</v>
       </c>
       <c r="AJ99" s="0" t="n">
-        <v>999977</v>
+        <v>999976</v>
       </c>
       <c r="AK99" s="0" t="n"/>
       <c r="AL99" s="0" t="n"/>
@@ -10616,7 +10650,7 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>999978</v>
+        <v>999977</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
@@ -10664,7 +10698,7 @@
         <v>10</v>
       </c>
       <c r="AJ100" s="0" t="n">
-        <v>999978</v>
+        <v>999977</v>
       </c>
       <c r="AK100" s="0" t="n"/>
       <c r="AL100" s="0" t="n"/>
@@ -10684,7 +10718,7 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>999979</v>
+        <v>999978</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
@@ -10732,7 +10766,7 @@
         <v>10</v>
       </c>
       <c r="AJ101" s="0" t="n">
-        <v>999979</v>
+        <v>999978</v>
       </c>
       <c r="AK101" s="0" t="n"/>
       <c r="AL101" s="0" t="n"/>
@@ -10752,7 +10786,7 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>999980</v>
+        <v>999979</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
@@ -10800,7 +10834,7 @@
         <v>10</v>
       </c>
       <c r="AJ102" s="0" t="n">
-        <v>999980</v>
+        <v>999979</v>
       </c>
       <c r="AK102" s="0" t="n"/>
       <c r="AL102" s="0" t="n"/>
@@ -10820,7 +10854,7 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>999981</v>
+        <v>999980</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
@@ -10868,7 +10902,7 @@
         <v>10</v>
       </c>
       <c r="AJ103" s="0" t="n">
-        <v>999981</v>
+        <v>999980</v>
       </c>
       <c r="AK103" s="0" t="n"/>
       <c r="AL103" s="0" t="n"/>
@@ -10888,7 +10922,7 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>999982</v>
+        <v>999981</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
@@ -10922,6 +10956,7 @@
       <c r="Y104" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="Z104" s="0" t="n"/>
       <c r="AB104" s="0" t="n">
         <v>100</v>
       </c>
@@ -10935,8 +10970,10 @@
         <v>10</v>
       </c>
       <c r="AJ104" s="0" t="n">
-        <v>999982</v>
-      </c>
+        <v>999981</v>
+      </c>
+      <c r="AK104" s="0" t="n"/>
+      <c r="AL104" s="0" t="n"/>
       <c r="AM104" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -10953,7 +10990,7 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>999983</v>
+        <v>999982</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
@@ -11000,7 +11037,7 @@
         <v>10</v>
       </c>
       <c r="AJ105" s="0" t="n">
-        <v>999983</v>
+        <v>999982</v>
       </c>
       <c r="AM105" s="0" t="inlineStr">
         <is>
@@ -11018,7 +11055,7 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>999984</v>
+        <v>999983</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
@@ -11065,7 +11102,7 @@
         <v>10</v>
       </c>
       <c r="AJ106" s="0" t="n">
-        <v>999984</v>
+        <v>999983</v>
       </c>
       <c r="AM106" s="0" t="inlineStr">
         <is>
@@ -11083,7 +11120,7 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>999985</v>
+        <v>999984</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
@@ -11130,7 +11167,7 @@
         <v>10</v>
       </c>
       <c r="AJ107" s="0" t="n">
-        <v>999985</v>
+        <v>999984</v>
       </c>
       <c r="AM107" s="0" t="inlineStr">
         <is>
@@ -11148,7 +11185,7 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>999986</v>
+        <v>999985</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
@@ -11195,7 +11232,7 @@
         <v>10</v>
       </c>
       <c r="AJ108" s="0" t="n">
-        <v>999986</v>
+        <v>999985</v>
       </c>
       <c r="AM108" s="0" t="inlineStr">
         <is>
@@ -11213,7 +11250,7 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>999987</v>
+        <v>999986</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
@@ -11260,7 +11297,7 @@
         <v>10</v>
       </c>
       <c r="AJ109" s="0" t="n">
-        <v>999987</v>
+        <v>999986</v>
       </c>
       <c r="AM109" s="0" t="inlineStr">
         <is>
@@ -11278,7 +11315,7 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>999988</v>
+        <v>999987</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
@@ -11325,7 +11362,7 @@
         <v>10</v>
       </c>
       <c r="AJ110" s="0" t="n">
-        <v>999988</v>
+        <v>999987</v>
       </c>
       <c r="AM110" s="0" t="inlineStr">
         <is>
@@ -11343,7 +11380,7 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>999989</v>
+        <v>999988</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
@@ -11390,7 +11427,7 @@
         <v>10</v>
       </c>
       <c r="AJ111" s="0" t="n">
-        <v>999989</v>
+        <v>999988</v>
       </c>
       <c r="AM111" s="0" t="inlineStr">
         <is>
@@ -11408,7 +11445,7 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>999990</v>
+        <v>999989</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
@@ -11455,7 +11492,7 @@
         <v>10</v>
       </c>
       <c r="AJ112" s="0" t="n">
-        <v>999990</v>
+        <v>999989</v>
       </c>
       <c r="AM112" s="0" t="inlineStr">
         <is>
@@ -11473,7 +11510,7 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>999991</v>
+        <v>999990</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
@@ -11520,7 +11557,7 @@
         <v>10</v>
       </c>
       <c r="AJ113" s="0" t="n">
-        <v>999991</v>
+        <v>999990</v>
       </c>
       <c r="AM113" s="0" t="inlineStr">
         <is>
@@ -11538,7 +11575,7 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>999992</v>
+        <v>999991</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
@@ -11585,7 +11622,7 @@
         <v>10</v>
       </c>
       <c r="AJ114" s="0" t="n">
-        <v>999992</v>
+        <v>999991</v>
       </c>
       <c r="AM114" s="0" t="inlineStr">
         <is>
@@ -11603,7 +11640,7 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>999993</v>
+        <v>999992</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
@@ -11650,7 +11687,7 @@
         <v>10</v>
       </c>
       <c r="AJ115" s="0" t="n">
-        <v>999993</v>
+        <v>999992</v>
       </c>
       <c r="AM115" s="0" t="inlineStr">
         <is>
@@ -11668,7 +11705,7 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>999994</v>
+        <v>999993</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
@@ -11715,7 +11752,7 @@
         <v>10</v>
       </c>
       <c r="AJ116" s="0" t="n">
-        <v>999994</v>
+        <v>999993</v>
       </c>
       <c r="AM116" s="0" t="inlineStr">
         <is>
@@ -11733,7 +11770,7 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>999995</v>
+        <v>999994</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
@@ -11780,7 +11817,7 @@
         <v>10</v>
       </c>
       <c r="AJ117" s="0" t="n">
-        <v>999995</v>
+        <v>999994</v>
       </c>
       <c r="AM117" s="0" t="inlineStr">
         <is>
@@ -11798,7 +11835,7 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>999996</v>
+        <v>999995</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
@@ -11845,7 +11882,7 @@
         <v>10</v>
       </c>
       <c r="AJ118" s="0" t="n">
-        <v>999996</v>
+        <v>999995</v>
       </c>
       <c r="AM118" s="0" t="inlineStr">
         <is>
@@ -11863,7 +11900,7 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>999997</v>
+        <v>999996</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
@@ -11910,7 +11947,7 @@
         <v>10</v>
       </c>
       <c r="AJ119" s="0" t="n">
-        <v>999997</v>
+        <v>999996</v>
       </c>
       <c r="AM119" s="0" t="inlineStr">
         <is>
@@ -11928,7 +11965,7 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>999998</v>
+        <v>999997</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
@@ -11975,7 +12012,7 @@
         <v>10</v>
       </c>
       <c r="AJ120" s="0" t="n">
-        <v>999998</v>
+        <v>999997</v>
       </c>
       <c r="AM120" s="0" t="inlineStr">
         <is>
@@ -11993,7 +12030,7 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>999999</v>
+        <v>999998</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
@@ -12040,17 +12077,82 @@
         <v>10</v>
       </c>
       <c r="AJ121" s="0" t="n">
+        <v>999998</v>
+      </c>
+      <c r="AM121" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_4</t>
+        </is>
+      </c>
+      <c r="AR121" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT121" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="n">
         <v>999999</v>
       </c>
-      <c r="AM121" s="0" t="inlineStr">
+      <c r="B122" s="0" t="inlineStr">
+        <is>
+          <t>测试数据</t>
+        </is>
+      </c>
+      <c r="C122" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P122" s="0" t="n">
+        <v>200001</v>
+      </c>
+      <c r="S122" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="T122" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="U122" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V122" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X122" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y122" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB122" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE122" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG122" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ122" s="0" t="n">
+        <v>999999</v>
+      </c>
+      <c r="AM122" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AR121" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT121" s="0" t="inlineStr">
+      <c r="AR122" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT122" s="0" t="inlineStr">
         <is>
           <t>1,3,4,6</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureInfo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CreatureInfo'!$A$1:$AN$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CreatureInfo'!$A$1:$AN$65</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1080,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT122"/>
+  <dimension ref="A1:AT65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="7.375" customWidth="1" style="3" min="1" max="1"/>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>可装备武器类型（1法杖 2单手剑 3双手剑 4刀盾 5大剑 6大盾 7弓 8投掷物 9爆炸物）</t>
+          <t>可装备武器类型（1法杖 2单手剑 3双手剑 4刀盾 5大剑 6大盾 7弓 8投掷物 9爆炸物 10长枪）</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">
@@ -7924,11 +7924,26 @@
         </is>
       </c>
       <c r="J62" s="0" t="n">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Idle2</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Dead2</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Walk2</t>
+        </is>
       </c>
       <c r="N62" s="0" t="inlineStr">
         <is>
-          <t>Attack8</t>
+          <t>Attack9</t>
         </is>
       </c>
       <c r="P62" s="0" t="n">
@@ -8001,102 +8016,102 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
+      <c r="A63" s="0" t="n">
         <v>104104</v>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t>人类-大剑战士-勇者</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>2</v>
-      </c>
-      <c r="F63" t="inlineStr">
+      <c r="C63" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" s="0" t="inlineStr">
         <is>
           <t>2000100001,</t>
         </is>
       </c>
-      <c r="G63" t="n">
+      <c r="G63" s="0" t="n">
         <v>1000001</v>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I63" s="0" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="J63" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="N63" s="0" t="inlineStr">
         <is>
           <t>Attack8</t>
         </is>
       </c>
-      <c r="P63" t="n">
+      <c r="P63" s="0" t="n">
         <v>101007</v>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="Q63" s="0" t="inlineStr">
         <is>
           <t>0,0.5,0</t>
         </is>
       </c>
-      <c r="S63" t="n">
-        <v>1</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB63" t="n">
+      <c r="S63" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U63" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X63" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y63" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB63" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="AD63" t="n">
+      <c r="AD63" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="AE63" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK63" t="n">
+      <c r="AE63" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ63" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK63" s="0" t="n">
         <v>1000001</v>
       </c>
-      <c r="AL63" t="inlineStr">
+      <c r="AL63" s="0" t="inlineStr">
         <is>
           <t>ui_class_7</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
+      <c r="AM63" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_2</t>
         </is>
       </c>
-      <c r="AR63" t="n">
+      <c r="AR63" s="0" t="n">
         <v>104101</v>
       </c>
-      <c r="AT63" t="inlineStr">
+      <c r="AT63" s="0" t="inlineStr">
         <is>
           <t>1,3,4,6</t>
         </is>
@@ -8338,3848 +8353,28 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="0" t="n">
-        <v>989996</v>
-      </c>
-      <c r="B66" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C66" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S66" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T66" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U66" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V66" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X66" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y66" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z66" s="0" t="n"/>
-      <c r="AB66" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE66" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF66" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG66" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ66" s="0" t="n">
-        <v>989996</v>
-      </c>
-      <c r="AK66" s="0" t="n"/>
-      <c r="AL66" s="0" t="n"/>
-      <c r="AM66" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR66" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT66" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="0" t="n">
-        <v>989997</v>
-      </c>
-      <c r="B67" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C67" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P67" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S67" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T67" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U67" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V67" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W67" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X67" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y67" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z67" s="0" t="n"/>
-      <c r="AB67" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE67" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF67" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG67" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ67" s="0" t="n">
-        <v>989997</v>
-      </c>
-      <c r="AK67" s="0" t="n"/>
-      <c r="AL67" s="0" t="n"/>
-      <c r="AM67" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR67" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT67" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="0" t="n">
-        <v>989998</v>
-      </c>
-      <c r="B68" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C68" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P68" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S68" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T68" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U68" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V68" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X68" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y68" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z68" s="0" t="n"/>
-      <c r="AB68" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE68" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF68" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG68" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ68" s="0" t="n">
-        <v>989998</v>
-      </c>
-      <c r="AK68" s="0" t="n"/>
-      <c r="AL68" s="0" t="n"/>
-      <c r="AM68" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR68" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT68" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="0" t="n">
-        <v>989999</v>
-      </c>
-      <c r="B69" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C69" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P69" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S69" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T69" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U69" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V69" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X69" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y69" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z69" s="0" t="n"/>
-      <c r="AB69" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE69" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF69" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG69" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ69" s="0" t="n">
-        <v>989999</v>
-      </c>
-      <c r="AM69" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR69" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT69" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="0" t="n">
-        <v>999947</v>
-      </c>
-      <c r="B70" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C70" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P70" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S70" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T70" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U70" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V70" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X70" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y70" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z70" s="0" t="n"/>
-      <c r="AB70" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE70" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF70" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG70" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ70" s="0" t="n">
-        <v>999947</v>
-      </c>
-      <c r="AK70" s="0" t="n"/>
-      <c r="AL70" s="0" t="n"/>
-      <c r="AM70" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR70" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT70" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="0" t="n">
-        <v>999948</v>
-      </c>
-      <c r="B71" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C71" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P71" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S71" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T71" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U71" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V71" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X71" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y71" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z71" s="0" t="n"/>
-      <c r="AB71" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE71" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF71" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG71" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ71" s="0" t="n">
-        <v>999948</v>
-      </c>
-      <c r="AK71" s="0" t="n"/>
-      <c r="AL71" s="0" t="n"/>
-      <c r="AM71" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR71" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT71" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="0" t="n">
-        <v>999949</v>
-      </c>
-      <c r="B72" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C72" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P72" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S72" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T72" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U72" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V72" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X72" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y72" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z72" s="0" t="n"/>
-      <c r="AB72" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE72" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF72" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG72" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ72" s="0" t="n">
-        <v>999949</v>
-      </c>
-      <c r="AK72" s="0" t="n"/>
-      <c r="AL72" s="0" t="n"/>
-      <c r="AM72" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR72" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT72" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="0" t="n">
-        <v>999950</v>
-      </c>
-      <c r="B73" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C73" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P73" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S73" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T73" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U73" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V73" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X73" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y73" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z73" s="0" t="n"/>
-      <c r="AB73" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE73" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF73" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG73" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ73" s="0" t="n">
-        <v>999950</v>
-      </c>
-      <c r="AK73" s="0" t="n"/>
-      <c r="AL73" s="0" t="n"/>
-      <c r="AM73" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR73" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT73" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="0" t="n">
-        <v>999951</v>
-      </c>
-      <c r="B74" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C74" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P74" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S74" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T74" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U74" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V74" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X74" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y74" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z74" s="0" t="n"/>
-      <c r="AB74" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE74" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF74" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG74" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ74" s="0" t="n">
-        <v>999951</v>
-      </c>
-      <c r="AK74" s="0" t="n"/>
-      <c r="AL74" s="0" t="n"/>
-      <c r="AM74" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR74" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT74" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="0" t="n">
-        <v>999952</v>
-      </c>
-      <c r="B75" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C75" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P75" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S75" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T75" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U75" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V75" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W75" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X75" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y75" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z75" s="0" t="n"/>
-      <c r="AB75" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE75" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF75" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG75" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ75" s="0" t="n">
-        <v>999952</v>
-      </c>
-      <c r="AK75" s="0" t="n"/>
-      <c r="AL75" s="0" t="n"/>
-      <c r="AM75" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR75" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT75" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="0" t="n">
-        <v>999953</v>
-      </c>
-      <c r="B76" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C76" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P76" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S76" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T76" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U76" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V76" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W76" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X76" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y76" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z76" s="0" t="n"/>
-      <c r="AB76" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE76" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF76" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG76" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ76" s="0" t="n">
-        <v>999953</v>
-      </c>
-      <c r="AK76" s="0" t="n"/>
-      <c r="AL76" s="0" t="n"/>
-      <c r="AM76" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR76" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT76" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="0" t="n">
-        <v>999954</v>
-      </c>
-      <c r="B77" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C77" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P77" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S77" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T77" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U77" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V77" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W77" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X77" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y77" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z77" s="0" t="n"/>
-      <c r="AB77" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE77" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF77" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG77" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ77" s="0" t="n">
-        <v>999954</v>
-      </c>
-      <c r="AK77" s="0" t="n"/>
-      <c r="AL77" s="0" t="n"/>
-      <c r="AM77" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR77" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT77" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="0" t="n">
-        <v>999955</v>
-      </c>
-      <c r="B78" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C78" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P78" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S78" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T78" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U78" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V78" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W78" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X78" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y78" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z78" s="0" t="n"/>
-      <c r="AB78" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE78" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF78" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG78" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ78" s="0" t="n">
-        <v>999955</v>
-      </c>
-      <c r="AK78" s="0" t="n"/>
-      <c r="AL78" s="0" t="n"/>
-      <c r="AM78" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR78" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT78" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="0" t="n">
-        <v>999956</v>
-      </c>
-      <c r="B79" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C79" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P79" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S79" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T79" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U79" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V79" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X79" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y79" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z79" s="0" t="n"/>
-      <c r="AB79" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE79" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF79" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG79" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ79" s="0" t="n">
-        <v>999956</v>
-      </c>
-      <c r="AK79" s="0" t="n"/>
-      <c r="AL79" s="0" t="n"/>
-      <c r="AM79" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR79" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT79" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="0" t="n">
-        <v>999957</v>
-      </c>
-      <c r="B80" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C80" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P80" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S80" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T80" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U80" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V80" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W80" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X80" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y80" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z80" s="0" t="n"/>
-      <c r="AB80" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE80" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF80" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG80" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ80" s="0" t="n">
-        <v>999957</v>
-      </c>
-      <c r="AK80" s="0" t="n"/>
-      <c r="AL80" s="0" t="n"/>
-      <c r="AM80" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR80" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT80" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="0" t="n">
-        <v>999958</v>
-      </c>
-      <c r="B81" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C81" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P81" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S81" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T81" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U81" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V81" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W81" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X81" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y81" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z81" s="0" t="n"/>
-      <c r="AB81" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE81" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF81" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG81" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ81" s="0" t="n">
-        <v>999958</v>
-      </c>
-      <c r="AK81" s="0" t="n"/>
-      <c r="AL81" s="0" t="n"/>
-      <c r="AM81" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR81" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT81" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="0" t="n">
-        <v>999959</v>
-      </c>
-      <c r="B82" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C82" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P82" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S82" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T82" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U82" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V82" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W82" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X82" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y82" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z82" s="0" t="n"/>
-      <c r="AB82" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE82" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF82" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG82" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ82" s="0" t="n">
-        <v>999959</v>
-      </c>
-      <c r="AK82" s="0" t="n"/>
-      <c r="AL82" s="0" t="n"/>
-      <c r="AM82" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR82" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT82" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="0" t="n">
-        <v>999960</v>
-      </c>
-      <c r="B83" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C83" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P83" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S83" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T83" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U83" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V83" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W83" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X83" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y83" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z83" s="0" t="n"/>
-      <c r="AB83" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE83" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF83" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG83" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ83" s="0" t="n">
-        <v>999960</v>
-      </c>
-      <c r="AK83" s="0" t="n"/>
-      <c r="AL83" s="0" t="n"/>
-      <c r="AM83" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR83" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT83" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="0" t="n">
-        <v>999961</v>
-      </c>
-      <c r="B84" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C84" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P84" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S84" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T84" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U84" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V84" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X84" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y84" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z84" s="0" t="n"/>
-      <c r="AB84" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE84" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF84" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG84" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ84" s="0" t="n">
-        <v>999961</v>
-      </c>
-      <c r="AK84" s="0" t="n"/>
-      <c r="AL84" s="0" t="n"/>
-      <c r="AM84" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR84" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT84" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="0" t="n">
-        <v>999962</v>
-      </c>
-      <c r="B85" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C85" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P85" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S85" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T85" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U85" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V85" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X85" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y85" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z85" s="0" t="n"/>
-      <c r="AB85" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE85" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF85" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG85" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ85" s="0" t="n">
-        <v>999962</v>
-      </c>
-      <c r="AK85" s="0" t="n"/>
-      <c r="AL85" s="0" t="n"/>
-      <c r="AM85" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR85" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT85" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="0" t="n">
-        <v>999963</v>
-      </c>
-      <c r="B86" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C86" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P86" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S86" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T86" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U86" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V86" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W86" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X86" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y86" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z86" s="0" t="n"/>
-      <c r="AB86" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE86" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF86" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG86" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ86" s="0" t="n">
-        <v>999963</v>
-      </c>
-      <c r="AK86" s="0" t="n"/>
-      <c r="AL86" s="0" t="n"/>
-      <c r="AM86" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR86" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT86" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="0" t="n">
-        <v>999964</v>
-      </c>
-      <c r="B87" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C87" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P87" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S87" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T87" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U87" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V87" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W87" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X87" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y87" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z87" s="0" t="n"/>
-      <c r="AB87" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE87" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF87" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG87" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ87" s="0" t="n">
-        <v>999964</v>
-      </c>
-      <c r="AK87" s="0" t="n"/>
-      <c r="AL87" s="0" t="n"/>
-      <c r="AM87" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR87" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT87" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="0" t="n">
-        <v>999965</v>
-      </c>
-      <c r="B88" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C88" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P88" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S88" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T88" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U88" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V88" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W88" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X88" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y88" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z88" s="0" t="n"/>
-      <c r="AB88" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE88" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF88" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG88" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ88" s="0" t="n">
-        <v>999965</v>
-      </c>
-      <c r="AK88" s="0" t="n"/>
-      <c r="AL88" s="0" t="n"/>
-      <c r="AM88" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR88" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT88" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="0" t="n">
-        <v>999966</v>
-      </c>
-      <c r="B89" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C89" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P89" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S89" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T89" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U89" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V89" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W89" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X89" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y89" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z89" s="0" t="n"/>
-      <c r="AB89" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE89" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF89" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG89" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ89" s="0" t="n">
-        <v>999966</v>
-      </c>
-      <c r="AK89" s="0" t="n"/>
-      <c r="AL89" s="0" t="n"/>
-      <c r="AM89" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR89" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT89" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="0" t="n">
-        <v>999967</v>
-      </c>
-      <c r="B90" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C90" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P90" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S90" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T90" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U90" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V90" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W90" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X90" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y90" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z90" s="0" t="n"/>
-      <c r="AB90" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE90" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF90" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG90" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ90" s="0" t="n">
-        <v>999967</v>
-      </c>
-      <c r="AK90" s="0" t="n"/>
-      <c r="AL90" s="0" t="n"/>
-      <c r="AM90" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR90" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT90" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="0" t="n">
-        <v>999968</v>
-      </c>
-      <c r="B91" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C91" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P91" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S91" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T91" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U91" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V91" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W91" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X91" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y91" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z91" s="0" t="n"/>
-      <c r="AB91" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE91" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF91" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG91" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ91" s="0" t="n">
-        <v>999968</v>
-      </c>
-      <c r="AK91" s="0" t="n"/>
-      <c r="AL91" s="0" t="n"/>
-      <c r="AM91" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR91" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT91" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="0" t="n">
-        <v>999969</v>
-      </c>
-      <c r="B92" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C92" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P92" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S92" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T92" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U92" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V92" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W92" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X92" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y92" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z92" s="0" t="n"/>
-      <c r="AB92" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE92" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF92" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG92" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ92" s="0" t="n">
-        <v>999969</v>
-      </c>
-      <c r="AK92" s="0" t="n"/>
-      <c r="AL92" s="0" t="n"/>
-      <c r="AM92" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR92" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT92" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="0" t="n">
-        <v>999970</v>
-      </c>
-      <c r="B93" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C93" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P93" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S93" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T93" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U93" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V93" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X93" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y93" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z93" s="0" t="n"/>
-      <c r="AB93" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE93" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF93" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG93" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ93" s="0" t="n">
-        <v>999970</v>
-      </c>
-      <c r="AK93" s="0" t="n"/>
-      <c r="AL93" s="0" t="n"/>
-      <c r="AM93" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR93" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT93" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="0" t="n">
-        <v>999971</v>
-      </c>
-      <c r="B94" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C94" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P94" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S94" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T94" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U94" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V94" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W94" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X94" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y94" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z94" s="0" t="n"/>
-      <c r="AB94" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE94" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF94" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG94" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ94" s="0" t="n">
-        <v>999971</v>
-      </c>
-      <c r="AK94" s="0" t="n"/>
-      <c r="AL94" s="0" t="n"/>
-      <c r="AM94" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR94" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT94" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="0" t="n">
-        <v>999972</v>
-      </c>
-      <c r="B95" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C95" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P95" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S95" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T95" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U95" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V95" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W95" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X95" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y95" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z95" s="0" t="n"/>
-      <c r="AB95" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE95" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF95" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG95" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ95" s="0" t="n">
-        <v>999972</v>
-      </c>
-      <c r="AK95" s="0" t="n"/>
-      <c r="AL95" s="0" t="n"/>
-      <c r="AM95" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR95" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT95" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="0" t="n">
-        <v>999973</v>
-      </c>
-      <c r="B96" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C96" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P96" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S96" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T96" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U96" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V96" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X96" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y96" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z96" s="0" t="n"/>
-      <c r="AB96" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE96" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF96" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG96" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ96" s="0" t="n">
-        <v>999973</v>
-      </c>
-      <c r="AK96" s="0" t="n"/>
-      <c r="AL96" s="0" t="n"/>
-      <c r="AM96" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR96" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT96" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="0" t="n">
-        <v>999974</v>
-      </c>
-      <c r="B97" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C97" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P97" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S97" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T97" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U97" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V97" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W97" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X97" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y97" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z97" s="0" t="n"/>
-      <c r="AB97" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE97" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF97" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG97" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ97" s="0" t="n">
-        <v>999974</v>
-      </c>
-      <c r="AK97" s="0" t="n"/>
-      <c r="AL97" s="0" t="n"/>
-      <c r="AM97" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR97" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT97" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="0" t="n">
-        <v>999975</v>
-      </c>
-      <c r="B98" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C98" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P98" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S98" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T98" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U98" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V98" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W98" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X98" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y98" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z98" s="0" t="n"/>
-      <c r="AB98" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE98" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF98" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG98" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ98" s="0" t="n">
-        <v>999975</v>
-      </c>
-      <c r="AK98" s="0" t="n"/>
-      <c r="AL98" s="0" t="n"/>
-      <c r="AM98" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR98" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT98" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="0" t="n">
-        <v>999976</v>
-      </c>
-      <c r="B99" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C99" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P99" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S99" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T99" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U99" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V99" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W99" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X99" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y99" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z99" s="0" t="n"/>
-      <c r="AB99" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE99" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF99" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG99" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ99" s="0" t="n">
-        <v>999976</v>
-      </c>
-      <c r="AK99" s="0" t="n"/>
-      <c r="AL99" s="0" t="n"/>
-      <c r="AM99" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR99" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT99" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="0" t="n">
-        <v>999977</v>
-      </c>
-      <c r="B100" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C100" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P100" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S100" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T100" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U100" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V100" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W100" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X100" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y100" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z100" s="0" t="n"/>
-      <c r="AB100" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE100" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF100" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG100" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ100" s="0" t="n">
-        <v>999977</v>
-      </c>
-      <c r="AK100" s="0" t="n"/>
-      <c r="AL100" s="0" t="n"/>
-      <c r="AM100" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR100" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT100" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="0" t="n">
-        <v>999978</v>
-      </c>
-      <c r="B101" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C101" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P101" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S101" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T101" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U101" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V101" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X101" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y101" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z101" s="0" t="n"/>
-      <c r="AB101" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE101" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG101" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ101" s="0" t="n">
-        <v>999978</v>
-      </c>
-      <c r="AK101" s="0" t="n"/>
-      <c r="AL101" s="0" t="n"/>
-      <c r="AM101" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR101" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT101" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="0" t="n">
-        <v>999979</v>
-      </c>
-      <c r="B102" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C102" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P102" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S102" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T102" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U102" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V102" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X102" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y102" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z102" s="0" t="n"/>
-      <c r="AB102" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE102" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG102" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ102" s="0" t="n">
-        <v>999979</v>
-      </c>
-      <c r="AK102" s="0" t="n"/>
-      <c r="AL102" s="0" t="n"/>
-      <c r="AM102" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR102" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT102" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="0" t="n">
-        <v>999980</v>
-      </c>
-      <c r="B103" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C103" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P103" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S103" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T103" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U103" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V103" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W103" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X103" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y103" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z103" s="0" t="n"/>
-      <c r="AB103" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE103" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF103" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG103" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ103" s="0" t="n">
-        <v>999980</v>
-      </c>
-      <c r="AK103" s="0" t="n"/>
-      <c r="AL103" s="0" t="n"/>
-      <c r="AM103" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR103" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT103" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="0" t="n">
-        <v>999981</v>
-      </c>
-      <c r="B104" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C104" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P104" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S104" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T104" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U104" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V104" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W104" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X104" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y104" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z104" s="0" t="n"/>
-      <c r="AB104" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE104" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF104" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG104" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ104" s="0" t="n">
-        <v>999981</v>
-      </c>
-      <c r="AK104" s="0" t="n"/>
-      <c r="AL104" s="0" t="n"/>
-      <c r="AM104" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR104" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT104" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="0" t="n">
-        <v>999982</v>
-      </c>
-      <c r="B105" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C105" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P105" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S105" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T105" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U105" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V105" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W105" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X105" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y105" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB105" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE105" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF105" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG105" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ105" s="0" t="n">
-        <v>999982</v>
-      </c>
-      <c r="AM105" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR105" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT105" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="0" t="n">
-        <v>999983</v>
-      </c>
-      <c r="B106" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C106" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P106" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S106" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T106" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U106" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V106" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W106" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X106" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y106" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB106" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE106" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF106" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG106" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ106" s="0" t="n">
-        <v>999983</v>
-      </c>
-      <c r="AM106" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR106" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT106" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="0" t="n">
-        <v>999984</v>
-      </c>
-      <c r="B107" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C107" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P107" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S107" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T107" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U107" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V107" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W107" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X107" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y107" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB107" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE107" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF107" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG107" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ107" s="0" t="n">
-        <v>999984</v>
-      </c>
-      <c r="AM107" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR107" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT107" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="0" t="n">
-        <v>999985</v>
-      </c>
-      <c r="B108" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C108" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P108" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S108" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T108" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U108" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V108" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W108" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X108" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y108" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB108" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE108" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF108" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG108" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ108" s="0" t="n">
-        <v>999985</v>
-      </c>
-      <c r="AM108" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR108" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT108" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="0" t="n">
-        <v>999986</v>
-      </c>
-      <c r="B109" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C109" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P109" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S109" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T109" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U109" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V109" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W109" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X109" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y109" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB109" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE109" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF109" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG109" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ109" s="0" t="n">
-        <v>999986</v>
-      </c>
-      <c r="AM109" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR109" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT109" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="0" t="n">
-        <v>999987</v>
-      </c>
-      <c r="B110" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C110" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P110" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S110" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T110" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U110" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V110" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W110" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X110" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y110" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB110" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE110" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF110" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG110" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ110" s="0" t="n">
-        <v>999987</v>
-      </c>
-      <c r="AM110" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR110" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT110" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="0" t="n">
-        <v>999988</v>
-      </c>
-      <c r="B111" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C111" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P111" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S111" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T111" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U111" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V111" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W111" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X111" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y111" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB111" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE111" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF111" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG111" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ111" s="0" t="n">
-        <v>999988</v>
-      </c>
-      <c r="AM111" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR111" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT111" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="0" t="n">
-        <v>999989</v>
-      </c>
-      <c r="B112" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C112" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P112" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S112" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T112" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U112" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V112" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W112" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X112" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y112" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB112" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE112" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF112" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG112" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ112" s="0" t="n">
-        <v>999989</v>
-      </c>
-      <c r="AM112" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR112" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT112" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="0" t="n">
-        <v>999990</v>
-      </c>
-      <c r="B113" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C113" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P113" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S113" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T113" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U113" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V113" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W113" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X113" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y113" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB113" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE113" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF113" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG113" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ113" s="0" t="n">
-        <v>999990</v>
-      </c>
-      <c r="AM113" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR113" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT113" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="0" t="n">
-        <v>999991</v>
-      </c>
-      <c r="B114" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C114" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P114" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S114" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T114" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U114" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V114" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W114" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X114" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y114" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB114" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE114" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF114" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG114" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ114" s="0" t="n">
-        <v>999991</v>
-      </c>
-      <c r="AM114" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR114" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT114" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="0" t="n">
-        <v>999992</v>
-      </c>
-      <c r="B115" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C115" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P115" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S115" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T115" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U115" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V115" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W115" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X115" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y115" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB115" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE115" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF115" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG115" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ115" s="0" t="n">
-        <v>999992</v>
-      </c>
-      <c r="AM115" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR115" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT115" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="0" t="n">
-        <v>999993</v>
-      </c>
-      <c r="B116" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C116" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P116" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S116" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T116" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U116" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V116" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X116" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y116" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB116" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE116" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF116" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG116" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ116" s="0" t="n">
-        <v>999993</v>
-      </c>
-      <c r="AM116" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR116" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT116" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="0" t="n">
-        <v>999994</v>
-      </c>
-      <c r="B117" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C117" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P117" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S117" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T117" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U117" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V117" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W117" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X117" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y117" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB117" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE117" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF117" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG117" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ117" s="0" t="n">
-        <v>999994</v>
-      </c>
-      <c r="AM117" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR117" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT117" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="0" t="n">
-        <v>999995</v>
-      </c>
-      <c r="B118" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C118" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P118" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S118" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T118" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U118" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V118" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W118" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X118" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y118" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB118" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE118" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF118" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG118" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ118" s="0" t="n">
-        <v>999995</v>
-      </c>
-      <c r="AM118" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR118" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT118" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="0" t="n">
-        <v>999996</v>
-      </c>
-      <c r="B119" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C119" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P119" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S119" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T119" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U119" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V119" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W119" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X119" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y119" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB119" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE119" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF119" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG119" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ119" s="0" t="n">
-        <v>999996</v>
-      </c>
-      <c r="AM119" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR119" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT119" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="0" t="n">
-        <v>999997</v>
-      </c>
-      <c r="B120" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C120" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P120" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S120" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T120" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U120" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V120" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W120" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X120" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y120" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB120" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE120" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF120" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG120" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ120" s="0" t="n">
-        <v>999997</v>
-      </c>
-      <c r="AM120" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR120" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT120" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="0" t="n">
-        <v>999998</v>
-      </c>
-      <c r="B121" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C121" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P121" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S121" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T121" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U121" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V121" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W121" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X121" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y121" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB121" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE121" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF121" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG121" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ121" s="0" t="n">
-        <v>999998</v>
-      </c>
-      <c r="AM121" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR121" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT121" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="0" t="n">
-        <v>999999</v>
-      </c>
-      <c r="B122" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C122" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P122" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S122" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T122" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U122" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V122" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W122" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X122" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y122" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB122" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE122" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF122" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG122" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ122" s="0" t="n">
-        <v>999999</v>
-      </c>
-      <c r="AM122" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR122" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT122" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="15" customHeight="1" s="3"/>
-    <row r="132" ht="15" customHeight="1" s="3"/>
-    <row r="133" ht="15" customHeight="1" s="3"/>
-    <row r="134" ht="15" customHeight="1" s="3"/>
-    <row r="135" ht="15" customHeight="1" s="3"/>
-    <row r="136" ht="15" customHeight="1" s="3"/>
-    <row r="137" ht="15" customHeight="1" s="3"/>
-    <row r="138" ht="15" customHeight="1" s="3"/>
-    <row r="139" ht="15" customHeight="1" s="3"/>
-    <row r="140" ht="15" customHeight="1" s="3"/>
-    <row r="141" ht="15" customHeight="1" s="3"/>
-    <row r="173" ht="12" customHeight="1" s="3"/>
-    <row r="174" ht="12" customHeight="1" s="3"/>
-    <row r="175" ht="12" customHeight="1" s="3"/>
-    <row r="176" ht="12" customHeight="1" s="3"/>
-    <row r="177" ht="12" customHeight="1" s="3"/>
-    <row r="178" ht="12" customHeight="1" s="3"/>
-    <row r="179" ht="12" customHeight="1" s="3"/>
-    <row r="180" ht="12" customHeight="1" s="3"/>
-    <row r="181" ht="12" customHeight="1" s="3"/>
+    <row r="74" ht="15" customHeight="1" s="3"/>
+    <row r="75" ht="15" customHeight="1" s="3"/>
+    <row r="76" ht="15" customHeight="1" s="3"/>
+    <row r="77" ht="15" customHeight="1" s="3"/>
+    <row r="78" ht="15" customHeight="1" s="3"/>
+    <row r="79" ht="15" customHeight="1" s="3"/>
+    <row r="80" ht="15" customHeight="1" s="3"/>
+    <row r="81" ht="15" customHeight="1" s="3"/>
+    <row r="82" ht="15" customHeight="1" s="3"/>
+    <row r="83" ht="15" customHeight="1" s="3"/>
+    <row r="84" ht="15" customHeight="1" s="3"/>
+    <row r="116" ht="12" customHeight="1" s="3"/>
+    <row r="117" ht="12" customHeight="1" s="3"/>
+    <row r="118" ht="12" customHeight="1" s="3"/>
+    <row r="119" ht="12" customHeight="1" s="3"/>
+    <row r="120" ht="12" customHeight="1" s="3"/>
+    <row r="121" ht="12" customHeight="1" s="3"/>
+    <row r="122" ht="12" customHeight="1" s="3"/>
+    <row r="123" ht="12" customHeight="1" s="3"/>
+    <row r="124" ht="12" customHeight="1" s="3"/>
   </sheetData>
-  <autoFilter ref="A1:AN116"/>
+  <autoFilter ref="A1:AN65"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -6244,7 +6244,7 @@
         <v>1</v>
       </c>
       <c r="T46" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U46" s="4" t="n">
         <v>1</v>
@@ -6354,7 +6354,7 @@
         <v>1</v>
       </c>
       <c r="T47" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U47" s="4" t="n">
         <v>1</v>
@@ -6464,7 +6464,7 @@
         <v>1</v>
       </c>
       <c r="T48" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U48" s="4" t="n">
         <v>1</v>
@@ -6574,7 +6574,7 @@
         <v>1</v>
       </c>
       <c r="T49" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U49" s="4" t="n">
         <v>1</v>
@@ -6684,7 +6684,7 @@
         <v>1</v>
       </c>
       <c r="T50" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U50" s="4" t="n">
         <v>1</v>
@@ -6794,7 +6794,7 @@
         <v>1</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U51" s="4" t="n">
         <v>1</v>
@@ -6904,7 +6904,7 @@
         <v>1</v>
       </c>
       <c r="T52" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U52" s="4" t="n">
         <v>1</v>
@@ -7005,7 +7005,7 @@
         <v>1</v>
       </c>
       <c r="T53" s="0" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U53" s="0" t="n">
         <v>1</v>
@@ -7099,7 +7099,7 @@
         <v>1</v>
       </c>
       <c r="T54" s="0" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U54" s="0" t="n">
         <v>1</v>
@@ -7926,17 +7926,17 @@
       <c r="J62" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K62" s="0" t="inlineStr">
         <is>
           <t>Idle2</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L62" s="0" t="inlineStr">
         <is>
           <t>Dead2</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M62" s="0" t="inlineStr">
         <is>
           <t>Walk2</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -2598,7 +2598,7 @@
       </c>
       <c r="Q13" s="0" t="inlineStr">
         <is>
-          <t>0,1.5,0</t>
+          <t>0,3,0</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="Q14" s="0" t="inlineStr">
         <is>
-          <t>0,1.5,0</t>
+          <t>0,3,0</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -1080,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT65"/>
+  <dimension ref="A1:AT64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="7.375" customWidth="1" style="3" min="1" max="1"/>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X24" s="1" t="n">
         <v>0.5</v>
@@ -4110,35 +4110,35 @@
     </row>
     <row r="27" customFormat="1" s="1">
       <c r="A27" s="1" t="n">
-        <v>4005</v>
+        <v>5001</v>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>盾之魅魔</t>
+          <t>牛头人战士</t>
         </is>
       </c>
       <c r="C27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>4000001</v>
+        <v>5000001</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>1,2,3,6</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="P27" s="1" t="n">
-        <v>500002</v>
+        <v>101002</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="U27" s="1" t="n">
         <v>1</v>
@@ -4159,13 +4159,13 @@
         <v>10</v>
       </c>
       <c r="AA27" s="1" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AB27" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AE27" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AF27" s="1" t="n">
         <v>0</v>
@@ -4174,14 +4174,14 @@
         <v>10</v>
       </c>
       <c r="AJ27" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK27" s="1" t="n">
-        <v>4000001</v>
+        <v>5000001</v>
       </c>
       <c r="AL27" s="1" t="inlineStr">
         <is>
-          <t>ui_class_16</t>
+          <t>ui_class_3</t>
         </is>
       </c>
       <c r="AM27" s="1" t="inlineStr">
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="AN27" s="1" t="n">
-        <v>300400005</v>
+        <v>300500001</v>
       </c>
       <c r="AO27" s="0" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="AR27" s="1" t="n">
-        <v>4005</v>
+        <v>5001</v>
       </c>
       <c r="AS27" s="0" t="n">
-        <v>4005</v>
+        <v>5001</v>
       </c>
       <c r="AT27" s="0" t="inlineStr">
         <is>
@@ -4211,11 +4211,11 @@
     </row>
     <row r="28" customFormat="1" s="1">
       <c r="A28" s="1" t="n">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>牛头人战士</t>
+          <t>牛头人投手</t>
         </is>
       </c>
       <c r="C28" s="1" t="n">
@@ -4224,22 +4224,33 @@
       <c r="G28" s="1" t="n">
         <v>5000001</v>
       </c>
+      <c r="H28" s="1" t="n">
+        <v>51010001</v>
+      </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>1,2,3,5</t>
-        </is>
+          <t>1,2,3,5,10</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="n">
+        <v>8</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>101002</v>
+        <v>203001</v>
+      </c>
+      <c r="Q28" s="1" t="inlineStr">
+        <is>
+          <t>0,0.8,0</t>
+        </is>
       </c>
       <c r="R28" s="1" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="S28" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="U28" s="1" t="n">
         <v>1</v>
@@ -4260,7 +4271,7 @@
         <v>10</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AB28" s="1" t="n">
         <v>300</v>
@@ -4282,7 +4293,7 @@
       </c>
       <c r="AL28" s="1" t="inlineStr">
         <is>
-          <t>ui_class_3</t>
+          <t>ui_class_6</t>
         </is>
       </c>
       <c r="AM28" s="1" t="inlineStr">
@@ -4291,7 +4302,7 @@
         </is>
       </c>
       <c r="AN28" s="1" t="n">
-        <v>300500001</v>
+        <v>300500002</v>
       </c>
       <c r="AO28" s="0" t="inlineStr">
         <is>
@@ -4299,10 +4310,10 @@
         </is>
       </c>
       <c r="AR28" s="1" t="n">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="AS28" s="0" t="n">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="AT28" s="0" t="inlineStr">
         <is>
@@ -4312,11 +4323,11 @@
     </row>
     <row r="29" customFormat="1" s="1">
       <c r="A29" s="1" t="n">
-        <v>5002</v>
+        <v>5003</v>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>牛头人投手</t>
+          <t>牛头人魔法师（火）</t>
         </is>
       </c>
       <c r="C29" s="1" t="n">
@@ -4325,27 +4336,16 @@
       <c r="G29" s="1" t="n">
         <v>5000001</v>
       </c>
-      <c r="H29" s="1" t="n">
-        <v>51010001</v>
-      </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>1,2,3,5,10</t>
-        </is>
-      </c>
-      <c r="J29" s="1" t="n">
-        <v>8</v>
+          <t>1,2,3,5</t>
+        </is>
       </c>
       <c r="P29" s="1" t="n">
-        <v>203001</v>
-      </c>
-      <c r="Q29" s="1" t="inlineStr">
-        <is>
-          <t>0,0.8,0</t>
-        </is>
+        <v>101003</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="S29" s="1" t="n">
         <v>2</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X29" s="1" t="n">
         <v>0.5</v>
@@ -4372,10 +4372,10 @@
         <v>10</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AB29" s="1" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="AE29" s="1" t="n">
         <v>5</v>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="AL29" s="1" t="inlineStr">
         <is>
-          <t>ui_class_6</t>
+          <t>ui_class_10</t>
         </is>
       </c>
       <c r="AM29" s="1" t="inlineStr">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="AN29" s="1" t="n">
-        <v>300500002</v>
+        <v>300500003</v>
       </c>
       <c r="AO29" s="0" t="inlineStr">
         <is>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="AR29" s="1" t="n">
-        <v>5002</v>
+        <v>5003</v>
       </c>
       <c r="AS29" s="0" t="n">
-        <v>5002</v>
+        <v>5003</v>
       </c>
       <c r="AT29" s="0" t="inlineStr">
         <is>
@@ -4424,11 +4424,11 @@
     </row>
     <row r="30" customFormat="1" s="1">
       <c r="A30" s="1" t="n">
-        <v>5003</v>
+        <v>5004</v>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>牛头人魔法师（火）</t>
+          <t>牛头人魔法师（冰）</t>
         </is>
       </c>
       <c r="C30" s="1" t="n">
@@ -4437,13 +4437,14 @@
       <c r="G30" s="1" t="n">
         <v>5000001</v>
       </c>
+      <c r="H30" s="1" t="n"/>
       <c r="I30" s="1" t="inlineStr">
         <is>
           <t>1,2,3,5</t>
         </is>
       </c>
       <c r="P30" s="1" t="n">
-        <v>101003</v>
+        <v>101004</v>
       </c>
       <c r="R30" s="1" t="n">
         <v>0</v>
@@ -4495,7 +4496,7 @@
       </c>
       <c r="AL30" s="1" t="inlineStr">
         <is>
-          <t>ui_class_10</t>
+          <t>ui_class_2</t>
         </is>
       </c>
       <c r="AM30" s="1" t="inlineStr">
@@ -4504,7 +4505,7 @@
         </is>
       </c>
       <c r="AN30" s="1" t="n">
-        <v>300500003</v>
+        <v>300500004</v>
       </c>
       <c r="AO30" s="0" t="inlineStr">
         <is>
@@ -4512,10 +4513,10 @@
         </is>
       </c>
       <c r="AR30" s="1" t="n">
-        <v>5003</v>
+        <v>5004</v>
       </c>
       <c r="AS30" s="0" t="n">
-        <v>5003</v>
+        <v>5004</v>
       </c>
       <c r="AT30" s="0" t="inlineStr">
         <is>
@@ -4525,36 +4526,48 @@
     </row>
     <row r="31" customFormat="1" s="1">
       <c r="A31" s="1" t="n">
-        <v>5004</v>
+        <v>6001</v>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>牛头人魔法师（冰）</t>
+          <t>哥布林刺客</t>
         </is>
       </c>
       <c r="C31" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>2000100001,2000200001,2000500001,</t>
+        </is>
+      </c>
       <c r="G31" s="1" t="n">
-        <v>5000001</v>
-      </c>
-      <c r="H31" s="1" t="n"/>
+        <v>6000001</v>
+      </c>
+      <c r="H31" s="0" t="n">
+        <v>61010001</v>
+      </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>1,2,3,5</t>
-        </is>
+          <t>1,2,3,10,</t>
+        </is>
+      </c>
+      <c r="J31" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>101004</v>
-      </c>
-      <c r="R31" s="1" t="n">
-        <v>0</v>
+        <v>100001</v>
+      </c>
+      <c r="Q31" s="1" t="inlineStr">
+        <is>
+          <t>0,0.3,0</t>
+        </is>
       </c>
       <c r="S31" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="U31" s="1" t="n">
         <v>1</v>
@@ -4563,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="X31" s="1" t="n">
         <v>0.5</v>
@@ -4575,13 +4588,16 @@
         <v>10</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AB31" s="1" t="n">
-        <v>150</v>
+        <v>30</v>
+      </c>
+      <c r="AD31" s="0" t="n">
+        <v>50</v>
       </c>
       <c r="AE31" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF31" s="1" t="n">
         <v>0</v>
@@ -4590,23 +4606,23 @@
         <v>10</v>
       </c>
       <c r="AJ31" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK31" s="1" t="n">
-        <v>5000001</v>
+        <v>6000001</v>
       </c>
       <c r="AL31" s="1" t="inlineStr">
         <is>
-          <t>ui_class_2</t>
+          <t>ui_class_1</t>
         </is>
       </c>
       <c r="AM31" s="1" t="inlineStr">
         <is>
-          <t>Card_Scene_1</t>
+          <t>Card_Scene_7</t>
         </is>
       </c>
       <c r="AN31" s="1" t="n">
-        <v>300500004</v>
+        <v>300600001</v>
       </c>
       <c r="AO31" s="0" t="inlineStr">
         <is>
@@ -4614,10 +4630,10 @@
         </is>
       </c>
       <c r="AR31" s="1" t="n">
-        <v>5004</v>
+        <v>6001</v>
       </c>
       <c r="AS31" s="0" t="n">
-        <v>5004</v>
+        <v>6001</v>
       </c>
       <c r="AT31" s="0" t="inlineStr">
         <is>
@@ -4627,26 +4643,21 @@
     </row>
     <row r="32" customFormat="1" s="1">
       <c r="A32" s="1" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>哥布林刺客</t>
+          <t>哥布林弓箭手</t>
         </is>
       </c>
       <c r="C32" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>2000100001,2000200001,2000500001,</t>
-        </is>
       </c>
       <c r="G32" s="1" t="n">
         <v>6000001</v>
       </c>
-      <c r="H32" s="0" t="n">
-        <v>61010001</v>
+      <c r="H32" s="1" t="n">
+        <v>61010002</v>
       </c>
       <c r="I32" s="1" t="inlineStr">
         <is>
@@ -4654,10 +4665,15 @@
         </is>
       </c>
       <c r="J32" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="N32" s="1" t="inlineStr">
+        <is>
+          <t>Attack2</t>
+        </is>
       </c>
       <c r="P32" s="1" t="n">
-        <v>100001</v>
+        <v>204001</v>
       </c>
       <c r="Q32" s="1" t="inlineStr">
         <is>
@@ -4668,7 +4684,7 @@
         <v>2</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U32" s="1" t="n">
         <v>1</v>
@@ -4677,7 +4693,7 @@
         <v>0</v>
       </c>
       <c r="W32" s="1" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X32" s="1" t="n">
         <v>0.5</v>
@@ -4692,13 +4708,10 @@
         <v>30</v>
       </c>
       <c r="AB32" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD32" s="0" t="n">
         <v>50</v>
       </c>
       <c r="AE32" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF32" s="1" t="n">
         <v>0</v>
@@ -4714,7 +4727,7 @@
       </c>
       <c r="AL32" s="1" t="inlineStr">
         <is>
-          <t>ui_class_1</t>
+          <t>ui_class_6</t>
         </is>
       </c>
       <c r="AM32" s="1" t="inlineStr">
@@ -4723,7 +4736,7 @@
         </is>
       </c>
       <c r="AN32" s="1" t="n">
-        <v>300600001</v>
+        <v>300600002</v>
       </c>
       <c r="AO32" s="0" t="inlineStr">
         <is>
@@ -4731,10 +4744,10 @@
         </is>
       </c>
       <c r="AR32" s="1" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="AS32" s="0" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="AT32" s="0" t="inlineStr">
         <is>
@@ -4744,11 +4757,11 @@
     </row>
     <row r="33" customFormat="1" s="1">
       <c r="A33" s="1" t="n">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>哥布林弓箭手</t>
+          <t>哥布林敢死队</t>
         </is>
       </c>
       <c r="C33" s="1" t="n">
@@ -4757,8 +4770,8 @@
       <c r="G33" s="1" t="n">
         <v>6000001</v>
       </c>
-      <c r="H33" s="1" t="n">
-        <v>61010002</v>
+      <c r="H33" s="0" t="n">
+        <v>61010017</v>
       </c>
       <c r="I33" s="1" t="inlineStr">
         <is>
@@ -4766,29 +4779,24 @@
         </is>
       </c>
       <c r="J33" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="N33" s="1" t="inlineStr">
-        <is>
-          <t>Attack2</t>
+        <v>9</v>
+      </c>
+      <c r="M33" s="0" t="inlineStr">
+        <is>
+          <t>Walk2</t>
         </is>
       </c>
       <c r="P33" s="1" t="n">
-        <v>204001</v>
-      </c>
-      <c r="Q33" s="1" t="inlineStr">
-        <is>
-          <t>0,0.3,0</t>
-        </is>
+        <v>300002</v>
       </c>
       <c r="S33" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="V33" s="0" t="n">
         <v>0</v>
@@ -4806,13 +4814,13 @@
         <v>10</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AB33" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AE33" s="1" t="n">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="AF33" s="1" t="n">
         <v>0</v>
@@ -4828,7 +4836,7 @@
       </c>
       <c r="AL33" s="1" t="inlineStr">
         <is>
-          <t>ui_class_6</t>
+          <t>ui_class_9</t>
         </is>
       </c>
       <c r="AM33" s="1" t="inlineStr">
@@ -4837,18 +4845,21 @@
         </is>
       </c>
       <c r="AN33" s="1" t="n">
-        <v>300600002</v>
+        <v>300600003</v>
       </c>
       <c r="AO33" s="0" t="inlineStr">
         <is>
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AQ33" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="AR33" s="1" t="n">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="AS33" s="0" t="n">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="AT33" s="0" t="inlineStr">
         <is>
@@ -4858,11 +4869,11 @@
     </row>
     <row r="34" customFormat="1" s="1">
       <c r="A34" s="1" t="n">
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>哥布林敢死队</t>
+          <t>哥布林魔法师（火）</t>
         </is>
       </c>
       <c r="C34" s="1" t="n">
@@ -4871,8 +4882,8 @@
       <c r="G34" s="1" t="n">
         <v>6000001</v>
       </c>
-      <c r="H34" s="0" t="n">
-        <v>61010017</v>
+      <c r="H34" s="1" t="n">
+        <v>61010003</v>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
@@ -4880,30 +4891,35 @@
         </is>
       </c>
       <c r="J34" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="M34" s="0" t="inlineStr">
-        <is>
-          <t>Walk2</t>
+        <v>1</v>
+      </c>
+      <c r="N34" s="1" t="inlineStr">
+        <is>
+          <t>Attack3</t>
         </is>
       </c>
       <c r="P34" s="1" t="n">
-        <v>300002</v>
+        <v>204002</v>
+      </c>
+      <c r="Q34" s="1" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
+        </is>
       </c>
       <c r="S34" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="V34" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W34" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X34" s="1" t="n">
         <v>0.5</v>
@@ -4915,13 +4931,13 @@
         <v>10</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="AB34" s="1" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AE34" s="1" t="n">
-        <v>500</v>
+        <v>5</v>
       </c>
       <c r="AF34" s="1" t="n">
         <v>0</v>
@@ -4937,7 +4953,7 @@
       </c>
       <c r="AL34" s="1" t="inlineStr">
         <is>
-          <t>ui_class_9</t>
+          <t>ui_class_10</t>
         </is>
       </c>
       <c r="AM34" s="1" t="inlineStr">
@@ -4946,21 +4962,18 @@
         </is>
       </c>
       <c r="AN34" s="1" t="n">
-        <v>300600003</v>
+        <v>300600004</v>
       </c>
       <c r="AO34" s="0" t="inlineStr">
         <is>
           <t>0.9,1.1</t>
         </is>
       </c>
-      <c r="AQ34" s="0" t="n">
-        <v>1</v>
-      </c>
       <c r="AR34" s="1" t="n">
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="AS34" s="0" t="n">
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="AT34" s="0" t="inlineStr">
         <is>
@@ -4970,11 +4983,11 @@
     </row>
     <row r="35" customFormat="1" s="1">
       <c r="A35" s="1" t="n">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>哥布林魔法师（火）</t>
+          <t>哥布林魔法师（冰）</t>
         </is>
       </c>
       <c r="C35" s="1" t="n">
@@ -5000,7 +5013,7 @@
         </is>
       </c>
       <c r="P35" s="1" t="n">
-        <v>204002</v>
+        <v>204003</v>
       </c>
       <c r="Q35" s="1" t="inlineStr">
         <is>
@@ -5054,7 +5067,7 @@
       </c>
       <c r="AL35" s="1" t="inlineStr">
         <is>
-          <t>ui_class_10</t>
+          <t>ui_class_2</t>
         </is>
       </c>
       <c r="AM35" s="1" t="inlineStr">
@@ -5063,7 +5076,7 @@
         </is>
       </c>
       <c r="AN35" s="1" t="n">
-        <v>300600004</v>
+        <v>300600005</v>
       </c>
       <c r="AO35" s="0" t="inlineStr">
         <is>
@@ -5071,10 +5084,10 @@
         </is>
       </c>
       <c r="AR35" s="1" t="n">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="AS35" s="0" t="n">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="AT35" s="0" t="inlineStr">
         <is>
@@ -5084,48 +5097,43 @@
     </row>
     <row r="36" customFormat="1" s="1">
       <c r="A36" s="1" t="n">
-        <v>6005</v>
+        <v>7001</v>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>哥布林魔法师（冰）</t>
+          <t>兽人战士</t>
         </is>
       </c>
       <c r="C36" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>2000300001,2000400001,</t>
+        </is>
+      </c>
       <c r="G36" s="1" t="n">
-        <v>6000001</v>
-      </c>
-      <c r="H36" s="1" t="n">
-        <v>61010003</v>
+        <v>7000001</v>
+      </c>
+      <c r="H36" s="0" t="n">
+        <v>71010001</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>1,2,3,10,</t>
-        </is>
-      </c>
-      <c r="J36" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" s="1" t="inlineStr">
-        <is>
-          <t>Attack3</t>
-        </is>
+          <t>1,2,3,6,10</t>
+        </is>
+      </c>
+      <c r="J36" s="0" t="n">
+        <v>8</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>204003</v>
-      </c>
-      <c r="Q36" s="1" t="inlineStr">
-        <is>
-          <t>0,0.5,0</t>
-        </is>
+        <v>205004</v>
       </c>
       <c r="S36" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="U36" s="1" t="n">
         <v>1</v>
@@ -5134,7 +5142,7 @@
         <v>0</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X36" s="1" t="n">
         <v>0.5</v>
@@ -5146,13 +5154,13 @@
         <v>10</v>
       </c>
       <c r="AA36" s="1" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AB36" s="1" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AE36" s="1" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AF36" s="1" t="n">
         <v>0</v>
@@ -5161,23 +5169,23 @@
         <v>10</v>
       </c>
       <c r="AJ36" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK36" s="1" t="n">
-        <v>6000001</v>
+        <v>7000001</v>
       </c>
       <c r="AL36" s="1" t="inlineStr">
         <is>
-          <t>ui_class_2</t>
+          <t>ui_class_3</t>
         </is>
       </c>
       <c r="AM36" s="1" t="inlineStr">
         <is>
-          <t>Card_Scene_7</t>
+          <t>Card_Scene_1</t>
         </is>
       </c>
       <c r="AN36" s="1" t="n">
-        <v>300600005</v>
+        <v>300700001</v>
       </c>
       <c r="AO36" s="0" t="inlineStr">
         <is>
@@ -5185,10 +5193,10 @@
         </is>
       </c>
       <c r="AR36" s="1" t="n">
-        <v>6005</v>
+        <v>7001</v>
       </c>
       <c r="AS36" s="0" t="n">
-        <v>6005</v>
+        <v>7001</v>
       </c>
       <c r="AT36" s="0" t="inlineStr">
         <is>
@@ -5198,43 +5206,48 @@
     </row>
     <row r="37" customFormat="1" s="1">
       <c r="A37" s="1" t="n">
-        <v>7001</v>
+        <v>7002</v>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>兽人战士</t>
+          <t>兽人投手</t>
         </is>
       </c>
       <c r="C37" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>2000300001,2000400001,</t>
-        </is>
       </c>
       <c r="G37" s="1" t="n">
         <v>7000001</v>
       </c>
-      <c r="H37" s="0" t="n">
-        <v>71010001</v>
+      <c r="H37" s="1" t="n">
+        <v>71000001</v>
       </c>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>1,2,3,6,10</t>
-        </is>
-      </c>
-      <c r="J37" s="0" t="n">
+          <t>1,2,3,5,10</t>
+        </is>
+      </c>
+      <c r="J37" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="N37" s="1" t="inlineStr">
+        <is>
+          <t>Attack3</t>
+        </is>
+      </c>
       <c r="P37" s="1" t="n">
-        <v>205004</v>
+        <v>205001</v>
+      </c>
+      <c r="Q37" s="1" t="inlineStr">
+        <is>
+          <t>0,0.7,0</t>
+        </is>
       </c>
       <c r="S37" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U37" s="1" t="n">
         <v>1</v>
@@ -5261,7 +5274,7 @@
         <v>120</v>
       </c>
       <c r="AE37" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AF37" s="1" t="n">
         <v>0</v>
@@ -5277,7 +5290,7 @@
       </c>
       <c r="AL37" s="1" t="inlineStr">
         <is>
-          <t>ui_class_3</t>
+          <t>ui_class_6</t>
         </is>
       </c>
       <c r="AM37" s="1" t="inlineStr">
@@ -5286,7 +5299,7 @@
         </is>
       </c>
       <c r="AN37" s="1" t="n">
-        <v>300700001</v>
+        <v>300700002</v>
       </c>
       <c r="AO37" s="0" t="inlineStr">
         <is>
@@ -5294,10 +5307,10 @@
         </is>
       </c>
       <c r="AR37" s="1" t="n">
-        <v>7001</v>
+        <v>7002</v>
       </c>
       <c r="AS37" s="0" t="n">
-        <v>7001</v>
+        <v>7002</v>
       </c>
       <c r="AT37" s="0" t="inlineStr">
         <is>
@@ -5307,11 +5320,11 @@
     </row>
     <row r="38" customFormat="1" s="1">
       <c r="A38" s="1" t="n">
-        <v>7002</v>
+        <v>7003</v>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>兽人投手</t>
+          <t>兽人魔法师（火）</t>
         </is>
       </c>
       <c r="C38" s="1" t="n">
@@ -5321,23 +5334,23 @@
         <v>7000001</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>71000001</v>
+        <v>71010004</v>
       </c>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>1,2,3,5,10</t>
+          <t>1,2,3,10,</t>
         </is>
       </c>
       <c r="J38" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>Attack3</t>
+          <t>Attack2</t>
         </is>
       </c>
       <c r="P38" s="1" t="n">
-        <v>205001</v>
+        <v>205002</v>
       </c>
       <c r="Q38" s="1" t="inlineStr">
         <is>
@@ -5357,7 +5370,7 @@
         <v>0</v>
       </c>
       <c r="W38" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X38" s="1" t="n">
         <v>0.5</v>
@@ -5372,10 +5385,10 @@
         <v>45</v>
       </c>
       <c r="AB38" s="1" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AE38" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AF38" s="1" t="n">
         <v>0</v>
@@ -5391,7 +5404,7 @@
       </c>
       <c r="AL38" s="1" t="inlineStr">
         <is>
-          <t>ui_class_6</t>
+          <t>ui_class_10</t>
         </is>
       </c>
       <c r="AM38" s="1" t="inlineStr">
@@ -5400,7 +5413,7 @@
         </is>
       </c>
       <c r="AN38" s="1" t="n">
-        <v>300700002</v>
+        <v>300700003</v>
       </c>
       <c r="AO38" s="0" t="inlineStr">
         <is>
@@ -5408,10 +5421,10 @@
         </is>
       </c>
       <c r="AR38" s="1" t="n">
-        <v>7002</v>
+        <v>7003</v>
       </c>
       <c r="AS38" s="0" t="n">
-        <v>7002</v>
+        <v>7003</v>
       </c>
       <c r="AT38" s="0" t="inlineStr">
         <is>
@@ -5421,11 +5434,11 @@
     </row>
     <row r="39" customFormat="1" s="1">
       <c r="A39" s="1" t="n">
-        <v>7003</v>
+        <v>7004</v>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>兽人魔法师（火）</t>
+          <t>兽人魔法师（冰）</t>
         </is>
       </c>
       <c r="C39" s="1" t="n">
@@ -5451,7 +5464,7 @@
         </is>
       </c>
       <c r="P39" s="1" t="n">
-        <v>205002</v>
+        <v>205003</v>
       </c>
       <c r="Q39" s="1" t="inlineStr">
         <is>
@@ -5505,7 +5518,7 @@
       </c>
       <c r="AL39" s="1" t="inlineStr">
         <is>
-          <t>ui_class_10</t>
+          <t>ui_class_2</t>
         </is>
       </c>
       <c r="AM39" s="1" t="inlineStr">
@@ -5514,7 +5527,7 @@
         </is>
       </c>
       <c r="AN39" s="1" t="n">
-        <v>300700003</v>
+        <v>300700004</v>
       </c>
       <c r="AO39" s="0" t="inlineStr">
         <is>
@@ -5522,10 +5535,10 @@
         </is>
       </c>
       <c r="AR39" s="1" t="n">
-        <v>7003</v>
+        <v>7004</v>
       </c>
       <c r="AS39" s="0" t="n">
-        <v>7003</v>
+        <v>7004</v>
       </c>
       <c r="AT39" s="0" t="inlineStr">
         <is>
@@ -5534,112 +5547,104 @@
       </c>
     </row>
     <row r="40" customFormat="1" s="1">
-      <c r="A40" s="1" t="n">
-        <v>7004</v>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>兽人魔法师（冰）</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="1" t="n">
-        <v>7000001</v>
-      </c>
-      <c r="H40" s="1" t="n">
-        <v>71010004</v>
-      </c>
-      <c r="I40" s="1" t="inlineStr">
+      <c r="A40" s="4" t="n">
+        <v>101001</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>人类-冒险者</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J40" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N40" s="1" t="inlineStr">
-        <is>
-          <t>Attack2</t>
-        </is>
-      </c>
-      <c r="P40" s="1" t="n">
-        <v>205003</v>
-      </c>
-      <c r="Q40" s="1" t="inlineStr">
-        <is>
-          <t>0,0.7,0</t>
-        </is>
-      </c>
-      <c r="S40" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T40" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="U40" s="1" t="n">
+      <c r="J40" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4" t="n"/>
+      <c r="O40" s="4" t="n"/>
+      <c r="P40" s="4" t="n">
+        <v>100001</v>
+      </c>
+      <c r="Q40" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
+        </is>
+      </c>
+      <c r="R40" s="4" t="n"/>
+      <c r="S40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U40" s="4" t="n">
         <v>1</v>
       </c>
       <c r="V40" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W40" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="X40" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y40" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z40" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA40" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="AB40" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE40" s="1" t="n">
+      <c r="W40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y40" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z40" s="4" t="n"/>
+      <c r="AA40" s="4" t="n"/>
+      <c r="AB40" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC40" s="4" t="n"/>
+      <c r="AD40" s="4" t="n"/>
+      <c r="AE40" s="4" t="n">
         <v>10</v>
       </c>
       <c r="AF40" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AG40" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ40" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK40" s="1" t="n">
-        <v>7000001</v>
-      </c>
-      <c r="AL40" s="1" t="inlineStr">
-        <is>
-          <t>ui_class_2</t>
-        </is>
-      </c>
-      <c r="AM40" s="1" t="inlineStr">
-        <is>
-          <t>Card_Scene_1</t>
-        </is>
-      </c>
-      <c r="AN40" s="1" t="n">
-        <v>300700004</v>
-      </c>
-      <c r="AO40" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AR40" s="1" t="n">
-        <v>7004</v>
-      </c>
-      <c r="AS40" s="0" t="n">
-        <v>7004</v>
+      <c r="AG40" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH40" s="4" t="n"/>
+      <c r="AI40" s="4" t="n"/>
+      <c r="AJ40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK40" s="4" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="AL40" s="4" t="inlineStr">
+        <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="AM40" s="4" t="inlineStr">
+        <is>
+          <t>Card_Scene_2</t>
+        </is>
+      </c>
+      <c r="AN40" s="4" t="n"/>
+      <c r="AR40" s="4" t="n">
+        <v>101001</v>
       </c>
       <c r="AT40" s="0" t="inlineStr">
         <is>
@@ -5649,11 +5654,11 @@
     </row>
     <row r="41" customFormat="1" s="2">
       <c r="A41" s="4" t="n">
-        <v>101001</v>
+        <v>101002</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>人类-冒险者</t>
+          <t>人类-持盾战士</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
@@ -5672,12 +5677,16 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K41" s="4" t="n"/>
       <c r="L41" s="4" t="n"/>
       <c r="M41" s="4" t="n"/>
-      <c r="N41" s="4" t="n"/>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>Attack5</t>
+        </is>
+      </c>
       <c r="O41" s="4" t="n"/>
       <c r="P41" s="4" t="n">
         <v>100001</v>
@@ -5715,7 +5724,9 @@
         <v>100</v>
       </c>
       <c r="AC41" s="4" t="n"/>
-      <c r="AD41" s="4" t="n"/>
+      <c r="AD41" s="4" t="n">
+        <v>100</v>
+      </c>
       <c r="AE41" s="4" t="n">
         <v>10</v>
       </c>
@@ -5735,7 +5746,7 @@
       </c>
       <c r="AL41" s="4" t="inlineStr">
         <is>
-          <t>ui_class_3</t>
+          <t>ui_class_7</t>
         </is>
       </c>
       <c r="AM41" s="4" t="inlineStr">
@@ -5745,7 +5756,7 @@
       </c>
       <c r="AN41" s="4" t="n"/>
       <c r="AR41" s="4" t="n">
-        <v>101001</v>
+        <v>101002</v>
       </c>
       <c r="AT41" s="0" t="inlineStr">
         <is>
@@ -5755,11 +5766,11 @@
     </row>
     <row r="42" customFormat="1" s="2">
       <c r="A42" s="4" t="n">
-        <v>101002</v>
+        <v>102001</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>人类-持盾战士</t>
+          <t>人类-弓箭手</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
@@ -5778,23 +5789,23 @@
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="4" t="n"/>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>Attack5</t>
+          <t>Attack4</t>
         </is>
       </c>
       <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n">
-        <v>100001</v>
-      </c>
-      <c r="Q42" s="0" t="inlineStr">
-        <is>
-          <t>0,0.5,0</t>
+        <v>207001</v>
+      </c>
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>0,0.6,0</t>
         </is>
       </c>
       <c r="R42" s="4" t="n"/>
@@ -5802,7 +5813,7 @@
         <v>1</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="U42" s="4" t="n">
         <v>1</v>
@@ -5822,12 +5833,10 @@
       <c r="Z42" s="4" t="n"/>
       <c r="AA42" s="4" t="n"/>
       <c r="AB42" s="4" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AC42" s="4" t="n"/>
-      <c r="AD42" s="4" t="n">
-        <v>100</v>
-      </c>
+      <c r="AD42" s="4" t="n"/>
       <c r="AE42" s="4" t="n">
         <v>10</v>
       </c>
@@ -5847,7 +5856,7 @@
       </c>
       <c r="AL42" s="4" t="inlineStr">
         <is>
-          <t>ui_class_7</t>
+          <t>ui_class_6</t>
         </is>
       </c>
       <c r="AM42" s="4" t="inlineStr">
@@ -5857,7 +5866,7 @@
       </c>
       <c r="AN42" s="4" t="n"/>
       <c r="AR42" s="4" t="n">
-        <v>101002</v>
+        <v>102001</v>
       </c>
       <c r="AT42" s="0" t="inlineStr">
         <is>
@@ -5867,11 +5876,11 @@
     </row>
     <row r="43" customFormat="1" s="2">
       <c r="A43" s="4" t="n">
-        <v>102001</v>
+        <v>102002</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>人类-弓箭手</t>
+          <t>人类-强弓手</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
@@ -5902,7 +5911,7 @@
       </c>
       <c r="O43" s="4" t="n"/>
       <c r="P43" s="4" t="n">
-        <v>207001</v>
+        <v>205001</v>
       </c>
       <c r="Q43" s="4" t="inlineStr">
         <is>
@@ -5967,7 +5976,7 @@
       </c>
       <c r="AN43" s="4" t="n"/>
       <c r="AR43" s="4" t="n">
-        <v>102001</v>
+        <v>102002</v>
       </c>
       <c r="AT43" s="0" t="inlineStr">
         <is>
@@ -5977,11 +5986,11 @@
     </row>
     <row r="44" customFormat="1" s="2">
       <c r="A44" s="4" t="n">
-        <v>102002</v>
+        <v>102003</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>人类-强弓手</t>
+          <t>人类-连射手</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
@@ -6012,7 +6021,7 @@
       </c>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n">
-        <v>205001</v>
+        <v>204001</v>
       </c>
       <c r="Q44" s="4" t="inlineStr">
         <is>
@@ -6077,7 +6086,7 @@
       </c>
       <c r="AN44" s="4" t="n"/>
       <c r="AR44" s="4" t="n">
-        <v>102002</v>
+        <v>102003</v>
       </c>
       <c r="AT44" s="0" t="inlineStr">
         <is>
@@ -6087,11 +6096,11 @@
     </row>
     <row r="45" customFormat="1" s="2">
       <c r="A45" s="4" t="n">
-        <v>102003</v>
+        <v>103001</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>人类-连射手</t>
+          <t>人类-魔法师（火）</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
@@ -6110,19 +6119,19 @@
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
       <c r="M45" s="4" t="n"/>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>Attack4</t>
+          <t>Attack2</t>
         </is>
       </c>
       <c r="O45" s="4" t="n"/>
       <c r="P45" s="4" t="n">
-        <v>204001</v>
+        <v>200002</v>
       </c>
       <c r="Q45" s="4" t="inlineStr">
         <is>
@@ -6134,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U45" s="4" t="n">
         <v>1</v>
@@ -6154,7 +6163,7 @@
       <c r="Z45" s="4" t="n"/>
       <c r="AA45" s="4" t="n"/>
       <c r="AB45" s="4" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AC45" s="4" t="n"/>
       <c r="AD45" s="4" t="n"/>
@@ -6177,7 +6186,7 @@
       </c>
       <c r="AL45" s="4" t="inlineStr">
         <is>
-          <t>ui_class_6</t>
+          <t>ui_class_2</t>
         </is>
       </c>
       <c r="AM45" s="4" t="inlineStr">
@@ -6187,7 +6196,7 @@
       </c>
       <c r="AN45" s="4" t="n"/>
       <c r="AR45" s="4" t="n">
-        <v>102003</v>
+        <v>103001</v>
       </c>
       <c r="AT45" s="0" t="inlineStr">
         <is>
@@ -6197,11 +6206,11 @@
     </row>
     <row r="46" customFormat="1" s="2">
       <c r="A46" s="4" t="n">
-        <v>103001</v>
+        <v>103002</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>人类-魔法师（火）</t>
+          <t>人类-魔法师（水）</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
@@ -6232,7 +6241,7 @@
       </c>
       <c r="O46" s="4" t="n"/>
       <c r="P46" s="4" t="n">
-        <v>200002</v>
+        <v>200003</v>
       </c>
       <c r="Q46" s="4" t="inlineStr">
         <is>
@@ -6297,7 +6306,7 @@
       </c>
       <c r="AN46" s="4" t="n"/>
       <c r="AR46" s="4" t="n">
-        <v>103001</v>
+        <v>103002</v>
       </c>
       <c r="AT46" s="0" t="inlineStr">
         <is>
@@ -6307,11 +6316,11 @@
     </row>
     <row r="47" customFormat="1" s="2">
       <c r="A47" s="4" t="n">
-        <v>103002</v>
+        <v>103003</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>人类-魔法师（水）</t>
+          <t>人类-魔法师（冰）</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
@@ -6342,7 +6351,7 @@
       </c>
       <c r="O47" s="4" t="n"/>
       <c r="P47" s="4" t="n">
-        <v>200003</v>
+        <v>200004</v>
       </c>
       <c r="Q47" s="4" t="inlineStr">
         <is>
@@ -6407,7 +6416,7 @@
       </c>
       <c r="AN47" s="4" t="n"/>
       <c r="AR47" s="4" t="n">
-        <v>103002</v>
+        <v>103003</v>
       </c>
       <c r="AT47" s="0" t="inlineStr">
         <is>
@@ -6417,11 +6426,11 @@
     </row>
     <row r="48" customFormat="1" s="2">
       <c r="A48" s="4" t="n">
-        <v>103003</v>
+        <v>103004</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>人类-魔法师（冰）</t>
+          <t>人类-魔法师（雷）</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
@@ -6452,7 +6461,7 @@
       </c>
       <c r="O48" s="4" t="n"/>
       <c r="P48" s="4" t="n">
-        <v>200004</v>
+        <v>800001</v>
       </c>
       <c r="Q48" s="4" t="inlineStr">
         <is>
@@ -6517,7 +6526,7 @@
       </c>
       <c r="AN48" s="4" t="n"/>
       <c r="AR48" s="4" t="n">
-        <v>103003</v>
+        <v>103004</v>
       </c>
       <c r="AT48" s="0" t="inlineStr">
         <is>
@@ -6527,11 +6536,11 @@
     </row>
     <row r="49" customFormat="1" s="2">
       <c r="A49" s="4" t="n">
-        <v>103004</v>
+        <v>103101</v>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>人类-魔法师（雷）</t>
+          <t>人类-大魔法师（火）</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
@@ -6562,7 +6571,7 @@
       </c>
       <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n">
-        <v>800001</v>
+        <v>200002</v>
       </c>
       <c r="Q49" s="4" t="inlineStr">
         <is>
@@ -6574,7 +6583,7 @@
         <v>1</v>
       </c>
       <c r="T49" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U49" s="4" t="n">
         <v>1</v>
@@ -6617,7 +6626,7 @@
       </c>
       <c r="AL49" s="4" t="inlineStr">
         <is>
-          <t>ui_class_2</t>
+          <t>ui_class_5</t>
         </is>
       </c>
       <c r="AM49" s="4" t="inlineStr">
@@ -6627,7 +6636,7 @@
       </c>
       <c r="AN49" s="4" t="n"/>
       <c r="AR49" s="4" t="n">
-        <v>103004</v>
+        <v>103101</v>
       </c>
       <c r="AT49" s="0" t="inlineStr">
         <is>
@@ -6637,11 +6646,11 @@
     </row>
     <row r="50" customFormat="1" s="2">
       <c r="A50" s="4" t="n">
-        <v>103101</v>
+        <v>103102</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>人类-大魔法师（火）</t>
+          <t>人类-大魔法师（水）</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
@@ -6672,7 +6681,7 @@
       </c>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n">
-        <v>200002</v>
+        <v>200003</v>
       </c>
       <c r="Q50" s="4" t="inlineStr">
         <is>
@@ -6737,7 +6746,7 @@
       </c>
       <c r="AN50" s="4" t="n"/>
       <c r="AR50" s="4" t="n">
-        <v>103101</v>
+        <v>103102</v>
       </c>
       <c r="AT50" s="0" t="inlineStr">
         <is>
@@ -6747,11 +6756,11 @@
     </row>
     <row r="51" customFormat="1" s="2">
       <c r="A51" s="4" t="n">
-        <v>103102</v>
+        <v>103103</v>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>人类-大魔法师（水）</t>
+          <t>人类-大魔法师（冰）</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
@@ -6782,7 +6791,7 @@
       </c>
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n">
-        <v>200003</v>
+        <v>200004</v>
       </c>
       <c r="Q51" s="4" t="inlineStr">
         <is>
@@ -6847,7 +6856,7 @@
       </c>
       <c r="AN51" s="4" t="n"/>
       <c r="AR51" s="4" t="n">
-        <v>103102</v>
+        <v>103103</v>
       </c>
       <c r="AT51" s="0" t="inlineStr">
         <is>
@@ -6856,108 +6865,92 @@
       </c>
     </row>
     <row r="52" customFormat="1" s="2">
-      <c r="A52" s="4" t="n">
-        <v>103103</v>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>人类-大魔法师（冰）</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="n"/>
-      <c r="G52" s="4" t="n">
+      <c r="A52" s="0" t="n">
+        <v>103104</v>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>人类-大魔法师（雷）</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" s="0" t="n">
         <v>1000001</v>
       </c>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="inlineStr">
+      <c r="I52" s="0" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" s="4" t="n"/>
-      <c r="L52" s="4" t="n"/>
-      <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="inlineStr">
+      <c r="J52" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="0" t="inlineStr">
         <is>
           <t>Attack2</t>
         </is>
       </c>
-      <c r="O52" s="4" t="n"/>
-      <c r="P52" s="4" t="n">
-        <v>200004</v>
+      <c r="P52" s="0" t="n">
+        <v>800001</v>
       </c>
       <c r="Q52" s="4" t="inlineStr">
         <is>
           <t>0,0.6,0</t>
         </is>
       </c>
-      <c r="R52" s="4" t="n"/>
-      <c r="S52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T52" s="4" t="n">
+      <c r="S52" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="U52" s="4" t="n">
+      <c r="U52" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V52" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X52" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y52" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z52" s="4" t="n"/>
-      <c r="AA52" s="4" t="n"/>
-      <c r="AB52" s="4" t="n">
+      <c r="W52" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X52" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y52" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB52" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="AC52" s="4" t="n"/>
-      <c r="AD52" s="4" t="n"/>
-      <c r="AE52" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH52" s="4" t="n"/>
-      <c r="AI52" s="4" t="n"/>
-      <c r="AJ52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK52" s="4" t="n">
+      <c r="AE52" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ52" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK52" s="0" t="n">
         <v>1000001</v>
       </c>
-      <c r="AL52" s="4" t="inlineStr">
+      <c r="AL52" s="0" t="inlineStr">
         <is>
           <t>ui_class_5</t>
         </is>
       </c>
-      <c r="AM52" s="4" t="inlineStr">
+      <c r="AM52" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_2</t>
         </is>
       </c>
-      <c r="AN52" s="4" t="n"/>
-      <c r="AR52" s="4" t="n">
-        <v>103103</v>
+      <c r="AR52" s="0" t="n">
+        <v>103104</v>
       </c>
       <c r="AT52" s="0" t="inlineStr">
         <is>
@@ -6967,11 +6960,11 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="n">
-        <v>103104</v>
+        <v>103105</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>人类-大魔法师（雷）</t>
+          <t>骷髅召唤师</t>
         </is>
       </c>
       <c r="C53" s="0" t="n">
@@ -6994,9 +6987,9 @@
         </is>
       </c>
       <c r="P53" s="0" t="n">
-        <v>800001</v>
-      </c>
-      <c r="Q53" s="4" t="inlineStr">
+        <v>500004</v>
+      </c>
+      <c r="Q53" s="0" t="inlineStr">
         <is>
           <t>0,0.6,0</t>
         </is>
@@ -7005,7 +6998,7 @@
         <v>1</v>
       </c>
       <c r="T53" s="0" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U53" s="0" t="n">
         <v>1</v>
@@ -7014,7 +7007,7 @@
         <v>0</v>
       </c>
       <c r="W53" s="0" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="X53" s="0" t="n">
         <v>0.5</v>
@@ -7042,7 +7035,7 @@
       </c>
       <c r="AL53" s="0" t="inlineStr">
         <is>
-          <t>ui_class_5</t>
+          <t>ui_class_2</t>
         </is>
       </c>
       <c r="AM53" s="0" t="inlineStr">
@@ -7051,7 +7044,7 @@
         </is>
       </c>
       <c r="AR53" s="0" t="n">
-        <v>103104</v>
+        <v>103105</v>
       </c>
       <c r="AT53" s="0" t="inlineStr">
         <is>
@@ -7061,18 +7054,21 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="n">
-        <v>103105</v>
+        <v>103106</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>骷髅召唤师</t>
+          <t>骷髅战士（召唤物，克隆2001改索敌防守方）</t>
         </is>
       </c>
       <c r="C54" s="0" t="n">
         <v>2</v>
       </c>
       <c r="G54" s="0" t="n">
-        <v>1000001</v>
+        <v>2000001</v>
+      </c>
+      <c r="H54" s="0" t="n">
+        <v>21010001</v>
       </c>
       <c r="I54" s="0" t="inlineStr">
         <is>
@@ -7080,7 +7076,7 @@
         </is>
       </c>
       <c r="J54" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N54" s="0" t="inlineStr">
         <is>
@@ -7088,18 +7084,18 @@
         </is>
       </c>
       <c r="P54" s="0" t="n">
-        <v>500004</v>
+        <v>100001</v>
       </c>
       <c r="Q54" s="0" t="inlineStr">
         <is>
-          <t>0,0.6,0</t>
+          <t>0,0.5,0</t>
         </is>
       </c>
       <c r="S54" s="0" t="n">
         <v>1</v>
       </c>
       <c r="T54" s="0" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U54" s="0" t="n">
         <v>1</v>
@@ -7108,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="W54" s="0" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="X54" s="0" t="n">
         <v>0.5</v>
@@ -7116,8 +7112,14 @@
       <c r="Y54" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="Z54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="AB54" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AE54" s="0" t="n">
         <v>10</v>
@@ -7129,23 +7131,34 @@
         <v>10</v>
       </c>
       <c r="AJ54" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK54" s="0" t="n">
-        <v>1000001</v>
+        <v>0</v>
       </c>
       <c r="AL54" s="0" t="inlineStr">
         <is>
-          <t>ui_class_2</t>
+          <t>ui_class_3</t>
         </is>
       </c>
       <c r="AM54" s="0" t="inlineStr">
         <is>
-          <t>Card_Scene_2</t>
+          <t>Card_Scene_1</t>
+        </is>
+      </c>
+      <c r="AN54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO54" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
         </is>
       </c>
       <c r="AR54" s="0" t="n">
-        <v>103105</v>
+        <v>2001</v>
+      </c>
+      <c r="AS54" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="AT54" s="0" t="inlineStr">
         <is>
@@ -7155,11 +7168,11 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>103106</v>
+        <v>103107</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>骷髅战士（召唤物，克隆2001改索敌防守方）</t>
+          <t>骷髅投手（召唤物，克隆2002改索敌防守方）</t>
         </is>
       </c>
       <c r="C55" s="0" t="n">
@@ -7169,7 +7182,7 @@
         <v>2000001</v>
       </c>
       <c r="H55" s="0" t="n">
-        <v>21010001</v>
+        <v>21000001</v>
       </c>
       <c r="I55" s="0" t="inlineStr">
         <is>
@@ -7177,26 +7190,26 @@
         </is>
       </c>
       <c r="J55" s="0" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N55" s="0" t="inlineStr">
         <is>
-          <t>Attack2</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="P55" s="0" t="n">
-        <v>100001</v>
+        <v>200001</v>
       </c>
       <c r="Q55" s="0" t="inlineStr">
         <is>
-          <t>0,0.5,0</t>
+          <t>0,0.7,0</t>
         </is>
       </c>
       <c r="S55" s="0" t="n">
         <v>1</v>
       </c>
       <c r="T55" s="0" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U55" s="0" t="n">
         <v>1</v>
@@ -7220,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AB55" s="0" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AE55" s="0" t="n">
         <v>10</v>
@@ -7239,7 +7252,7 @@
       </c>
       <c r="AL55" s="0" t="inlineStr">
         <is>
-          <t>ui_class_3</t>
+          <t>ui_class_6</t>
         </is>
       </c>
       <c r="AM55" s="0" t="inlineStr">
@@ -7256,7 +7269,7 @@
         </is>
       </c>
       <c r="AR55" s="0" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="AS55" s="0" t="n">
         <v>0</v>
@@ -7269,21 +7282,21 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>103107</v>
+        <v>103108</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>骷髅投手（召唤物，克隆2002改索敌防守方）</t>
+          <t>人类-牧师</t>
         </is>
       </c>
       <c r="C56" s="0" t="n">
         <v>2</v>
       </c>
       <c r="G56" s="0" t="n">
-        <v>2000001</v>
+        <v>1000001</v>
       </c>
       <c r="H56" s="0" t="n">
-        <v>21000001</v>
+        <v>0</v>
       </c>
       <c r="I56" s="0" t="inlineStr">
         <is>
@@ -7291,26 +7304,32 @@
         </is>
       </c>
       <c r="J56" s="0" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N56" s="0" t="inlineStr">
         <is>
-          <t>Attack</t>
-        </is>
+          <t>Attack2</t>
+        </is>
+      </c>
+      <c r="O56" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="P56" s="0" t="n">
-        <v>200001</v>
+        <v>102003</v>
       </c>
       <c r="Q56" s="0" t="inlineStr">
         <is>
-          <t>0,0.7,0</t>
-        </is>
+          <t>0,0.6,0</t>
+        </is>
+      </c>
+      <c r="R56" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="S56" s="0" t="n">
         <v>1</v>
       </c>
       <c r="T56" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U56" s="0" t="n">
         <v>1</v>
@@ -7319,7 +7338,7 @@
         <v>0</v>
       </c>
       <c r="W56" s="0" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X56" s="0" t="n">
         <v>0.5</v>
@@ -7334,7 +7353,13 @@
         <v>0</v>
       </c>
       <c r="AB56" s="0" t="n">
-        <v>70</v>
+        <v>50</v>
+      </c>
+      <c r="AC56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="AE56" s="0" t="n">
         <v>10</v>
@@ -7345,32 +7370,36 @@
       <c r="AG56" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="AH56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ56" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK56" s="0" t="n">
-        <v>0</v>
+        <v>1000001</v>
       </c>
       <c r="AL56" s="0" t="inlineStr">
         <is>
-          <t>ui_class_6</t>
+          <t>ui_class_5</t>
         </is>
       </c>
       <c r="AM56" s="0" t="inlineStr">
         <is>
-          <t>Card_Scene_1</t>
+          <t>Card_Scene_2</t>
         </is>
       </c>
       <c r="AN56" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="AO56" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
+      <c r="AQ56" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="AR56" s="0" t="n">
-        <v>2002</v>
+        <v>103108</v>
       </c>
       <c r="AS56" s="0" t="n">
         <v>0</v>
@@ -7383,54 +7412,50 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
-        <v>103108</v>
+        <v>104001</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>人类-牧师</t>
+          <t>人类-盗贼</t>
         </is>
       </c>
       <c r="C57" s="0" t="n">
         <v>2</v>
+      </c>
+      <c r="F57" s="0" t="inlineStr">
+        <is>
+          <t>2000100002,</t>
+        </is>
       </c>
       <c r="G57" s="0" t="n">
         <v>1000001</v>
       </c>
-      <c r="H57" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="I57" s="0" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
       <c r="J57" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N57" s="0" t="inlineStr">
         <is>
-          <t>Attack2</t>
-        </is>
-      </c>
-      <c r="O57" s="0" t="n">
-        <v>0</v>
+          <t>Attack6</t>
+        </is>
       </c>
       <c r="P57" s="0" t="n">
-        <v>102003</v>
+        <v>100002</v>
       </c>
       <c r="Q57" s="0" t="inlineStr">
         <is>
-          <t>0,0.6,0</t>
-        </is>
-      </c>
-      <c r="R57" s="0" t="n">
-        <v>0</v>
+          <t>0,0.5,0</t>
+        </is>
       </c>
       <c r="S57" s="0" t="n">
         <v>1</v>
       </c>
       <c r="T57" s="0" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="U57" s="0" t="n">
         <v>1</v>
@@ -7439,7 +7464,7 @@
         <v>0</v>
       </c>
       <c r="W57" s="0" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X57" s="0" t="n">
         <v>0.5</v>
@@ -7447,20 +7472,8 @@
       <c r="Y57" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="AB57" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="AC57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="0" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE57" s="0" t="n">
         <v>10</v>
@@ -7469,13 +7482,7 @@
         <v>0</v>
       </c>
       <c r="AG57" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI57" s="0" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ57" s="0" t="n">
         <v>1</v>
@@ -7485,7 +7492,7 @@
       </c>
       <c r="AL57" s="0" t="inlineStr">
         <is>
-          <t>ui_class_5</t>
+          <t>ui_class_3</t>
         </is>
       </c>
       <c r="AM57" s="0" t="inlineStr">
@@ -7493,17 +7500,8 @@
           <t>Card_Scene_2</t>
         </is>
       </c>
-      <c r="AN57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ57" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="AR57" s="0" t="n">
-        <v>103108</v>
-      </c>
-      <c r="AS57" s="0" t="n">
-        <v>0</v>
+        <v>104001</v>
       </c>
       <c r="AT57" s="0" t="inlineStr">
         <is>
@@ -7513,20 +7511,15 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
-        <v>104001</v>
+        <v>104002</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>人类-盗贼</t>
+          <t>人类-双持战士</t>
         </is>
       </c>
       <c r="C58" s="0" t="n">
         <v>2</v>
-      </c>
-      <c r="F58" s="0" t="inlineStr">
-        <is>
-          <t>2000100001,</t>
-        </is>
       </c>
       <c r="G58" s="0" t="n">
         <v>1000001</v>
@@ -7537,15 +7530,10 @@
         </is>
       </c>
       <c r="J58" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N58" s="0" t="inlineStr">
-        <is>
-          <t>Attack6</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="P58" s="0" t="n">
-        <v>100002</v>
+        <v>100001</v>
       </c>
       <c r="Q58" s="0" t="inlineStr">
         <is>
@@ -7583,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="AG58" s="0" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AJ58" s="0" t="n">
         <v>1</v>
@@ -7602,7 +7590,7 @@
         </is>
       </c>
       <c r="AR58" s="0" t="n">
-        <v>104001</v>
+        <v>104002</v>
       </c>
       <c r="AT58" s="0" t="inlineStr">
         <is>
@@ -7612,11 +7600,11 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>104002</v>
+        <v>104101</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>人类-双持战士</t>
+          <t>人类-大剑战士</t>
         </is>
       </c>
       <c r="C59" s="0" t="n">
@@ -7631,10 +7619,15 @@
         </is>
       </c>
       <c r="J59" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="N59" s="0" t="inlineStr">
+        <is>
+          <t>Attack8</t>
+        </is>
       </c>
       <c r="P59" s="0" t="n">
-        <v>100001</v>
+        <v>101006</v>
       </c>
       <c r="Q59" s="0" t="inlineStr">
         <is>
@@ -7665,6 +7658,9 @@
       <c r="AB59" s="0" t="n">
         <v>100</v>
       </c>
+      <c r="AD59" s="0" t="n">
+        <v>100</v>
+      </c>
       <c r="AE59" s="0" t="n">
         <v>10</v>
       </c>
@@ -7682,7 +7678,7 @@
       </c>
       <c r="AL59" s="0" t="inlineStr">
         <is>
-          <t>ui_class_3</t>
+          <t>ui_class_7</t>
         </is>
       </c>
       <c r="AM59" s="0" t="inlineStr">
@@ -7691,7 +7687,7 @@
         </is>
       </c>
       <c r="AR59" s="0" t="n">
-        <v>104002</v>
+        <v>104101</v>
       </c>
       <c r="AT59" s="0" t="inlineStr">
         <is>
@@ -7701,15 +7697,20 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>104101</v>
+        <v>104102</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>人类-大剑战士</t>
+          <t>人类-大盾战士</t>
         </is>
       </c>
       <c r="C60" s="0" t="n">
         <v>2</v>
+      </c>
+      <c r="F60" s="0" t="inlineStr">
+        <is>
+          <t>2000600001,</t>
+        </is>
       </c>
       <c r="G60" s="0" t="n">
         <v>1000001</v>
@@ -7720,15 +7721,20 @@
         </is>
       </c>
       <c r="J60" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="M60" s="0" t="inlineStr">
+        <is>
+          <t>Walk4</t>
+        </is>
       </c>
       <c r="N60" s="0" t="inlineStr">
         <is>
-          <t>Attack8</t>
+          <t>Attack7</t>
         </is>
       </c>
       <c r="P60" s="0" t="n">
-        <v>101006</v>
+        <v>100001</v>
       </c>
       <c r="Q60" s="0" t="inlineStr">
         <is>
@@ -7788,7 +7794,7 @@
         </is>
       </c>
       <c r="AR60" s="0" t="n">
-        <v>104101</v>
+        <v>104102</v>
       </c>
       <c r="AT60" s="0" t="inlineStr">
         <is>
@@ -7798,20 +7804,15 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>104102</v>
+        <v>104103</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>人类-大盾战士</t>
+          <t>人类-长枪骑士</t>
         </is>
       </c>
       <c r="C61" s="0" t="n">
         <v>2</v>
-      </c>
-      <c r="F61" s="0" t="inlineStr">
-        <is>
-          <t>2000600001,</t>
-        </is>
       </c>
       <c r="G61" s="0" t="n">
         <v>1000001</v>
@@ -7822,20 +7823,30 @@
         </is>
       </c>
       <c r="J61" s="0" t="n">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="K61" s="0" t="inlineStr">
+        <is>
+          <t>Idle2</t>
+        </is>
+      </c>
+      <c r="L61" s="0" t="inlineStr">
+        <is>
+          <t>Dead2</t>
+        </is>
       </c>
       <c r="M61" s="0" t="inlineStr">
         <is>
-          <t>Walk4</t>
+          <t>Walk2</t>
         </is>
       </c>
       <c r="N61" s="0" t="inlineStr">
         <is>
-          <t>Attack7</t>
+          <t>Attack9</t>
         </is>
       </c>
       <c r="P61" s="0" t="n">
-        <v>100001</v>
+        <v>101006</v>
       </c>
       <c r="Q61" s="0" t="inlineStr">
         <is>
@@ -7895,7 +7906,7 @@
         </is>
       </c>
       <c r="AR61" s="0" t="n">
-        <v>104102</v>
+        <v>104103</v>
       </c>
       <c r="AT61" s="0" t="inlineStr">
         <is>
@@ -7905,15 +7916,20 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>104103</v>
+        <v>104104</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>人类-长枪骑士</t>
+          <t>人类-大剑战士-勇者</t>
         </is>
       </c>
       <c r="C62" s="0" t="n">
         <v>2</v>
+      </c>
+      <c r="F62" s="0" t="inlineStr">
+        <is>
+          <t>2000100002,</t>
+        </is>
       </c>
       <c r="G62" s="0" t="n">
         <v>1000001</v>
@@ -7924,30 +7940,15 @@
         </is>
       </c>
       <c r="J62" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="K62" s="0" t="inlineStr">
-        <is>
-          <t>Idle2</t>
-        </is>
-      </c>
-      <c r="L62" s="0" t="inlineStr">
-        <is>
-          <t>Dead2</t>
-        </is>
-      </c>
-      <c r="M62" s="0" t="inlineStr">
-        <is>
-          <t>Walk2</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="N62" s="0" t="inlineStr">
         <is>
-          <t>Attack9</t>
+          <t>Attack8</t>
         </is>
       </c>
       <c r="P62" s="0" t="n">
-        <v>101006</v>
+        <v>101007</v>
       </c>
       <c r="Q62" s="0" t="inlineStr">
         <is>
@@ -8007,7 +8008,7 @@
         </is>
       </c>
       <c r="AR62" s="0" t="n">
-        <v>104103</v>
+        <v>104101</v>
       </c>
       <c r="AT62" s="0" t="inlineStr">
         <is>
@@ -8016,100 +8017,116 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="0" t="n">
-        <v>104104</v>
-      </c>
-      <c r="B63" s="0" t="inlineStr">
-        <is>
-          <t>人类-大剑战士-勇者</t>
-        </is>
-      </c>
-      <c r="C63" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F63" s="0" t="inlineStr">
-        <is>
-          <t>2000100001,</t>
-        </is>
-      </c>
-      <c r="G63" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="I63" s="0" t="inlineStr">
+      <c r="A63" s="5" t="n">
+        <v>900001</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>测试骷髅战士</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>21010001</v>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J63" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N63" s="0" t="inlineStr">
-        <is>
-          <t>Attack8</t>
-        </is>
-      </c>
-      <c r="P63" s="0" t="n">
-        <v>101007</v>
+      <c r="J63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>Attack2</t>
+        </is>
+      </c>
+      <c r="O63" s="5" t="n"/>
+      <c r="P63" s="5" t="n">
+        <v>100001</v>
       </c>
       <c r="Q63" s="0" t="inlineStr">
         <is>
           <t>0,0.5,0</t>
         </is>
       </c>
-      <c r="S63" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="T63" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U63" s="0" t="n">
+      <c r="R63" s="5" t="n"/>
+      <c r="S63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T63" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U63" s="5" t="n">
         <v>1</v>
       </c>
       <c r="V63" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W63" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X63" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y63" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB63" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AD63" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE63" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG63" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ63" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK63" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="AL63" s="0" t="inlineStr">
-        <is>
-          <t>ui_class_7</t>
-        </is>
-      </c>
-      <c r="AM63" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_2</t>
-        </is>
-      </c>
-      <c r="AR63" s="0" t="n">
-        <v>104101</v>
+      <c r="W63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X63" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y63" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA63" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB63" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AC63" s="5" t="n"/>
+      <c r="AD63" s="5" t="n"/>
+      <c r="AE63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH63" s="5" t="n"/>
+      <c r="AI63" s="5" t="n"/>
+      <c r="AJ63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK63" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="AL63" s="5" t="inlineStr">
+        <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="AM63" s="5" t="inlineStr">
+        <is>
+          <t>Card_Scene_1</t>
+        </is>
+      </c>
+      <c r="AN63" s="5" t="n">
+        <v>300200001</v>
+      </c>
+      <c r="AR63" s="5" t="n">
+        <v>900001</v>
       </c>
       <c r="AT63" s="0" t="inlineStr">
         <is>
@@ -8119,11 +8136,11 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
-        <v>900001</v>
+        <v>900002</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>测试骷髅战士</t>
+          <t>测试骷髅投手</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
@@ -8136,7 +8153,7 @@
         <v>2000001</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>21010001</v>
+        <v>21000001</v>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
@@ -8144,23 +8161,23 @@
         </is>
       </c>
       <c r="J64" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K64" s="5" t="n"/>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="5" t="n"/>
       <c r="N64" s="5" t="inlineStr">
         <is>
-          <t>Attack2</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="O64" s="5" t="n"/>
       <c r="P64" s="5" t="n">
-        <v>100001</v>
-      </c>
-      <c r="Q64" s="0" t="inlineStr">
-        <is>
-          <t>0,0.5,0</t>
+        <v>200001</v>
+      </c>
+      <c r="Q64" s="5" t="inlineStr">
+        <is>
+          <t>0,0.7,0</t>
         </is>
       </c>
       <c r="R64" s="5" t="n"/>
@@ -8168,7 +8185,7 @@
         <v>2</v>
       </c>
       <c r="T64" s="5" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="U64" s="5" t="n">
         <v>1</v>
@@ -8186,7 +8203,7 @@
         <v>0.5</v>
       </c>
       <c r="Z64" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA64" s="5" t="n">
         <v>10</v>
@@ -8215,7 +8232,7 @@
       </c>
       <c r="AL64" s="5" t="inlineStr">
         <is>
-          <t>ui_class_3</t>
+          <t>ui_class_6</t>
         </is>
       </c>
       <c r="AM64" s="5" t="inlineStr">
@@ -8224,130 +8241,12 @@
         </is>
       </c>
       <c r="AN64" s="5" t="n">
-        <v>300200001</v>
+        <v>300200002</v>
       </c>
       <c r="AR64" s="5" t="n">
-        <v>900001</v>
+        <v>900002</v>
       </c>
       <c r="AT64" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="n">
-        <v>900002</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>测试骷髅投手</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D65" s="5" t="n"/>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="n"/>
-      <c r="G65" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="H65" s="5" t="n">
-        <v>21000001</v>
-      </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>1,2,3,10,</t>
-        </is>
-      </c>
-      <c r="J65" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K65" s="5" t="n"/>
-      <c r="L65" s="5" t="n"/>
-      <c r="M65" s="5" t="n"/>
-      <c r="N65" s="5" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="O65" s="5" t="n"/>
-      <c r="P65" s="5" t="n">
-        <v>200001</v>
-      </c>
-      <c r="Q65" s="5" t="inlineStr">
-        <is>
-          <t>0,0.7,0</t>
-        </is>
-      </c>
-      <c r="R65" s="5" t="n"/>
-      <c r="S65" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T65" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="U65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V65" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X65" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y65" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z65" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA65" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB65" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AC65" s="5" t="n"/>
-      <c r="AD65" s="5" t="n"/>
-      <c r="AE65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF65" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG65" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH65" s="5" t="n"/>
-      <c r="AI65" s="5" t="n"/>
-      <c r="AJ65" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK65" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="AL65" s="5" t="inlineStr">
-        <is>
-          <t>ui_class_6</t>
-        </is>
-      </c>
-      <c r="AM65" s="5" t="inlineStr">
-        <is>
-          <t>Card_Scene_1</t>
-        </is>
-      </c>
-      <c r="AN65" s="5" t="n">
-        <v>300200002</v>
-      </c>
-      <c r="AR65" s="5" t="n">
-        <v>900002</v>
-      </c>
-      <c r="AT65" s="0" t="inlineStr">
         <is>
           <t>1,3,4,6</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -7473,7 +7473,7 @@
         <v>0.5</v>
       </c>
       <c r="AB57" s="0" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AE57" s="0" t="n">
         <v>10</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CreatureInfo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreatureInfo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CreatureInfo'!$A$1:$AN$65</definedName>
@@ -2462,6 +2462,11 @@
       <c r="C12" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2000200002,2000500001,</t>
+        </is>
+      </c>
       <c r="G12" s="1" t="n">
         <v>1000001</v>
       </c>
@@ -2797,6 +2802,11 @@
       <c r="C15" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2000100003,</t>
+        </is>
+      </c>
       <c r="G15" s="1" t="n">
         <v>2000001</v>
       </c>
@@ -2911,6 +2921,11 @@
       <c r="C16" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2000200002,2000500001,</t>
+        </is>
+      </c>
       <c r="G16" s="1" t="n">
         <v>2000001</v>
       </c>
@@ -4064,7 +4079,7 @@
         <v>100</v>
       </c>
       <c r="AE26" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AF26" s="1" t="n">
         <v>0</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreatureInfo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CreatureInfo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CreatureInfo'!$A$1:$AN$65</definedName>
@@ -2462,7 +2462,7 @@
       <c r="C12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>2000200002,2000500001,</t>
         </is>
@@ -2802,7 +2802,7 @@
       <c r="C15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="0" t="inlineStr">
         <is>
           <t>2000100003,</t>
         </is>
@@ -2921,7 +2921,7 @@
       <c r="C16" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="0" t="inlineStr">
         <is>
           <t>2000200002,2000500001,</t>
         </is>
@@ -7722,11 +7722,7 @@
       <c r="C60" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F60" s="0" t="inlineStr">
-        <is>
-          <t>2000600001,</t>
-        </is>
-      </c>
+      <c r="F60" s="0" t="n"/>
       <c r="G60" s="0" t="n">
         <v>1000001</v>
       </c>
